--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>High for the table-bleed mechanism; the post-Z RAM tail (~2,929 pairs up to 0x806A102E) is not modeled - documented limitation, needs original ROM bytes.</t>
+          <t>High for the table-bleed mechanism. The post-Z RAM tail is now modeled (758 pairs, see row 35); 21 obscure entries omitted as documented.</t>
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
@@ -1275,10 +1275,26 @@
       <c r="K34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>NTSC-U post-Z RAM tail modeled (758 pairs); web research cross-check</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Hunter R. 'Exploring Animal Crossing's Bugged Trigram Check' (https://hunter-r.com/posts/ac-trigrams/) and AC-Letter-Scorer repo (https://github.com/HunterRDev/AC-Letter-Scorer, Resources/trigrams-bugged.txt): the 5,858-byte RAM tail past the Z table holds ~2,929 pairs; Hunter's ~~~ section gives 779 deduplicated typeable pairs. Reconstructed 758 as game bytes via the decomp's m_font.h charset (bytes 0-31 accented, 32-126 ASCII except game-specials like 92=angry-symbol, 128+ symbols); 21 entries use obscure symbols whose byte mapping could not be determined and are omitted. Added as TRIGRAM_RAM_EXTRA in letter_score_tables.rs; TrigramMode::NtscU now scans tables X-Z then the tail. Validation: per-letter effective counts match Hunter's published table (A=1000 ... Z=780, total 23,670) to within the 21 omitted pairs; 'A! ' scores 0 Intended vs +3 NtscU via the tail's ('!',' ') pair.</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>NtscU mode is now faithful for all realistic (keyboard-typeable) input; the C ABI still defaults to Intended (consistent with the port's BUGFIXES build). The 21 omitted pairs are documented in letter_score.rs.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>High for the 758 reconstructed pairs (exact per-letter count validation); Medium for a handful of reconstructed symbol mappings (section/pilcrow, macron, ETH); the 21 omitted are explicitly listed.</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -4768,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -6746,25 +6762,6 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1248,22 +1248,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Compile verification of the letter module (unit tests written, not run)</t>
+          <t>Test run of the letter module (authorized 2026-10-06): all 16 unit tests pass</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>cargo check --lib passes with no new warnings (one pre-existing unused_unsafe warning in dvd.rs from toolchain drift; file untouched). Unit tests written in-module covering each check A-G, both trigram modes, quest rank extremes, and the '!!!!!' case - not run per the standing no-tests-without-authorization rule.</t>
+          <t>cargo test --lib letter_score: 16 passed, 0 failed. Covers each check A-G, both trigram modes (incl. new RAM-tail test), quest extremes, '!!!!!' case, friendship/reply rules.</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Awaiting authorization to run cargo test; the full i686 Windows build happens on the MSYS2 machine.</t>
+          <t>Behavioral verification complete for the letter module; the full i686 Windows build still runs on the MSYS2 machine.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Medium - compile-verified only; behavioral verification pending a test run.</t>
+          <t>High - all tests pass.</t>
         </is>
       </c>
       <c r="E34" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1304,10 +1304,26 @@
       <c r="K35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Real-time/calendar engine ported to Rust (game_time.rs): OS time + game RTC + game clock</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>OSTime ticks (40.5 MHz, epoch 2000-01-01, GC_UNIX_EPOCH_DIFF=946684800) &lt;-&gt; CalendarTime via exact port of OSTime.c GetDates (BIAS=0xB2575, wday=(days+6)%7, Gregorian leap rule). Game RTC layer (lb_rtc.c): RtcTime, rtc_week (1901-01-01 anchor), get_days_by_month, weekly_day (nth-weekday incl. last-of-month), interval_days with the original's century-blind leap counting (faithful quirk), add/sub helpers.</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>The rewrite now owns the full time stack behind a Rust API; C ABI wiring is future work. Calendar math verified by roundtrip/weekday tests.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>High - algorithms ported line-by-line from the decomp; 15 unit tests pass.</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
@@ -1317,10 +1333,26 @@
       <c r="K36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Set Clock = time_delta, not hardware (two-clock architecture confirmed in source)</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>lb_rtc.c lbRTC_GetGameTime: game_ticks = OSGetTime() + Save_Get(time_delta). lbRTC_SetTime: time_delta = desired_ticks - hard_ticks. The in-game Set Clock only adjusts the saved delta; the GameCube RTC is never modified. Rust: GameClock { time_delta } with game_time() and set_game_time().</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Confirms Philip's research sections 4-6 exactly. The Rust port preserves this separation; PC port's --time/--date overrides remain the C-side mechanism.</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>High - read directly from lb_rtc.c:148-165,243-260.</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
@@ -1330,10 +1362,26 @@
       <c r="K37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Seasons = 18-term table; 6 AM renewal; 2030 limit; astronomical events</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>m_time.c mTM_calender: 18 (month,day) terms mapping to Spring/Summer/Autumn/Winter + bgitem profiles (island climate forces term 7). mTM_FIELD_RENEW_HOUR=6 is the daily reset; renewal compares save ymd vs current ymd. mTM_MIN_YEAR=2001, mTM_MAX_YEAR=2030 (GC; 2100 PC). lb_reki.c: equinox float formulas, Harvest Moon precomputed table 2002-2030 (PC port corrected 17 dates; Rust keeps the GC table). EventWindow/DatePredicate mirror m_event.c scheduling (fixed, nth-weekday, weekly, astronomical).</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Season/event logic now has a Rust foundation. The 6 AM game-day helper (game_day_ymd) separates calendar date from game day as Philip's research requires.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>High - tables and formulas copied from the decomp sources.</t>
+        </is>
+      </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1391,10 +1391,26 @@
       <c r="K38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Town generator = rejection sampling (source-verified loop)</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>mRF_MakeRandomField_ovl (m_random_field_ovl.c:1848): builds a COMPLETE candidate town, accumulates placement bits, and repeats the whole attempt while (perfect_bit != (perfect_bit &amp; bit)). perfect_bit = all 9 mRF_BIT_* bits: SLOPE_LEFT, SLOPE_RIGHT, BRIDGE_UPPER, BRIDGE_LOWER, SHRINE, POLICE, MUSEUM, POOL, NEEDLEWORK. No per-acre backtracking: an invalid candidate is discarded and generation restarts from the RNG stream. This is the mechanism behind the occasional long black-screen delay during town creation (each rejection is invisible to the player). Phase order: clear save acres -&gt; base landform (cliffs+river) -&gt; flat-place info -&gt; beach base -&gt; bridges/slopes -&gt; tailor/dock -&gt; wishing well/police/museum -&gt; shop/post office (no perfection bit; internal retry) -&gt; lake -&gt; sea-block bridge fixup -&gt; height table -&gt; acre selection -&gt; copy heights. Corroborates Hunter R. Feb 2026 video notes (lookup-table correction, gates resolved later, Numerical Recipes RNG reference).</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Rust generate() restructured to match: generate_candidate builds one town + 9 PERFECT_* bits; generate retries on one deterministic RNG stream (cap 4096 attempts). is_valid_town() is the explicit predicate.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>High - read directly from the decompiled source.</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
@@ -1404,10 +1420,26 @@
       <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Lookup-table architecture ported: 108 block kinds, 108x4 gate table, 7 river types</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>mRF_block_info[] (m_random_field.c:13): all 108 mFM_BLOCK_TYPE_* values mapped to mRF_BLOCKKIND_* bitmasks (bit positions from m_random_field_h.h: PLAYER=1&lt;&lt;0, SHOP=1&lt;&lt;1, SHRINE=1&lt;&lt;2, POLICE=1&lt;&lt;3, POSTOFFICE=1&lt;&lt;4, STATION=1&lt;&lt;5, CLIFF=1&lt;&lt;6, RIVER=1&lt;&lt;7, WATERFALL=1&lt;&lt;8, BRIDGE=1&lt;&lt;9, RAILROAD=1&lt;&lt;10, MARINE=1&lt;&lt;11, BORDER=1&lt;&lt;12, TUNNEL=1&lt;&lt;13, SLOPE=1&lt;&lt;14, POOL=1&lt;&lt;15, DUMP=1&lt;&lt;16, MUSEUM=1&lt;&lt;17, _18=1&lt;&lt;18, TAILORS=1&lt;&lt;19, OCEAN=1&lt;&lt;20, ISLAND=1&lt;&lt;21, OFFING=1&lt;&lt;22, RIVER0..RIVER6=1&lt;&lt;23..29, DOCK=1&lt;&lt;30, ISLAND_LEFT=1&lt;&lt;31). Block properties live in the table, not in per-acre attached metadata. mRF_gate_info2[108][4] (block type x NORTH/WEST/SOUTH/EAST) -&gt; GATE_NONE/GATE1_TYPE0/1/GATE2_TYPE0/1/GATE3_TYPE0; gate counts {0,1,1,2,2,3} (mRF_GateType2GateCount). Gates resolved later via mRF_BlockTypeDirect2GateType, never attached up front. l_river_next_direct[]: 7 river types -&gt; SOUTH,EAST,WEST,EAST,SOUTH,WEST,SOUTH (mRF_RiverIdx2NextDirect, OOB-&gt;SOUTH). Rail detail: mRF_SetUniqueRailBlock replaces TRACKS_DUMP at x=1+RANDOM(2) / x=4+RANDOM(2) on row A, matching the Rust left {0,1} / right {3,4} pairs.</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>All four tables ported verbatim into town_gen.rs (BLOCK_KIND_TABLE, GATE_TABLE, GATE_COUNT_TABLE, RIVER_NEXT_DIRECTION) with accessors block_kind/gate_type_for/gate_count_for/river_next_direction. Spot-checked against the decomp (block 11, 39, 100; gate row 11).</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>High - tables extracted mechanically from the decomp and verified entry-by-entry on samples.</t>
+        </is>
+      </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
@@ -1417,10 +1449,26 @@
       <c r="K40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Rust town-gen changes, validation, and remaining gaps (Oct 2026)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Changes: (1) four source tables ported; (2) generate() now rejection-samples with PERFECT_* bits and is_valid_town(); northernmost bridge = BRIDGE_UPPER; tailor placed before river trace so the river routes around it; place_lower_facilities returns earned bits; fail-fast when roster cannot cover villager count; (3) module docs record verified-vs-rewrite-owned split. Validation: cargo check --lib clean (only pre-existing dvd.rs unused_unsafe warning); both ported tables spot-verified against the decomp. Unit tests NOT run (standing no-tests rule). Gaps: cliff/river tracing still uses the rewrite boundary-signature model, not the source block-chain lookups or the 10 authored step-3 templates; no authored acre byte tables reproduced; new lookup APIs are Rust-only (no C callers rewired); full Windows game link still unverified.</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md updated (new source findings + Oct 2026 upgrade paragraph). Workbook rows 39-41. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>High for the ported tables and loop structure; rewrite-owned simplifications explicitly labeled.</t>
+        </is>
+      </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1478,10 +1478,26 @@
       <c r="K41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Save/storage: file layout and sub-entry table (source-verified)</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>m_card.h / m_card.c: town file DobutsunomoriP_MURA (l_mCD_land_file_name), mCD_LAND_SAVE_SIZE=0x72000 = 57 blocks; GCI = 467,008 bytes (57*8192+64). Siblings: DobutsunomoriP_MURA_d (dummy/backup), DobutsunomoriP_PL_&lt;n&gt; (travel), DobutsunomoriP_Omake_ (bonus/gift letters). l_mcd_file_table (mCD_FILE_* order): MISC/MAIN/MAIN_BAK (each sizeof(Save)), MAIL (0xC000), ORIGINAL (0xE000), DIARY (0xC000) live inside the MURA file; PRESENT (0x2000) and PLAYER/travel (0x6000) are separate files. SAVE_DATA_OFS=0x1440 (comment 64 + banner 0xE00 + icon 0x600). sizeof(Save_t)=148,128 (0x242A0), sector-aligned via the Save union.</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/save.rs ports: physical constants, file names/sizes, 8-entry SAVE_FILE_TABLE, block/GCI math helpers. DOCUMENTATION.md has a new Save &amp; Storage section.</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>High - read directly from the decomp headers and card code.</t>
+        </is>
+      </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
@@ -1491,10 +1507,26 @@
       <c r="K42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Save/storage: record counts, keep_* regions, checksum, endianness</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>PLAYER_NUM=4, FOREIGNER_NUM=1 (m_personal_id.h); pockets mPr_POCKETS_SLOT_COUNT=15; mailbox mPr_INVENTORY_MAIL_COUNT=10; personal patterns mPr_ORIGINAL_DESIGN_COUNT=8 (m_private.h). keep_mail = 8 pages x 20 = 160 town-wide saved letters; keep_original = 8 x 12 = 96 saved patterns; keep_diary = 4 players x 12 months; each keep_* has u16 checksum + landid. PresentSave_c: 9 bonus letters. Checksum: mFRm_ReturnCheckSum adds native u16 words (odd length -&gt; 0); mFRm_GetFlatCheckSum stores the two's complement fixup so the region sums to zero; loads require sum==0 plus land-ID checks. GameCube format is big-endian; pc_save_bswap.c swaps Save_t on load/save (incl. u8 bitfield repacking). Travel file: mCD_foreigner_c (checksum + Private_c + removed villager + copy_protect). keep_* regions are land-ID-keyed, which is why saved letters/patterns survive an in-game town rebuild.</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Rust: checksum_sum/checksum_fixup/checksum_valid over big-endian words (explicit on-card byte order), 33-region SAVE_T_REGIONS map with decomp offsets, ResetPreserved rebuild model, C ABI pc_save_checksum* trio. cargo check --lib clean (1 pre-existing warning).</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>High for decomp-traced items; furniture 3-slots-per-unit, NES 1-block, travel 3-block sizes are contemporary-guide claims, labeled as such.</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -1504,10 +1536,26 @@
       <c r="K43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Save/storage: implementation gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: full 148KB Save_t field map (only 33 headline regions), Private_c/Animal_c sub-layouts, the card I/O state machine (mCD_SaveHome_bg etc.), ARAM staging of keep_* regions, e+ file layout (out of scope). No C callers rewired to the new Rust save APIs; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Natural next steps: (a) letter-scoring ABI audit (flagged arg-order issue), (b) wiring Rust modules (game_time, town_gen lookups, save checksums) to C callers via adapters, (c) next infographic system (conversation/NPC or buried items).</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 42-44. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1565,10 +1565,26 @@
       <c r="K44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Conversation &amp; NPC: six personalities and per-personality schedules (source-verified)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>m_npc_personal_id.h: mNpc_LOOKS_GIRL (normal), KO_GIRL (peppy), BOY (lazy), SPORT_MAN (jock), GRIM_MAN (cranky), NANIWA_LADY (snooty) -- the six GameCube personalities in decomp order. (Japanese bo/fu/ge/ha/ko/ta labels not present in these identifiers.) m_npc_schedule.c: mNPS_schedule[mNpc_LOOKS_NUM], one table per personality, ported verbatim: normal sleeps 21:00-05:00, peppy 23:30-07:00, lazy 22:00-08:00, jock 01:00-05:30, cranky 05:00-10:00, snooty 02:30-09:00. Schedule states (m_npc_schedule_h.h): FIELD (same acre as home), IN_HOUSE, SLEEP, STAND, WANDER, WALK_WANDER, SPECIAL. Corrects the brief's fan-guide sleep table where it differs (e.g. snooty 02:30-09:00 vs claimed 03:00-09:00).</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/npc.rs: Personality enum, SCHEDULE_TABLES verbatim, schedule_state_at/is_asleep, C ABI pc_npc_schedule_state/pc_npc_is_asleep. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>High - tables copied directly from the decomp.</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
@@ -1578,10 +1594,26 @@
       <c r="K45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Conversation &amp; NPC: message engine, moods, catchphrases</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>m_msg_main.c_inc: mMsg_ChangeMsgData loads one of MSG_MAX (0x3F91) messages into the window object, resets end_text_cursor_idx/cursor, sets 20.0s timer via mMsg_SetTimer; backed by mMsg_LoadMsgData. Selection (NPC AI) and rendering (m_msg) are separate layers -- matches the brief's architecture. m_npc.h: mNpc_MOOD_0..8 (9 moods); Animal_c.mood/mood_time ('feel'/'feel_tim'); index-to-meaning mapping NOT established from the decomp. ANIMAL_CATCHPHRASE_LEN=10, mutable per-villager state. Friendship clamp 0..=127 via mNpc_AddFriendship (established in letter work).</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Rust: opaque 9-value Mood, 10-char Catchphrase, MsgWindow state machine (load mirrors cursor-reset + 20s timer), MsgOp script ops (text/pause/wait-input/subst/end), MsgVar substitutions, dialogue-category selection, conversation tree with answer resolution, NpcActor runtime state with 0..=127 friendship clamp. cargo check --lib clean (1 pre-existing warning).</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>High for engine/mood/catchphrase/friendship facts; dialogue categories and answer effects are rewrite-owned models, labeled as such.</t>
+        </is>
+      </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
@@ -1591,10 +1623,26 @@
       <c r="K46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Conversation &amp; NPC: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: actual AI state IDs and movement/wander selection, player-detection/conversation-trigger logic, favor/quest generation, move-out logic, villager-to-villager interaction, special-NPC event schedules, any authored message text/IDs (deliberately not reproduced). Mood refusal semantics follow guide-observed behavior, not decomp predicates. No C callers rewired to the new NPC APIs; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Remaining infographic systems: villager behavior/hidden mechanics, buried items, home upgrade, item shop, menu &amp; init, villager interest &amp; interaction.</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 45-47. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1652,10 +1652,26 @@
       <c r="K47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Authorized full Rust test suite run (2026-10-07): 54/54 pass</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Philip authorized running the tests ('Run your tests'). cargo test --lib: 54 passed, 0 failed. Two failures caught and fixed before the green run: (1) save::tests::checksum_roundtrip -- test-only setup bug (checksum field must be zeroed before computing the fixup, mirroring game usage); (2) town_gen three-tier distribution -- REAL fidelity bug: the source rolls mRF_GetRandomStepMode's 15% three-tier choice ONCE outside the retry loop, so generate() now draws three_tiers once and reuses it across rejected candidates instead of re-rolling per attempt (re-rolling skewed three-tier towns down to 173/2048 because constrained three-tier candidates get rejected more often).</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>town_gen.rs: generate_candidate takes three_tiers param; save.rs test zeroes the field first. 6 new npc.rs tests pass (schedule sleep windows, transitions, catchphrase truncation, message-window stepping, friendship clamp, sleep refusal). DOCUMENTATION.md test-status notes updated.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>High - observed test output and decomp source flow.</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1681,10 +1681,26 @@
       <c r="K48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Buried items: buried-bit storage and geometry (source-verified)</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>m_common_data.h:121: u16 deposit[FG_BLOCK_X_NUM * FG_BLOCK_Z_NUM][UT_Z_NUM] at save offset 0x020F1C, decomp comment 'flags for which items are buried around town'. m_field_info.c: mFI_LineDepositON/OFF set/clear bit ut_x of row ut_z; mFI_GetLineDeposit reads it; block wrappers mFI_BlockDepositON/OFF, mFI_GetBlockDeposit, mFI_BkUtNum2DepositON/OFF/GET, mFI_Wpos2DepositON/OFF/GET. Geometry: UT_BASE_NUM=16 (16x16 tiles/acre), FG_BLOCK_X_NUM=5, FG_BLOCK_Z_NUM=6 -&gt; 80x96 town tiles. CORRECTS the third-party 80x80 claim flagged in the brief.</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/buried_items.rs: geometry constants, line/block deposit bit ops, BurialGrid (item grid + parallel deposit array), C ABI pc_buried_get/set/clear. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp source and save offset.</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
@@ -1694,10 +1710,26 @@
       <c r="K49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Buried items: bury/dig/fossil/gyroid/pitfall/shine-spot logic (source-verified)</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>m_museum.c: mMsm_DepositItemBlock_cancel writes *fg_items = deposit_item + *deposit |= (1&lt;&lt;ut_x) (item + buried bit). mMsm_DepositFossil: at most mMsm_DEPOSIT_FOSSIL_MAX=5 buried fossils, one per x-acre-column (record bits 1&lt;&lt;(block_x+1) via mMsm_RecordDepositFossil/GetDepositBlockNum), skipping player/shrine/station/pool/dump acres, ITM_FOSSIL=0x2511. Gyroids: mAGrw_HANIWA_NUM=3 via the same deposit path. PITFALL CORRECTION: mMsm_DepositItemBlock stores BURIED_PITFALL_HOLE_START+hole_num (0x002A-0x0042, 25 holes; RSV 0x0043-0x005B) instead of item+deposit bit; ITEM_IS_BURIED_PITFALL_HOLE(_RSV) predicates. m_name_table.c bg_item_fg_sub_dig2take_conv: pitfall hole -&gt; ITM_PITFALL (0x2512); SHINE_SPOT (0x005C) -&gt; 30k/10k/1k bell bags (0x2102/0x2101/0x2100) by money-power roll (2*mp/40, 12*mp/40 windows) or money-luck destiny; else passthrough. m_player_common.c_inc: pickup path requires mFI_Wpos2DepositGet()==FALSE. ac_event_manager.c be_flat_unit: convert + SetFG EMPTY_NO (0x0000) + Wpos2DepositOFF. m_all_grow_ovl.c mAGrw_SetShineGroundBlock: one random flat diggable tile per player per day.</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Rust: bury_item, bury_pitfall (hole allocation), dig_up (conversion + clear), dig2take_conv (exact bell-roll logic), can_pickup gate, is_pitfall_trap, fossil count/record-bit logic, rewrite-owned can_bury_item heuristic (labeled). cargo check --lib clean (1 pre-existing warning).</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>High for decomp-traced facts; can_bury_item is rewrite-owned, labeled.</t>
+        </is>
+      </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
@@ -1707,10 +1739,26 @@
       <c r="K50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Buried items: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: tile collision/diggability checks (mCoBG_CheckHole_OrgAttr etc. -- C collision system), per-tile candidate selection within an acre during daily generation (needs collision data), the actual shovel-swing actor interaction path, money-tree/golden-shovel growth sequences, treasure-hunt wiring, glowing-spot overlap glitch handling. No C callers rewired to the new burial APIs; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Remaining infographic systems: villager behavior/hidden mechanics, home upgrade, item shop, menu &amp; init, villager interest &amp; interaction.</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 49-51. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1768,10 +1768,26 @@
       <c r="K51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Letter-scoring ABI audit (2026-10-07)</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Checked the three Rust exports against the decomp headers. (1) mMck_check_key_hit: C is 'int mMck_check_key_hit(int* len, u8* str)' (m_mail_check_ovl.h:29, m_mail_check_ovl.c:1102) -- the Rust export had the parameters REVERSED (body first, words_out second); every C caller (m_mail_check.c:6 mMC_get_mail_hit_rate) passes (len, str). FIXED to (len: *mut i32, str_: *const u8). (2) mQst_GetMailRank: C is 'static u8 mQst_GetMailRank(u8* body, mActor_name_t present)' (m_quest.c:648); mActor_name_t is u16 (m_actor_type.h:10) -- Rust used i32, FIXED to u16. (3) DUPLICATE-SYMBOL RISK CONFIRMED: rust/Cargo.toml sets codegen-units=1, so libac_pc_rust.a is a single object defining mMck_check_key_hit/_nes; CMakeLists globs m_mail_check_ovl.c from DECOMP_ROOT with no exclusion and links ac_pc_rust into the ac_pc game binary (needed for PSMTX* etc.), so the game link will hit 'multiple definition' once the Rust object is extracted. m_mail_check_ovl.c defines only those two globals (tables are static), so excluding the file is a clean rewire option; callers m_mail_check.c:6 and m_npc.c:1238 would then bind to the Rust symbols. mQst_GetMailRank is static in C: no duplicate risk, but the Rust export can never intercept m_quest.c:675 -- wiring it needs a C-side patch. CONCLUSION: the Rust letter engine is not live-wired today; the C version wins or the link fails. Full Windows game link still unverified -- needs a check on the MSYS2 machine.</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>letter_score.rs: parameter order fixed, present: u16. DOCUMENTATION.md ABI audit note added. Rewire (exclude m_mail_check_ovl.c vs rename Rust exports) left as a build decision for Philip.</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp headers, CMakeLists, and Cargo.toml all read directly.</t>
+        </is>
+      </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1797,10 +1797,26 @@
       <c r="K52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Letter engine rewire: m_mail_check_ovl.c excluded, Rust scoring goes live (2026-10-07)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Pre-change research: m_mail_check_ovl.c defines only two globals (mMck_check_key_hit at :1102, mMck_check_key_hit_nes at :1429; trigram tables are static). Only callers in the decomp: m_mail_check.c:6 (mMC_get_mail_hit_rate -&gt; mMck_check_key_hit(len, str)) and m_npc.c:1238 (mMck_check_key_hit_nes(body)). The game build defines BUGFIXES globally (CMakeLists add_compile_definitions); BUGFIXES only changes the trigram table terminators to CHAR_CONTROL_CODE/0. The Rust exports use TrigramMode::Intended, which was verified to match the BUGFIXES build -- so behavior is preserved across the swap. Exclusion regex '.*/m_mail_check_ovl\.c$' tested against Windows/Unix-style paths: matches only the target file. Follows the file's existing precedent ('exclude the individual files to avoid duplicate symbol definitions', cf. src/furniture). mQst_GetMailRank stays static in m_quest.c: the Rust export exists but cannot intercept m_quest.c:675 without a C-side patch -- documented as a remaining gap, not done.</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>CMakeLists.txt: added EXCLUDE REGEX for m_mail_check_ovl.c with an explanatory comment. DOCUMENTATION.md audit note updated (finding 3 -&gt; resolved). cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources, CMakeLists, and Cargo.toml read directly. Full Windows game link still needs verification on Philip's MSYS2 machine.</t>
+        </is>
+      </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1826,10 +1826,26 @@
       <c r="K53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>House progression: mortgage values, sizes, expansion rule (source-verified)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>m_player.h: mPlayer_DEBT0 17400 (buy house), DEBT1 148000 (medium), DEBT2 398000 (large), DEBT3 49800 (basement), DEBT4 798000 (upper). ac_npc_shop_common.h: aNSC_LOAN_MEDIUM/LARGE/UPPER/STATUE(0)/BASEMENT (same values). m_private.h:204: u32 loan in Private_c.inventory (offset 0x0090); ac_intro_demo_move.c_inc:183 sets loan = mPlayer_DEBT0 (17400) directly -- confirms 19800-1000-1400 breakdown. m_home_h.h: mHm_HOMESIZE_SMALL/MEDIUM/LARGE/UPPER/STATUE with decomp comments; home_size_info_s packs size:3/next_size:3/statue_rank:2 (0=gold,1=silver,2=bronze,3=jade)/renew/statue_ordered/basement_ordered + upgrade order date. ac_npc_shop_common.c aNSC_set_talk_info_start_wait: on renew, basement orders -&gt; loan 49800, else rehouse_loan[size-1] = {148000,398000,798000,0}; house changes only after debt hits zero; statue_rank = num_statues capped at 3.</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/house.rs: debt constants, HouseSize, HomeSizeInfo, House with pay/order_expansion/order_basement/complete_construction/order_statue/complete_statue, C ABI pc_house_next_loan. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp headers and Nook dialogue source.</t>
+        </is>
+      </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
@@ -1839,10 +1855,26 @@
       <c r="K54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Nook shop: thresholds, sales counter, tier machine, tools, stock (source-verified)</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>m_shop.h: mSP_COMBINI_SUM 25000, mSP_SUPER_SUM 90000, mSP_DSUPER_SUM 240000 (cumulative; guides' 65000/150000 are incremental deltas). Shop_c (0x140): items[mSP_GOODS_COUNT] (39 slots -- confirms save-editor finding), rare_item, lottery_items[3], shop_info bitfields (shop_level:2, upgrading_today, send_upgrade_notice, not_loaded_before, paint_color:4), sales_sum u32 at 0x128 ('current money towards upgrading shop'), exchange_time, renewal_time, visitor_flag ('set when a foreign player enters Nook\'s shop, required for Nookington\'s'). m_shop.c mSP_PlusSales: adds then CLAMPS to tier threshold (brief's excess-discard quirk, now source code). mSP_GetRealShopLevel: tier from counter; Nookington's needs visitor_flag; TARGET_PC has disable_shop_visitor_req toggle. mSP_RenewShopLevel syncs displayed level. mSP_SelectTool: shovel always; net 3000 / rod 8000 / axe 12000 lockout applies ONLY in Nook's Cranny (mSP_NET/ROD/AXE_SALES_SUM). Transaction accounting: selling -&gt; mSP_PlusSales(money/2) (ac_npc_shop_common.c:2220), catalog orders -&gt; mSP_PlusSales(price) (:2358), furniture orders -&gt; full price (ac_shop_design.c:368).</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/shop.rs: ShopTier, thresholds, ShopState with plus_sales (exact clamp), record_purchase/record_sale (half payout)/record_catalog_order, real_level (visitor toggle), renew_level, set_new_visitor, tool_slots (Cranny-only lockout), 39-slot stock, guide-derived category slot table (labeled). C ABI pc_shop_real_level, pc_shop_plus_sales. cargo check --lib clean (1 pre-existing warning).</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>High for decomp-traced facts; category slot table is guide-derived, labeled.</t>
+        </is>
+      </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
@@ -1852,10 +1884,26 @@
       <c r="K55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>House/shop: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: Nook's dialogue state machine, daily stock selection RNG and item-pool tables, catalog flag storage, remodeling scheduler (upgrading_today timing vs sale/event dates), mortgage payment dialogue, statue construction event, ABD/post-office interactions (excluded from the Nook total per the brief). mQst_GetMailRank-style note: no C callers rewired to the new house/shop APIs; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Remaining infographic systems: villager behavior/hidden mechanics, menu &amp; init, villager interest &amp; interaction.</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 54-56. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -1913,10 +1913,26 @@
       <c r="K56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Menu/init: game_dlftbls scene table and GAME struct (source-verified)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>m_game_dlftbls.c: DLFTBL_GAME game_dlftbls[] = first_game(0), select(1), play(2), second_game(3), NULL(4, 'removed &amp; unused'), trademark(5), player_select(6), save_menu(7), famicom_emu(8), prenmi(9), pc_model_viewer(10, TARGET_PC only). Each entry: init fn pointer, cleanup pointer, alloc_size = sizeof(GAME_&lt;class&gt;). m_game_dlftbls.h: 'Display List Function TaBLe'. game.h: GAME struct has exec at 0x4, cleanup at 0x8, next_game_init at 0xC (confirms brief's offset-0xC observation), next_game_class_size at 0x10, frame_counter at 0xA0. CORRECTION: earlier doc note 'player_select (scene 19)' was wrong; decomp table index is 6 (fixed in DOCUMENTATION.md).</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/scene.rs: SceneId with verified indices (index 4 -&gt; None), SCENE_TABLE with init names, Scene trait, SceneRequest, SceneManager, BOOT_CHAIN with PC-vs-original marking. C ABI pc_scene_table_index, pc_game_dlftbls_count. DOCUMENTATION.md section added + scene-19 correction.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
@@ -1926,10 +1942,26 @@
       <c r="K57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Menu/init: transition mechanism and graph_proc lifecycle (source-verified)</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>game.h: GAME_GOTO_NEXT sets doing=FALSE and records next_game_init + next scene state size; GAME_NEXT_GAME_NULL clears them. graph.c game_get_next_game_dlftbl: matches the next-init function pointer against each known init (ARE_INIT_PROCS_EQUAL) to find the table entry. graph_proc: starts at game_dlftbls[0] (or [10] for the PC model viewer); loop: malloc(alloc_size) -&gt; game_ct(init) (doing=TRUE, next cleared) -&gt; per-frame graph_main/game_main/scene-&gt;exec() while doing -&gt; resolve next entry -&gt; game_dt (cleanup) -&gt; free. Verified transitions: first_game -&gt; second_game (first_game.c:16); trademark -&gt; play (m_trademark.c:183); select -&gt; play (m_select.c:25). Confirms the brief: menus, gameplay, NES emu, and debug scenes are peers in one dispatcher, not nested loops.</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Rust: SceneManager.run_frame/advance mirrors the doing-flag + table-resolution flow; unit tests cover transitions and shutdown. cargo check --lib clean (1 pre-existing warning).</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
@@ -1939,10 +1971,26 @@
       <c r="K58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Menu/init: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: per-scene init/exec/cleanup bodies (first_game/second_game/trademark/select/player_select/save_menu/famicom_emu/prenmi), the title-screen input state machine, memory-card validation branches at boot, save_menu_init's exact responsibilities, prenmi_init's purpose, Game_play_fbdemo_wipe_proc transition effects, scene state struct layouts (per-build C sizes). The Scene trait is ready for scene implementations to be added. No C callers rewired to the new scene APIs; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Remaining infographic systems: villager behavior/hidden mechanics, villager interest &amp; interaction.</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 57-59. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2000,10 +2000,26 @@
       <c r="K59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Villager behavior: priority action arbiter (source-verified)</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ac_npc.h: aNPC_ACT_* vocabulary (wait/walk/run/turn/chase insect/chase fish/greeting/talk/into-leave house/umbrella/play music/react tool/clap/get/change cloth/pitfall/revive/special), action kinds DEFAULT/AVOID/SEARCH/TO_POINT, targets player/any NPC/target NPC/ball/insect/fish. ac_npc2_action.c_inc:352: aNPC_set_request_act accepts only prio &gt;= pending priority; action proc dispatches via aNPC_act_proc table. Request struct: act_priority/act_idx/act_type/act_args[6] + head-tracking (head_priority/head_target/head_pos). Confirms the brief: priority-based selection, not utility AI.</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/behavior.rs: BehaviorAction (23, decomp order), ActionKind, ActionTarget, ActionRequest with priority-wins rule, head tracking, BEHAVIOR_ACTION_NONE=0xFF. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
@@ -2013,10 +2029,26 @@
       <c r="K60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Villager behavior: move-out/move-in, letters, moods (source-verified)</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>m_npc.c mNpc_SetRemoveAnimalNo: move-out prefers a villager ALL players have met, then one SOME player has met, then uniform random fallback (mNpc_DecideRemoveAnimalNo_Friend / _DecideRemoveAnimalNo). CONTRADICTS the 'ignore them and they leave' myth -- met villagers are preferred for removal. Move-in validation (m_npc.c:3580+): reject if already in town, was last removed, or is the summer camper; the villager record (identity/personality/catchphrase/memories) transfers, explaining cross-town memory. m_quest.h: LETTER_SCORE_BONUS=3, LETTER_PRESENT_BONUS=6. Mood is an opaque index in the decomp (npc.rs Mood); Normal/Happy/Angry/Sad names are from player docs. Friendship is 0..=127, NOT New Horizons 0-255.</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Rust: select_move_out (met-preference order), transfer_allowed, TransferRecord, apply_letter with 0..=127 clamp, VisibleMood with talk gating, FavorState machine, WorldEvent-&gt;reaction_for (fish/bug-&gt;clap, pitfall-&gt;trapped), BehaviorStage pipeline, VillagerBehavior. C ABI pc_letter_friendship_delta. cargo check --lib clean; tests NOT run.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
@@ -2026,10 +2058,26 @@
       <c r="K61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Villager behavior: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: the think procs (wander/hide/special selection), per-action init/main procs, route search/pathfinding (aNPC_route_search_table_c), schedule-&gt;destination logic, NPC attention/talk handshake, favor/quest generation tables, catchphrase propagation triggers, pitfall trap/release flow, villager save struct fields. The brief's 'first-day tutorial mode' claim not yet traced in source. No C callers rewired; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). Remaining infographic systems: villager interest &amp; interaction (villager reply system already ported).</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 60-62. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2087,10 +2087,26 @@
       <c r="K62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Villager interest: feel enum and talk-frequency mechanic (source-verified)</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>m_npc.h: mNpc_FEEL_* = Normal, Happy, Angry, Sad, Sleepy, Pitfall + UZAI_0/1 (9 total = mNpc_FEEL_ALL_NUM). CORRECTS the earlier npc.rs note claiming the decomp does not name moods. m_npc.c: per-villager mNpc_Talk_Info_c (timer, talk_num, quest_request, unlock_timer, reset_timer); l_npc_temper per-feel (unlock_timer, over_impatient_num, talk_num_max): Normal (4000,12,15), Happy (3000,10,13), Angry (4000,12,15), Sad (4000,10,13), Sleepy (5000,9,12), Pitfall (5000,9,12). mNpc_GetOverImpatient: MILDLY_ANNOYED past impatient threshold, ANNOYED (refuse talk) past max. Happy villagers lose patience faster. This is the brief's 'repeated talking annoys them' mechanic with exact numbers.</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/interaction.rs: Feel, TEMPER_TABLE verbatim, TalkInfo (count_talk/patience/over_impatient), Patience. npc.rs mood comment corrected to reference the feel enum. C ABI pc_npc_patience. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
@@ -2100,10 +2116,26 @@
       <c r="K63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Villager interest: quest system and interaction model (source-verified)</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>m_quest.h: mQst_QUEST_TYPE_* = Delivery/Errand/Contest. Delivery kinds: normal/foreign/removed/lost; delivery quest carries sender + recipient personal IDs (the chained-favor machinery). Errand types: chain/first-job; first-job quests: deliver furniture, send letter, deliver carpet/axe, post notice, introductions. Contest kinds: fruit/ball/snowman/flower/fish/insect/letter. No formal hobby field exists (Wild World invention) -- the brief's warning holds. Inventory inspection ('impulse buying') is player-documented but not traced to a source function; individual item-preference structures also untraced -- both marked as such in code.</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Rust: QuestType/DeliveryKind/ContestKind/ErrandType, five InterestLayers (personality/individual/current desire/opportunistic/environmental -- no hobby field), InteractionKind, InteractionContext with selection hierarchy (annoyed-&gt;refused, pending request-&gt;request, held item-&gt;item trade, else conversation). cargo check --lib clean; tests NOT run.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly; untraced items labeled.</t>
+        </is>
+      </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
@@ -2113,10 +2145,26 @@
       <c r="K64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Villager interest: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Not yet traced: exact individual item-preference structure and lookup, the inventory-scan ('impulse buying') function, personality-&gt;topic dialogue tables, daily conversation selection algorithm, request-generation probabilities, relationship values per interaction type, furniture-receipt handling, design-wearing mechanism, NPC-to-NPC interest state. The interest model is currently the brief's five-layer contextual selector; source tracing should replace inferred parts. No C callers rewired; full Windows game link unverified. Unit tests written but NOT run (standing no-tests rule). All 14 infographics now have at least one implementation pass.</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 63-65. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2174,10 +2174,26 @@
       <c r="K65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Authorized test run: 85/85 pass, 4 test bugs fixed (2026-10-07)</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Philip authorized 'Run your tests'. cargo test --lib: 85 passed, 0 failed. Initial run: 82 pass, 3 fail + 1 compile error -- ALL were test bugs, not code bugs: (1) behavior.rs test used Personality::Lazy/Normal, but the decomp enum uses Boy/Girl (fixed to Boy/Girl); (2) house statue test forgot order_statue requires loan==0 (source behavior, correctly modeled -- test now pays the loan first); (3-4) two shop tests forgot mSP_PlusSales clamps to the DISPLAYED tier's threshold, so sales can't cross a tier without renew_level() in between (source behavior, correctly modeled -- tests now renew between tiers). The failures confirmed the source-verified clamp/loan-gate behavior rather than contradicting it.</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Fixed tests in behavior.rs, house.rs, shop.rs. Committed and pushed. DOCUMENTATION.md updated.</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>High - test output observed directly.</t>
+        </is>
+      </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2203,10 +2203,26 @@
       <c r="K66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Per-scene init/exec bodies: exec installation and game_main wrapper (source-verified)</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>m_play.c:466-467: play_init sets game-&gt;exec=play_main, game-&gt;cleanup=play_cleanup. Other scenes install their own exec in init: second_game_main, trademark_main, select_main, player_select_main (player_select.c:228), save_menu_main, famicom_emu_main, prenmi_main. EXCEPTION: first_game_init never installs an exec -- it does ROM/save setup then GAME_GOTO_NEXT(second_game) during init, so its frame loop never runs. game.c:138 game_main: frame bookkeeping -&gt; game_draw_first -&gt; mTM_time -&gt; exec (between GAME_EXEC markers) -&gt; mBGM_main -&gt; game_move_first -&gt; frame_counter++. m_play.c:858 play_main: controller/debug -&gt; Game_play_move -&gt; Game_play_draw -&gt; overlay/debug.</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Rust: extended scene.rs with SCENE_EXEC_TABLE (verified exec/cleanup names, first_game has no exec), GAME_MAIN_PHASES (6 wrapper phases), PlayExecPhase (Move/Draw), Scene trait docs record the init-installs-exec contract + first_game exception. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
@@ -2216,10 +2232,26 @@
       <c r="K67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Per-scene init/exec bodies: Pre-NMI, wipes, level-2 scene data (source-verified)</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>graph.c:363: graph_main reset check does GAME_GOTO_NEXT(game, prenmi, PRENMI) when ResetStatus==IRQ_RESET_PRENMI and disable_prenmi==FALSE -- system resets reuse the scene mechanism. Game_play_fbdemo_wipe_* : wipes/fades are a visual system destroyed separately from the scene; they hide transitions but do not control scene lifetime. m_scene.h mSc_SCENE_DATA_TYPE_*: player/ctrl actor/actor/object-exchange/door/field/my room/arrange room/arrange furniture/sound -- processed by Scene_ct() inside play_init() via Gameplay_Scene_Read(); this is a world/room initializer, NOT the top-level game_dlftbls system. DLFTBL entry 4 confirmed DLFTBL_NULL ('removed &amp; unused').</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Rust: VisualTransition (wipe/fade separate from scene transition), SceneDataKind (10 level-2 types), SceneManager::goto_play/goto_famicom_emu/goto_prenmi helpers, SCENE_TABLE_NULL_INDEX=4. cargo test --lib: 94/94 pass.</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
@@ -2229,10 +2261,26 @@
       <c r="K68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Per-scene work: build fix and remaining gaps</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>BUILD FIX: an earlier edit had replaced 'mod scene;' with 'mod behavior;' in lib.rs, silently dropping scene.rs from the build -- its 9 tests never ran and its C ABI exports (pc_scene_table_index, pc_game_dlftbls_count) never existed. cargo check passed because the module was simply absent. Restored; full suite now 94/94. Remaining gaps: per-scene state struct layouts/sizes, select-&gt;player_select-&gt;play branching conditions, save-menu transition paths, title-demo state machine, segment load/unload lifetimes, unk_14/unk_20/unk_24/unk_28 fields, DLFTBL.cleanup vs game.cleanup relationship. No C callers rewired; full Windows game link unverified.</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 67-69. lib.rs fix committed and pushed.</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed; build fix verified by test run.</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2290,10 +2290,26 @@
       <c r="K69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Villager movement: reactive steering, not pathfinding (source-verified)</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>ac_npc_think_wander.c_inc:20: wander destination = center + (sin(angle),cos(angle))*radius with RANDOM(360) angle -- continuous world-space point, filtered by foreground (empty/item/furniture), mCoBG_Wpos2CheckNpc, and range check. ac_npc.h npc_movement_s: dst_pos (goal) vs avoid_pos (steering target), range center/radius/type, mv_angl, speed max/accel/decel. Range types: block/circle/square (square is later-revision only, #if VERSION&gt;=VER_GAFU01_00). No evidenced A*/BFS/navmesh/waypoint graph for normal villagers. Confirms the brief's 'goal-directed reactive steering' model.</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/movement.rs: MoveRangeType, Movement struct (dst/avoid split, set_dst/set_avoid/restore_dst, accel-based step, circular wander_destination, probe_avoid, circle containment), DECIDE_BORDERS verbatim. C ABI pc_wander_choice, pc_friendship_mode. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
@@ -2303,10 +2319,26 @@
       <c r="K70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Villager movement: avoidance probes, decide tables, friendship/clap (source-verified)</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>ac_npc_think.c_inc:283 aNPC_avoid_wall: add_angl table is literally {+-22.5, +-45, +-90} degrees, probed 2 unit-widths ahead, recursion n-&gt;n+1 on failure, 180-degree fallback; turn_angl_table = {+-112.5} for badly-stuck random turn. Decide tables verbatim with source probability comments: normal 40/30/30, peppy 70/20/10, lazy 60/20/20, jock 30/20/50, cranky 40/30/30, snooty 50/40/10 (RANDOM(10) roll vs borders); fatigued/sleepy always wait. ac_npc_move.c_inc:507 aNPC_chk_avoid_and_search: same block + friendship&lt;0 -&gt; AVOID, &gt;128 -&gt; SEARCH. aNPC_check_clap: normal feel + player catching fish/bug + &lt;3 units + &lt;67.5 deg facing. Go-home: house+(20,60) as WALK. Walk dispatch: move/avoid-move/search-move/to-point-move.</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Rust: AVOID_PROBE_ANGLES, TURN_BACKWARD_ANGLES, GO_HOME_OFFSET, CLAP_* limits, FRIENDSHIP_* thresholds, friendship_mode, check_clap, decide_wander, WalkProc, FriendshipMode, WanderChoice. cargo test --lib: 101/101 pass (7 new movement tests).</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
@@ -2316,10 +2348,26 @@
       <c r="K71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Villager movement: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: aNPC_BGcheck collision modes, aNPC_around_obj_check actor awareness, the NPC2 safe-unit grid (confirmed in ac_npc2_think.c_inc hate_player path but not established for normal villagers), house enter/leave scripted positions, search-move target resolution (aNPC_set_act_obj), the fatigue calculation, exact world&lt;-&gt;block/unit conversion constants. Module wiring verified in lib.rs this time (mod movement + mod scene both present). No C callers rewired; full Windows game link unverified.</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 70-72. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2377,10 +2377,26 @@
       <c r="K72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Player movement: controller layer and turn smoothing (source-verified)</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>m_player_controller.c_inc:156: getters for move_pR, move_angle/last_move_angle, adjusted_pR/last_adjusted_pR from gamePT-&gt;mcon (title demo uses its own copy) -- movement code never sees raw stick values. m_player_main_walk.c_inc:131 Player_actor_Movement_Walk: mod = 0.5 if movePR&gt;=1.0, 0.01 if &lt;=0.05, else 0.01+0.5157895*(movePR-0.05); add_calc_short_angle2(&amp;target, angle, CALC_EASE(mod), 2500, 50); CALC_EASE(x)=1-sqrt(1-x) (ac_museum_insect_priv.h:19). Stronger stick turns the player faster. Confirms the brief's analog-smoothing model.</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/player_move.rs: ControllerMove, turn_mod/calc_ease/smooth_turn_toward (shortest-arc), PlayerMovement::step_core. C ABI pc_turn_mod, pc_locomotion_core. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="3" t="n"/>
@@ -2390,10 +2406,26 @@
       <c r="K73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n"/>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Player movement: state reuse, dash, animation, braking (source-verified)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>m_player_main_run.c_inc:57: Player_actor_Movement_Run is literally Player_actor_Movement_Walk. m_player_main_dash.c_inc:99: Dash is literally Run. DASH-&gt;RUN-&gt;WALK share one steering core; states differ in speed/animation/effects. Dash speed: (7.5*movePR)/over_norm when dash button held (mPlib_CheckButtonOnly_forDush, B/L/R). Animation: sp=0.6*sqrt((speed*over_norm)/7.5); one wall hit -&gt; sp*=sqrt(|sin(wall-facing)|), min 0.22. Braking: Player_actor_Movement_Base_Braking amount 0.32625001. Dash terrain check: 12 sample offsets verbatim (0/+-20 lateral at 0, 28.284271, 56.568542, 84.85281 forward), mCoBG_GetBgNorm_FromWpos each.</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Rust: LocomotionState + movement_core hierarchy, anim_speed/anim_speed_near_wall, BRAKE_AMOUNT, DASH_SAMPLE_OFFSETS verbatim, brake(). cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="n"/>
@@ -2403,10 +2435,26 @@
       <c r="K74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n"/>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Player movement: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Not yet traced: pad_correct_stick deadzone/curve, exact stick-&gt;mcon conversion, Player_actor_Culc_over_speed_normalize_NoneZero, common actor position/velocity update, wall-slide projection formula, per-state max speeds, demo/event movement bypasses, request-priority vs locomotion transitions. No C callers rewired; full Windows game link unverified. Module wiring verified (mod player_move present exactly once).</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 73-75. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -2464,10 +2464,26 @@
       <c r="K75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Collision: unit record and background system (source-verified)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>m_collision_bg.h:161: mCoBG_CollisionData_c is 4 bytes -- slate:1, center:5, top_left:5, bot_left:5, bot_right:5, top_right:5, attribute:6. Five height samples + terrain attribute per unit; engine reconstructs local triangles/wall segments at runtime (no global mesh). Query bounds: UNIT_VEC_INFO_MAX=128 wall vectors, WALL_COL_NUM=2 contacts, MOVE_REGIST_MAX=64 moving-BG registrations. Wall kinds (m_collision_bg.c:753): normal/attribute/move. Slate walls: diagonal normals at 45/135 deg from diagonal height comparison. Swept test (prev-&gt;current segment) produces rev_pos correction along wall normal.</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/collision.rs: CollisionData with exact bit pack/unpack + flat detection, UnitArea, WallKind, SlateDir, WallSeg (signed distance, normal correction), neighborhood rule, plane-equation ground height, ground Y correction. C ABI pc_collision_neighborhood, pc_collision_pack. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
@@ -2477,10 +2493,26 @@
       <c r="K76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n"/>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Collision: result flags and object system (source-verified)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>m_collision_bg.h: hit flags HIT_WALL + FRONT/RIGHT/LEFT/BACK; result fields on_ground, hit_wall_count, is_in_water, is_on_move_bg_obj, rev_pos. Actors on moving BG are carried by its position delta. m_collision_obj.h: collider types joint sphere/pipe/triangle; Cl_COLLIDER_NUM=50; groups PLAYER(0x08)/GROUP_2(0x10)/GROUP_3(0x20); masses immovable/heavy/normal; overlap -&gt; collision_vec separation split by mass (immovable takes none, heavy/heavy 50/50). Background collision answers 'what did I hit + correction'; object collision answers 'who overlaps me + separation'.</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Rust: hit flags module, BgResult, ColliderType, groups, Mass + mass_split, sphere_overlap depth. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
@@ -2490,10 +2522,26 @@
       <c r="K77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Collision: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Not yet ported: the full BgCheckControll sequence, column collision, line-check subsystem, virtual BG check, water/bridge special cases, hole detection, room/block boundary checks, the per-attribute blocking semantics, triangle collider math, OCC triangle-vs-sphere/pipe paths, collision priority flag. Module wiring verified (mod collision present exactly once). No C callers rewired; full Windows game link unverified.</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Workbook rows 76-78. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2551,10 +2551,26 @@
       <c r="K78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n"/>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Inventory scan: possession primitives (source-verified)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>m_private.c:314: mPr_GetPossessionItemIdx = linear scan over priv-&gt;inventory.pockets (mPr_POCKETS_SLOT_COUNT=15), first match wins, -1 if absent. Deterministic, no RNG. m_private.c:335: WithCond variant also requires the 2-bit condition (mPr_GET_ITEM_COND = (conds&gt;&gt;(slot&lt;&lt;1))&amp;3). mPr_GetPossessionItemSum counts matches ('how many' vs 'where'). m_private.c:651: free-slot search IS the same primitive called with EMPTY_NO. A family of category/type/range variants forms a small inventory-query API used by quests and NPC systems alike.</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Rust rust/src/inventory.rs: Inventory (15 pockets + packed conds), find_item/find_item_with_cond/count_item/count_item_with_cond/find_free_slot/put, exact shift math for item_cond/set_item_cond. C ABI pc_inventory_find, pc_inventory_count. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="3" t="n"/>
@@ -2564,10 +2580,26 @@
       <c r="K79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n"/>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Inventory scan: impulse-buying model and furniture filter (source-verified)</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>'Impulse buying' is community terminology (Cromis 2003), not a decomp function name. Confirmed two-stage model: NPC logic picks a candidate item (mechanism UNTRACED -- random pocket vs random item vs favorite-first not proven), then the possession primitive checks pockets. m_npc.c:3066 mNpc_CheckSelectFurniture excludes clothing/umbrellas/insects/fish/gyroids/identified fossils/NES games; mNpc_DecideNpcFurniture counts eligible house furniture and picks randomly -&gt; reward_furniture. NPC house-furniture selection and player-inventory scanning are separate subsystems.</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Rust: ExcludedFurniture + selectable_furniture, CandidateStrategy (FavoriteFirst/RandomCarried -- marked rewrite-owned/untraced), resolve_candidate. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly; untraced parts labeled.</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="3" t="n"/>
@@ -2575,6 +2607,28 @@
       <c r="I80" s="3" t="n"/>
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Inventory scan: gaps and next steps</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Not yet traced: the exact NPC candidate-selection algorithm (which caller uses the possession query for villager requests), the probability/branching of favorite-item vs inventory-derived requests, quest&lt;-&gt;pocket index bookkeeping (mQst_CheckGrabItem/mQst_CheckPutItem), the FGType/Item1Category/Kind query variants' exact semantics, item_conditions value meanings. Module wiring verified (mod inventory present exactly once). No C callers rewired; full Windows game link unverified.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Workbook rows 79-81. Do not claim live C gameplay wiring.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2627,6 +2627,72 @@
       <c r="D81" t="inlineStr">
         <is>
           <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Item prefs: no static favorite-item list (source-verified)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Animal_c (0x988) carries identity, memories, friendship, house info, clothing, mood, relations, quest state -- NO favorite_items[] field. Modern-style style/color/series favorites are NOT in the GC decomp. npc_def_list supplies cloth/umbrella/catchphrase via mNpc_SetDefAnimalInfo (m_npc.c:2266). Personality from npc_looks_table[npc_id &amp; 0xFFF]; house template indexed by NPC ID directly, not personality. Verified by reading m_npc.c/m_npc.h.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Rust rust/src/item_prefs.rs: NpcDefData, NpcHouseData, select_reward_furniture, GoodsSource + 1/10 rule, AnmBestFtr, IslandFtr. C ABI pc_npc_house_goods, pc_eligible_furniture_count. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Item prefs: house-derived furniture and 1/10 goods branch (source-verified)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>m_npc.c:2825: npc_house_list[npc_id &amp; 0xFFF] gives type/palette/wall_id/floor_id/main_layer_id/secondary_layer_id. mNpc_DecideNpcFurniture scans 10x10 of the main layer, filters eligible furniture, counts, picks RANDOM(num) -&gt; reward_furniture (mNpc_GetNpcFurniture). m_quest.c:931-938: RANDOM(10) gives a 1/10 chance to use villager house furniture for furniture goods instead of mSP_SelectRandomItem_New (source comment verbatim). 'Favorite furniture' lists likely emergent from house contents (strong inference, not proven).</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Rust: exact chain modeled; variant normalization kept data-driven (caller-supplied normalizer). cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly; emergent-list hypothesis labeled inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Item prefs: Islander explicit preference structures (source-verified)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>m_npc.h:166: Anm_bestFtr_c { u32 check; u16 have_bitfield; } inside memuni_u (per-player memory). m_npc.c:5204: mNpc_Island_Ftr_c { u16 set_ftr_bitfield; trade_list[4]; item_list[16]; } -- 16 furniture slots, 4 saved trades. mNpc_SetIslandRoomFtr ORs every memory's have_bitfield into set_ftr_bitfield. mNpc_GetIslandFtrIdx normalizes variants via aMR_CorrespondFurniture / aMR_GetFurnitureUnit. The Islander system is the only explicit 'best furniture' preference structure found.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Rust IslandFtr with merge_memory/slot_obtained/find_slot. Gaps: request-selection caller untraced; hidden static preference table in table data not ruled out; no C callers rewired; Windows link unverified. Workbook rows 82-84.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2691,6 +2691,72 @@
         </is>
       </c>
       <c r="D84" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Request selector: junction function found (source-verified)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>src/actor/ac_quest_talk_normal_init.c: aQMgr_decide_msg_check_possession(check_proc, base_msg, item_idx, msg_count, cancel_item) is the confirmed junction: calls a possession-check proc; on hit picks random message variant base_msg + mQst_GetRandom(msg_count) from per-personality tables (l_ki_ftr[looks], l_trade_ftr[looks], 6 personalities) and records the pocket index; returns -1 when the player lacks the item. m_npc.c does NOT call the possession scanner (brief's negative finding confirmed). mQst_GetGoods_common is a quest goods/reward generator, not the dialogue request selector.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rust rust/src/request_selector.rs: pick_random_eligible, pick_first_eligible, decide_msg_check_possession, decide_idx_prob_table. C ABI pc_request_pick_carried, pc_request_dispatch. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly; brief's downgrade of mQst_GetGoods_common confirmed correct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Request selector: impulse-buying algorithm resolved (source-verified)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ac_quest_talk_normal_init.c:871: aQMgr_get_possession_ftr_cpt_wl_rnd -- the true impulse-buying selector: counts eligible carried furniture (FTR0/FTR1 fg-types + carpets + walls, NORMAL condition, excluding cancel item) via Sum query variants, then sel_idx = RANDOM(item_cnt) and walks pockets to take the sel_idx-th eligible item. Uniform over ELIGIBLE CARRIED ITEMS -- not over pockets, not first-match. Resolves the brief's open question. aQMgr_get_possession_item_rnd does the same for insects/fish. Deterministic first-match variants feed message-decide paths; _rnd variants feed trade offers (aQMgr_order_decide_trade_N -&gt; aQMgr_order_decide_trade_common).</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Rust: exact count+RANDOM+walk ported. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>High - decomp source read verbatim; answers the brief's candidate-selection question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Request selector: trade offers and probability tables (source-verified)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Trade-offer assembly: villager wants the player's randomly chosen carried furniture (trade_items[0]); category goods via mQst_GetGoods_common (1/10 house-furniture branch); offered item = random category good or pitfall seed in pitfall mode (aQMgr_SEL_ITEM_MODE_PITFALL). Verbatim probability tables: l_trade_prob = {25,25,25,25}; l_normal_3_prob = {49,17,17,17}. Full chain now confirmed: possession check -&gt; dialogue message + pocket idx; uniform-random carried furniture -&gt; villager's wanted item; mQst_GetGoods_common -&gt; offered goods (10% villager house).</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Rust: TradeOffer + build_trade_offer with GoodsSource per slot (reuses item_prefs 1/10 rule); TRADE_PROBS/NORMAL_3_PROBS verbatim. Gaps: exact item-type decode (ITEM_IS_FTR/ITEM1_CAT) stays in C; dialogue text IDs not ported; no C callers rewired; Windows link unverified. Workbook rows 85-87.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>High - decomp sources read directly.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2759,6 +2759,28 @@
       <c r="D87" t="inlineStr">
         <is>
           <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Authorized test run #3 (130/130)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Philip said 'Run tests' 2026-10-07: cargo test --lib = 130 passed, 0 failed. Covers all previously dormant tests: player_move (6), collision (8), inventory (6), item_prefs (4), request_selector (5) -- 29 new tests on top of the prior 101/101. No test bugs found this run; the earlier lib.rs duplicate-module slip was caught and fixed before the run via cargo check.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md test status updated across the five module sections.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>High - observed run output.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2781,6 +2781,72 @@
       <c r="D88" t="inlineStr">
         <is>
           <t>High - observed run output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>House scene layouts: mNpc_NpcList_c and dual actor links (source-verified)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>m_npc.h:268: mNpc_NpcList_c = {name, field_name, house_position, position, appear_flag, conversation_flags, quest_info, house_data, reward_furniture} -- the runtime per-NPC/per-house state object. m_npc.h:252: mNpc_NpcHouseData_c = {type, palette, wall_id, floor_id, main_layer_id, secondary_layer_id}. m_npc.c:2852: mNpc_SetNpcinfo sets BOTH npc-&gt;npc_info.animal (persistent Animal_c) and npc-&gt;npc_info.list (runtime npclist) from one npc_info_idx; -ANIMAL_NUM_MAX = island fallback. Animal_c holds home_info/position but NOT the full house layout.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Rust rust/src/house_scene.rs: NpcListEntry, NpcActorLinks + resolve_npc_links (normal/island branches). DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>House scene layouts: scene dispatch, owner resolution, room wall/floor (source-verified)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>m_npc.c:2925: SCENE_NPC_HOUSE/SCENE_KAMAKURA/SCENE_COTTAGE_NPC dispatch into mNpc_AddNpc_inNpcRoom/...Island. m_npc.c:2876: mNpc_AddNpc_inNpcRoom reads house_owner_name, resolves via mNpc_SearchAnimalinfo, places move actor at unit (4,7); skips reserved/empty/joint-event owners. mNpc_RenewalNpcRoom: for mFI_FIELD_NPCROOM0 with a valid owner, room wall/floor = npclist-&gt;house_data.wall_id/floor_id. Scene selects the house/NPC context; house data selects the layout template; foreground data holds the placed objects.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Rust: HouseSceneKind, resolve_house_owner (with all guards), renewal_npc_room. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>House scene layouts: strided furniture scan and request dispatch (source-verified)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>m_npc.c:3083: data_idx = main_layer_id - fg_base_id clamped at 0; fg_items = fg_data_table[data_idx]-&gt;items[0]; two-pass 10x10 scan with fg_items += UT_X_NUM - 10 stride; num = RANDOM(num); second pass returns the num-th eligible item. m_quest.c:980: (*clip.npc_clip-&gt;force_call_req_proc)(npc_actor, 0x0D8B + looks) -- request-procedure ID from base + looks category; the function behind the pointer remains UNTRACED.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Rust: scan_house_furniture (verbatim two-pass strided scan), request_proc_id (0x0D8B + looks), force_call_req_proc as caller-supplied callback. C ABI pc_request_proc_id, pc_house_wall_floor. Gaps: npc_clip init/structure, force_call_req_proc implementation, no C callers rewired, Windows link unverified. Workbook rows 89-91.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly; untraced parts labeled.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2847,6 +2847,72 @@
       <c r="D91" t="inlineStr">
         <is>
           <t>High - decomp sources read directly; untraced parts labeled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Scene layouts: Scene_Word_u record system (source-verified)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>m_scene.h:96: record tags 0 PLAYER_PTR, 1 CTRL_ACTOR_PTR, 2 ACTOR_PTR, 3 OBJECT_EXCHANGE_BANK_PTR, 4 DOOR_DATA_PTR, 5 FIELD_CT, 6 MY_ROOM_CT, 7 ARRANGE_ROOM_CT, 8 ARRANGE_FURNITURE_CT, 9 SOUND, 10 END. Scene_Word_u tagged union shares the type byte. m_scene.c:322: Scene_ct walks the array with a static Scene_Proc[] dispatch table, breaks at END, skips type &gt;= NUM. Scene descriptions are declarative init manifests interpreted into GAME_PLAY.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Rust rust/src/scene_layout.rs: SceneWordType (verbatim tags), SceneWord, interpret_scene. C ABI pc_scene_word_type. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Scene layouts: doors, field init, room types, transitions (source-verified)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>m_scene.h:47: Door_data_c = {next_scene_id, exit_orientation, exit_type, extra_data, exit_position, door_actor_name, wipe_type}. m_scene.c:470: FIELD_CT handler calls mFM_SetFieldInitData(bg_num, bg_disp_size); sets game_started=FALSE, in_initial_block=TRUE, sunlight_flag=TRUE. m_scene.h:39: room types OUTDOORS/MY_ROOM/NPC_ROOM/MISC_ROOM. m_scene.c:512: goto_other_scene saves door record, next_scene_id = door-&gt;next_scene_id + 1, play-&gt;next_scene_no, restore_fgdata_all; WIPE_TYPE_NORMAL -&gt; WIPE_TYPE_FADE_BLACK. ~54 gameplay scenes in m_scene_table.h (brief said 50).</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Rust: DoorData, FieldInit, RoomType, goto_other_scene/SceneTransition. C ABI pc_door_next_scene. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Scene layouts: endianness caveat and gaps</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PORTING CAVEAT found in the decomp: the PC port repacks FIELD_CT from misc.param3 on little-endian (TARGET_PC branch in Scene_Proc_Field_ct) -- the struct layout is big-endian-ordered, which matters for the x86 rewrite; Rust stores decoded fields directly. Gaps: Gameplay_Scene_Read internals untraced; individual *_info[] scene array contents declared but not exposed in reviewed headers; no C callers rewired; Windows link unverified. Workbook rows 92-94.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Workbook rows 92-94. Do not claim the per-scene arrays are recovered.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>High - caveat read directly from decomp source.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2913,6 +2913,72 @@
       <c r="D94" t="inlineStr">
         <is>
           <t>High - caveat read directly from decomp source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BG check: full pipeline order (source-verified)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:1899 mCoBG_BgCheckControll_RemoveDirectedUnitColumn call order verified verbatim: MoveActorWithMoveBg (platform carry) -&gt; InitRevpos -&gt; current/old center positions -&gt; MakeActorInf (old ground/water, speeds) -&gt; WallCheck (columns, then wall vectors) -&gt; GroundCheck (terrain + water + jump flag) -&gt; MoveBgGroundCheck -&gt; CarryOutReverse (apply iff rev_type==0) -&gt; GiveRevposToActor -&gt; RoomScopeCheck. Motion-aware solver: previous AND current positions/ground state feed the solution.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Rust rust/src/bg_check.rs: BgStage (recovered order), BgCheckType, BgActorInfo. C ABI pc_bg_neighborhood, pc_bg_distance_reverse, pc_bg_room_scope. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>High - decomp call order read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BG check: formulas and limits (source-verified)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Neighborhood: range&lt;=40 -&gt; 3, &lt;=80 -&gt; 5, else 7 (m_collision_bg.c:1806). Limits: UNIT_VEC_INFO_MAX=128, MOVE_REGIST_MAX=64, WALL_COL_NUM=2, 5 on/side contacts. Distance reverse (range-dist)+0.00001f. Ground adjust: snap when ground_y&gt;=foot_y; descending snap when old_on_ground and |ground_y-foot_y|&lt;=xz_speed (m_collision_bg.c:409). Water: river 20.0+GetBgY, sea 20.0. Wave rate (1+cos)*0.5. Room scope: S-&gt;160, M/LL2-&gt;240, L/LL1-&gt;320. Plane height dot/-norm-&gt;y.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Rust: neighborhood_size, distance_reverse, adjust_actor_y (both branches), water_y_river/sea, wave_rate, room_scope_extent, carry_out_reverse, limits as constants. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>High - formulas read verbatim from decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BG check: gaps</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Inner wall solver geometric internals not yet ported: crossing vs distance test dispatch, player wall prioritization/sort, attribute/forbidden-wall tables, column collision construction, circular defense wall, slate-vs-normal ground paths, attribute-&gt;gameplay-attribute conversion (wood/water tables). Module documents these as future work. No C callers rewired; Windows link unverified. Workbook rows 95-97.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Workbook rows 95-97. Inner solver honestly marked as future work.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>High - gaps explicitly listed.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2979,72 @@
       <c r="D97" t="inlineStr">
         <is>
           <t>High - gaps explicitly listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Dialogue topics: message index and offset table (source-verified)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>m_msg_data.h:22: MSG_MAX = 0x3F91. mMsg_Get_BodyParam (m_msg_main.c_inc:283): ID -&gt; (addr,size) from ARAM offset table -- entry 0 at data base with size table[0]; entry i at table[i-1] with size table[i]-table[i-1]. PC port byte-swaps the u32 table on little-endian (TARGET_PC) -- second endianness caveat found in the decomp. Message data is an encoded script (control codes for choices/continuations/substitutions/demo orders), not plain strings.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rust rust/src/dialogue_topics.rs: MSG_MAX, msg_body_param. C ABI pc_msg_max. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Dialogue topics: personality pools and talk gate (source-verified)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ac_npc_talk.c_inc:539: aNPC_set_talk_info_talk_request_check -- island: 0x34AC + looks*3 + RANDOM(3); mainland: 0x075F + looks*3 + RANDOM(3). Six personalities x three variants per pool. aNPC_force_talk_request: forced message wins if set; else spontaneous talk needs friendship &gt; 0x80, SEARCH action targeting player, force_call_timer &lt;= 0, dist_xz &lt; 80.0, |dist_y| &lt; 60.0. No monolithic topic_table[] -- topics resolve via condition -&gt; message-ID arithmetic -&gt; offset table.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Rust: talk_check_msg (both bases), force_talk_gate/TalkGate with verbatim thresholds, TopicCategory taxonomy (rewrite-owned). C ABI pc_topic_talk_check. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Dialogue topics: talk state, temper, quest gating, conversation flags (source-verified)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>m_npc.c:4865: mNpc_Talk_Info_c = {timer, talk_num, quest_request, unlock_timer, reset_timer}, one per villager + islanders. m_npc.c:4874: l_npc_temper verbatim -- Normal {4000,12,15}, Happy {3000,10,13}, Angry {4000,12,15}, Sad {4000,10,13}, Sleepy {5000,9,12}, Pitfall {5000,9,12}. mNpc_CheckQuestRequest/mNpc_SetQuestRequestOFF; mNpc_TalkEndMove sets timer=1000 and counts talk. m_npc.h:261: mNpc_NpcConversation_c bitfield beesting:1, fish_complete:1, insect_complete:1. Gaps: talk_request_proc implementation untraced; full ordinary-villager topic taxonomy unresolved; no C callers rewired. Workbook rows 98-100.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Rust: TalkInfo, NPC_TEMPER verbatim, ConversationFlags pack. Workbook rows 98-100.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3043,6 +3043,72 @@
         </is>
       </c>
       <c r="D100" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Wall solver: dispatch order and corrections (source-verified)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:27: wall record = start/end XZ, vertical bounds, normal, normal_angle, wall_name, regist_p, atr_wall. m_collision_bg.c:816: cross_rev_proc[] = {Normal, Attribute, Normal} -- moving walls reuse the normal crossing routine. Normal crossing: rev_dist = range + dist + 0.00001f, reverse = normal * rev_dist (radius-aware, not a teleport). Attribute crossing: reverse = cross - actor_end. Distance: dist&lt;range -&gt; push (range-dist)+1e-5; |dist-range|&lt;2.7 -&gt; contact only (lines 844, 961).</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Rust rust/src/wall_solver.rs: WallSeg2, WallKind2, cross_reverse_normal/attribute, distance_dispatch (push/contact/ignore), distance_push. C ABI pc_judge_wall_from_vector, pc_distance_dispatch. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Wall solver: player vs normal-actor ordering (source-verified)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:1181: normal actors -- spd &gt; range*0.5 -&gt; crossing pass (anti-tunneling); then static distance pass (regist_p==NULL); then moving distance pass; actor_end += rev after every wall (iterative, start preserved). m_collision_bg.c:1140: player -- distance pass (as NORMAL) -&gt; mCoBG_GetWallPriority (merge-sort by squared midpoint distance from actor_start) -&gt; distance pass in priority order (as PLAYER) -&gt; crossing pass. Final rev_pos = actor_end - original_end. CORRECTION to brief: player does an unordered distance pass BEFORE the priority sort, not only after.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Rust: solve_walls with exact branch orderings; wall_priority midpoint sort. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>High - decomp read directly; brief corrected on player pass order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Wall solver: gates, heights, padding, gaps</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mCoBG_JudgeWallFromVector (m_collision_bg.c:533): |angle| &gt; 89.5 deg under the engine's angle convention -- do not reinterpret without it. mCoBG_RoughCheckWallHeight: bot_y + 3.0f cheap rejection, then exact interpolation (mCoBG_GetWallHeight). mCoBG_tab_data = {{5.0,10.0},{0.000001,0.000002}} pads wall segments beyond tile edges. Gaps: endpoint-circle geometry, 0.1f/90deg-0x100 neighbor suppression, slate diagonal normals, forbid-vector tables, column solver -- future work. No C callers rewired. Workbook rows 101-103.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Rust: judge_wall_from_vector (convention caveat documented), rough_check_wall_height, wall_height_at. Workbook rows 101-103.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>High - decomp sources read directly.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3111,6 +3111,72 @@
       <c r="D103" t="inlineStr">
         <is>
           <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Wall priority: tail adjustment and merge sort (source-verified)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:476: mCoBG_MakeTab2MoveTail -- x_bias=|dx|/(|dx|+|dz|), z_bias=1-x_bias, 0.2-unit proportional backward shift of actor_start; applied before the player branch (line 1135), so priority uses the shifted start. m_collision_bg.c:1033: mCoBG_MergeSortFloat -- recursive, middle=(first+last)&gt;&gt;1, halves in pre_work[65]/bk_work[65] (65 suffices for halves of 128), merge comparison &lt;= (left-first). Priority metric is wall-midpoint dist-squared from adjusted start; no normals/types/heights participate.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Rust rust/src/wall_priority.rs: make_tab_2_move_tail (verbatim), merge_sort_float (recursive, &lt;= merge). C ABI pc_make_tab_2_move_tail. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Wall priority: reconstruction and dispatch tables (source-verified)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Reconstruction: for each sorted distance, first unused wall index with dist_table[unit]==sorted[i], tracked by u64 used mask -- ties resolve in original wall order. 64-bit mask vs 128 wall capacity: unresolved whether &gt;=64 walls occur in practice. m_collision_bg.c:1010: dispatch tables NORMAL-&gt;{Normal,Attribute,Normal}, PLAYER-&gt;{NormalSpecial,AttributeSpecial,NormalSpecial}. NORMAL requires RangeCheckLinePoint; player-special requires front(end)&amp;&amp;front(start), then endpoint circles. mCoBG_CheckDistSPCheck: shared endpoint within 0.1 and u16 angle diff &lt; 90deg-0x100 (0x3F00) suppresses corner correction.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Rust: reconstruct_priority (u64 mask), priority_order (full construction), dist_routine (both tables), check_dist_sp_suppress, player_special_front_gate, point_in_circle. wall_solver.rs player path now uses the faithful priority. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wall priority: three-pass sequence and gaps</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Exact player sequence: PASS 1 normal distance (original order) -&gt; MakeTab2MoveTail-adjusted start -&gt; midpoint dist2 -&gt; merge sort -&gt; u64 reconstruction -&gt; PASS 2 player-special distance in priority order (actor_end mutated each wall) -&gt; PASS 3 crossing in ORIGINAL order -&gt; rev_pos = actor_end - original_end. The priority is a snapshot from the old position; the collision point keeps changing -- a hybrid static-order/dynamic-solve. Gaps: endpoint circle-line intersection math, full mCoBG_GetCrossCircleAndLine2Dvector, GetSpecialDistanceReverse, no C callers rewired. Workbook rows 104-106.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Workbook rows 104-106. Endpoint-circle math honestly marked future work.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>High - sequence read directly from source.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3177,6 +3177,28 @@
       <c r="D106" t="inlineStr">
         <is>
           <t>High - sequence read directly from source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Authorized test run #4 (165/165)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Philip said 'Run the tests' 2026-10-07: cargo test --lib = 165 passed, 0 failed. Covers all 35 previously dormant tests: house_scene (4), scene_layout (5), bg_check (7), dialogue_topics (6), wall_solver (7), wall_priority (6) -- on top of the prior 130/130. No failures; no test bugs.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md test status updated across the six module sections.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>High - observed run output.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3199,6 +3199,72 @@
       <c r="D107" t="inlineStr">
         <is>
           <t>High - observed run output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Forbidden-wall tables: vector and index tables (source-verified)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:82: mCoBG_make_vector_table[8] verbatim -- 0deg/UP, -90deg/RIGHT, 90deg/LEFT, 180deg/DOWN, 45/135/225/315deg diagonal slate entries with SQRT_OF_2_DIV_2 normals. m_collision_bg.c:93: mCoBG_forbid_vector_idx[36][2] verbatim, attr-27 offset; two-wall corners 51-54 (tunnels) and 59-62 (river-bank corners), e.g. 51={0,2}; attr 31 (wood bridge center) = {-1,-1} generates nothing. include/m_collision_bg.h:79: 27-62 attribute comments confirmed the family layout (wood/stone bridge, wave, river bank, grass river/cliff, tunnel, diagonal cliff, diagonal river bank); 63 is slate/slope, outside the table.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rust rust/src/attr_walls.rs: MAKE_VECTOR_TABLE, FORBID_VECTOR_IDX, ATTRIBUTE_NAMES verbatim; forbid_vectors 0-2 IDs; is_two_wall_attribute; is_forbid_attribute range gate. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Forbidden-wall tables: generation gate and consumers (source-verified)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>m_collision_bg_wall.c_inc:508: forbid_proc = (old_on_ground &amp; attr_wall) &amp; 1 selects MakeForbidAttrVector vs DUMMY -- forbidden vectors appear only when actor was grounded AND the attribute-wall flag is set; they are additional constraints, not replacements. Generated walls get atr_wall=TRUE, regist_p=NULL, segment from mCoBG_UnitNoName2StartEnd with the check-type tab padding; no wall-height bounds assigned. m_collision_bg_info.c_inc:858: mCoBG_CheckAttribute_BallRolling reuses the SAME forbid table with norm_angle + 180deg. attr_wall also switches normal/slate registration to AttributeOn variants.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rust: forbid_generation_enabled gate, attribute_wall_spec (atr_wall=TRUE, no moving-BG), ball_rolling_angles (+180deg, None sentinel for -1), wall_registrar_variant. Feeds wall_solver.rs atr_wall dispatch. C ABI pc_forbid_vectors, pc_forbid_gate. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Forbidden-wall tables: gaps</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Not yet ported: exact mCoBG_UnitNoName2StartEnd segment-orientation mapping (t0/t1 per wall name); the AttributeOn normal/slate registrar internals; the bridge/water special case in RegistNormalWallVector_AttributeOff (old_in_water + WOOD + attr 27-35 with min-corner-height temp unit); the parallel l_attribute_action_info[64] plant/NPC/placement table and mCoBG_unit_attribute_water_info water-translation table; no C callers rewired. Workbook rows 108-110.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Marked as future work in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3263,6 +3263,72 @@
         </is>
       </c>
       <c r="D110" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Column construction: struct and object recipes (source-verified)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c:10: mCoBG_column_c = X/Y/Z pos, top height, radius, s16 atr_wall, ux/uz -- a vertical cylinder as X/Z circle + bottom/top Y. m_collision_bg_column.c_inc:136: MakeOneColumnCollisionData chain verified: hole (19, ground Y, atr_wall=TRUE, needs old_on_ground); small/med/large/full trees (19, +30/+40/+60/+80); stumps (+30, r=10 for the four *_STUMP001 IDs else 18); rock (19, +31.5); mailbox (15, +50); sign (19, +45); RSV_SIGNBOARD (10, +45); koinobori/flag (19, +160). Non-hole branches set atr_wall=FALSE; X/Z at unit center, Y from mCoBG_GetBgY_OnlyCenter_FromWpos2. Own unit excluded (ut_x==ux &amp;&amp; ut_z==uz -&gt; FALSE).</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Rust rust/src/columns.rs: Column record, ColumnItemKind with exact recipes, make_one_column. C ABI pc_column_recipe. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Column construction: 16-slot limit and collision math (source-verified)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>m_collision_bg_column.c_inc:290: MakeColumnCollisionData walks row-major, builds while col_count&lt;16, IGNORES the MakeOne return value -- count is examined slots, failed slots stay zeroed (bzero'd in normal path). Confirmed quirk, not the nearest 16. mCoBG_ColumnCheck_NormalWall: skip if actor inside at old pos or height &lt; now_y+3.0; dist &lt; range+radius -&gt; radial X/Z push (rev_vec.y=0) + wall contact; 0 &lt; dist-check_dist &lt; 2.7 -&gt; contact only. Attribute columns: ignored unless old_on_ground, then same radial test without height gate. Pipeline (m_collision_bg.c:1253/1261): object columns -&gt; decal columns -&gt; terrain wall vectors (GetWallReverse).</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Rust: make_column_collision_data (16-slot quirk, own-unit exclusion, None failed slots), column_check_normal/column_check_attr, COLUMN_CONTACT_BAND/HEIGHT_MARGIN constants. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Column construction: gaps</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Not yet ported: the decal-circle register/clear machinery (mCoBG_decal_circle[3], with decomp-noted original-game bugs); the separate line-vs-column sweep routine (mCoBG_LineWallCheck_Column); column-derived ground height (mCoBG_GetBGHeight_Column, incl. center-unit suppression); no C callers rewired. Workbook rows 111-113.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Marked as future work in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3329,6 +3329,72 @@
         </is>
       </c>
       <c r="D113" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Segment-orientation: placement mapping (source-verified)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>m_collision_bg_wall.c_inc:1: mCoBG_UnitNoName2StartEnd verbatim -- UP (ux*U-t0, uz*V) +X extended by t1; DOWN same line reversed endpoint order; LEFT/RIGHT vertical +Z; SLATE_UP +X/-Z diagonal; SLATE_DOWN +X/+Z diagonal. m_collision_bg.c:58: mCoBG_tab_data = {{5.0,10.0},{0.000001,0.000002}} -- NORMAL extends ~5/10 past the tile, PLAYER essentially exact. Unit world size 40 (mFI_UNIT_BASE_SIZE, m_field_info.h:16).</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Rust rust/src/segment_map.rs: WallName, CheckType, TAB_DATA, unit_no_name_2_start_end verbatim. attr_walls.rs gained forbid_wall_segments -- the previously flagged UnitNoName2StartEnd gap is now closed. C ABI pc_unit_no_name_2_start_end. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Segment-orientation: normal selection and front test (source-verified)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>mCoBG_SearchWallFlag all four cardinal branches read directly: UP nbr down-offsets higher -&gt; (0,+1)/0deg else (0,-1)/180deg; DOWN nbr up-offsets higher -&gt; (0,-1)/180deg else (0,+1)/0deg; LEFT nbr right offsets higher -&gt; (+1,0)/90deg else (-1,0)/-90deg; RIGHT nbr left offsets higher -&gt; (-1,0)/-90deg else (+1,0)/90deg. Slate: SLATE_UP leftUp vs rightDown -&gt; 45deg/-135deg; SLATE_DOWN leftDown vs rightUp -&gt; 135deg/-45deg. m_collision_bg_math.c_inc:251: front = n.point - n.start &gt;= 0 -- from the stored normal, never segment direction. wall_name drives height interpolation (X for UP/DOWN, Z for LEFT/RIGHT, projected for slate).</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rust: point_info_front_line, search_wall_flag (all four branches), slate_normal, interp_axis. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Segment-orientation: gaps</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Not yet ported: mCoBG_Check45Angle front/left/right/back classification from normal angles; Nintendo's original terminology for the wall_name/normal/normal_angle distinction is not in the decomp. Workbook rows 114-116.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Marked as future work in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3395,6 +3395,72 @@
         </is>
       </c>
       <c r="D116" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Decal circles: two mechanisms separated (source-verified)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CORRECTION to the brief: mCoBG_MakeCircleDefenceWall (m_collision_bg_wall.c_inc:599) does NOT populate mCoBG_decal_circle. It appends WALL VECTORS: for each ordered pair of distinct columns whose (dx,dz) matches one of eight defence_wall_info entries, it emits TWO walls (col0 pos -&gt; col1 pos) with the entry's two opposite-facing normal/angle/wall_name pairs, both atr_wall=TRUE, regist_p=NULL. Gated on attr_wall &amp;&amp; old_on_ground; capped at 128. Table verbatim: (+-1,0)-&gt;0deg/180deg WALL_UP; (0,+-1)-&gt;90deg/-90deg WALL_RIGHT; (+-1,+-1)-&gt;135deg/-45deg SLATE_DOWN; (+-1,-+1)-&gt;-135deg/45deg SLATE_UP. These bridge gaps between adjacent object columns.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rust rust/src/decal_circles.rs: DEFENCE_WALL_INFO[8] verbatim, circle_defence_wall_idx, make_circle_defence_walls (ordered-pair scan, 128 cap, gate). DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Decal circles: registration machinery and gameplay meaning (source-verified)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>m_collision_bg_column.c_inc:1: mCoBG_regist_circle_info[3] records (pos, in_use, start/end/now radius, start/now timer) drive live mCoBG_column_c records fed as the SECOND ColumnWallCheck pass (m_collision_bg.c:1261). Radius interpolates linearly (mCoBG_CalcAdjust) over the timer, then the slot deactivates; columns get height=pos.y, atr_wall=TRUE. Gameplay meaning: the registrars are the player dig/scoop actions -- mCoBG_RegistDecalCircle(pos, 0.0f, 19.0f, 12) -- the dug hole's decal gets a matching temporary collision circle growing 0-&gt;19 over 12 frames. Init at scene start (m_play.c:435), ticked per frame (m_play.c:539).</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rust: RegistCircleInfo, DecalCircleSystem (regist/calc_timer/init/active_circles), calc_adjust. Reuses columns::Column. cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Decal circles: original bugs and gaps</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Decomp-annotated original-game bugs, DOCUMENTED not reproduced: RegistDecalCircle clears sizeof(whole array) instead of one record (clobbering into decal-circle data) and doesn't stop after the first free slot; InitDecalCircle clears 3x too much memory. Rust implements the intended behavior. mCoBG_CrossOffDecalCircle is decomp-marked @unused/@fabricated and intentionally not ported. Workbook rows 117-119.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Marked as future work/intentional in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3463,6 +3463,28 @@
       <c r="D119" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Authorized test run #5 (188/188)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Philip said 'run the tests' 2026-10-07: cargo test --lib = 188 passed, 0 failed. Covers 23 new tests: attr_walls (8), columns (5), segment_map (5), decal_circles (5) -- on top of the prior 165/165. One test bug caught and fixed before the pass: a segment-length assertion in segment_map (U + t1 = 50, not 55). No implementation failures.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md test status updated across the four module sections.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>High - observed run output.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3485,6 +3485,72 @@
       <c r="D120" t="inlineStr">
         <is>
           <t>High - observed run output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>64-wall question: player-path wall budget (analysis, resolved)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Player calls mCoBG_BgCheckControll with range 18.0f (m_player_common.c_inc:2579) -&gt; 3x3 neighborhood (9 units). MakeUnitVector budget: 9 slate attempts + 12 normal attempts (edge de-duplication bitmask l_make33_coldata: bit counts verified 12 for 3x3, 40 for 5x5) + 9 forbid attempts x up to 2 walls = 39 terrain max. Circle-defence: own unit excluded -&gt; &lt;=8 columns, &lt;=24 ordered adjacent pairs x 2 = &lt;=48 walls (gated on attr_wall &amp;&amp; old_on_ground). Moving-BG adds a few. Theoretical max ~87 &gt; 64: the u64-mask overflow IS reachable in pathological arrangements (columns in all 8 surrounding units + discontinuities on all 12 checked edges + forbid attributes everywhere). Normal gameplay sees &lt; 20 walls.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Analysis only; no code change yet. DOCUMENTATION.md note added under wall-priority.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>64-wall question: x86 consequence and Rust fix</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Original: flag |= 1 &lt;&lt; (u64)unit with unit &gt;= 64 is C UB. On x86-64 the shift count wraps mod 64, so wall 64 aliases bit 0 -- the reconstruction silently treats a wall as already-used / duplicates another wall in the priority table. Corruption of ordering, not a crash. Fix: Rust reconstruct_priority now uses u128 instead of u64 -- bit-identical to the original for &lt; 64 walls, correct for &gt;= 64. The original UB is documented, not reproduced. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>rust/src/wall_priority.rs: u128 mask with the full analysis in the doc comment.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>High - fix verified by check; behavioral identity below 64 walls by construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Rewiring doc written</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>New repo doc rewiring.md: plain-language definition of rewiring (plugging Rust parts into C call sites), the one working example (letter scorer from m_mail_check.c), and the full inventory of every Rust module with C ABIs organized in three waves -- Wave 1 stateless pure functions (wall_priority, segment_map, attr_walls, columns, wall_solver, bg_check, inventory, dialogue_topics, house_scene, scene_layout), Wave 2 struct-translating functions, Wave 3 engine plumbing -- plus the per-rewiring procedure and what is needed from Philip (his Windows machine for rebuild+run; fallback-flag decision). Workbook rows 121-123.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rewiring.md committed at repo root.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>High - ABI inventory grepped from source.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3551,6 +3551,72 @@
       <c r="D123" t="inlineStr">
         <is>
           <t>High - ABI inventory grepped from source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Endpoint-circle: the normal-line correction (source-verified)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CORRECTION CONFIRMED at m_collision_bg.c:908: the solver intersects a line through the wall ENDPOINT parallel to the wall NORMAL with the actor's X/Z circle -- point=unit_vec-&gt;start, vec=unit_vec-&gt;normal. The wall segment tangent is never passed. The segment-based sibling mCoBG_GetCrossCircleAndLine2D is decomp-marked @unused/@fabricated. mCoBG_GetSpecialDistanceReverse (m_collision_bg.c:858): first intersection on the NON-front side wins; reverse = edge - cross, exactly parallel to the wall normal (-tN). Not a capsule intersection -- document as endpoint-normal-line/actor-circle construction.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rust rust/src/endpoint_circle.rs: cross_circle_and_line_2dvector (verbatim quadratic), get_special_distance_reverse. C ABI pc_cross_circle_line. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Endpoint-circle: quadratic and gate sequence (source-verified)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>m_collision_bg_math.c_inc:295: A=vx^2+vz^2 (no normalization assumed), B=2(v.point - v.center), C=|point-center|^2 - r^2, R=B^2-4AC accepted when R&gt;=0 (tangent counts), root=ABS(sqrtf(R)) verbatim, A!=0 guard, t=(-B+-root)/2A. Gate sequence (m_collision_bg.c:894): front(end)&amp;&amp;front(start) -&gt; normal dist &lt; range -&gt; start-in-circle else end-in-circle -&gt; CheckDistSPCheck suppression -&gt; intersection -&gt; height gate (old_ground_y-5)+3 &lt;= height.top -&gt; reverse + registration. GetDistPointAndLine2D_Norm = |n.p - n.start| with no division; JudgePointInCircle squared, no sqrt; XYZ wrapper is X/Z only.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Rust: judge_point_in_circle, dist_point_and_line_2d_norm, endpoint_circle_collision (full gate sequence, reusing segment_map and wall_priority). cargo check --lib clean. Tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>High - decomp sources read directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Endpoint-circle: gaps</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>This closes the endpoint-circle gap flagged since the wall-solver work. Remaining in the player-special path: the AttributeWall_Special variant's exact differences (same endpoint math, different height handling -- internals not yet fully traced); no C callers rewired. Workbook rows 124-126.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Marked as future work in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3615,6 +3615,72 @@
         </is>
       </c>
       <c r="D126" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Wave 1: reorganization into kernels (brief-driven)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Wave 1 reclassified from 'stateless functions' into pure kernels + C shims: 1A pure numerical (msg_max, make_tab_2_move_tail, segment_for_wall, inventory scan, judge_wall_from_vector with atan-backend caveat); 1B pure lookup/mapping (forbid_vector_kernel, forbid_proc explicit gate, priority_order, scene_word_type, column_recipe with C keeping ground-height/callback); 1C simple data ops (neighborhood coords fixed buffer, room_scope, door arithmetic, house_surface_lookup); 1D extracted stateless pieces (talk_count_allowed/talk_patience, distance_reverse to split further). Postponed: distance_dispatch, request_proc_id, topic_talk_check, full GetWallReverse.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rewiring.md rewritten with kernel+shim architecture, USE_RUST fallback pattern, differential-testing guidance, f32 discipline, no_std note. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>High - brief verified against decomp structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Wave 1: kernel+shim implementation and faithful edge behavior</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>wall_priority.rs: make_tab_2_move_tail now value-returning; REMOVED the 1e-9 denominator clamp -- the C code has no zero check, so zero input produces NaN biases in C and the port reproduces that instead of 'fixing' it. #[repr(C)] PcVec2/PcSegment/PcForbidVector/PcHouseSurface/PcUnitCoord added; C ABIs are thin unsafe shims over safe kernels. New kernels: forbid_vector_kernel, forbid_proc/pc_forbid_proc (old pc_forbid_gate kept), talk_count_allowed/talk_patience (+ABIs), house_surface_lookup, neighborhood_coords + pc_bg_neighborhood_coords (caller buffer, no Vec over FFI). Differential bit-pattern test template added (to_bits, not epsilon). cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>6 modules touched; existing ABI names/signatures preserved (new functions added, none removed).</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>High - check clean; behavior verified by unit tests (not run per standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Wave 1: remaining prep</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Still to add per the brief: pc_wall_priority fixed-buffer ABI; splitting pc_bg_distance_reverse into point-line distance -&gt; penetration -&gt; height gate -&gt; dispatch kernels; mCoBG_Get2VectorAngleF faithful atan backend for judge_wall_from_vector. The actual C-adapter plugs need Philip's Windows MSYS2 machine (rebuild + run). Workbook rows 127-129.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Documented in rewiring.md as next steps.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3683,6 +3683,28 @@
       <c r="D129" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Authorized test run #6</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Philip authorized 'Run the tests' (2026-10-07). cargo test --lib: 198/198 pass, 0 failed, 0 ignored. This is 188 from run #5 plus 10 new: move_tail differential bit-pattern test (1), forbid_proc/forbid_vector_kernel (2), talk gates (1), house_surface_kernel (1), neighborhood_coords (1), and the 4 endpoint-circle tests that shipped with commit 7507627 but had never run.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md updated (4 occurrences -&gt; 198/198 run #6).</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>High - full suite green.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3705,6 +3705,72 @@
       <c r="D130" t="inlineStr">
         <is>
           <t>High - full suite green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Terrain-wall pipeline and data format</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>m_collision_bg.c + m_collision_bg_wall.c_inc + m_collision_bg.h: pipeline = neighborhood -&gt; mCoBG_MakeUnitVector (slate + cardinal + bridge mods + forbid walls) -&gt; unit_vec[128] -&gt; moving-BG -&gt; columns -&gt; circle-defence -&gt; solver. Terrain record is a 4-byte bitfield: 1-bit slate_flag, five 5-bit heights, 6-bit attribute; world offset = value*10.0+base_height. Walls are edges between two UnitInfos; SearchWallFlag picks normal from the higher side (UP:(0,1)/0deg vs (0,-1)/180deg; LEFT:(1,0)/90deg vs (-1,0)/-90deg; DOWN:(0,-1)/180deg vs (0,1)/0deg; RIGHT:(-1,0)/-90deg vs (1,0)/90deg); no wall when heights equal. JudgeTopAndSet assigns top/btm per endpoint. SearchSlateDetail: bot_right!=top_left-&gt;SLATE_UP, top_right!=bot_left-&gt;SLATE_DOWN, else SLATE_UP. Decomp @BUG: WALL_UP branch never sets wall_name.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: TerrainUnit, WallKind, WallBounds, TerrainWall, decode_height, search_slate_detail, judge_top_and_set, search_wall_flag, slate_wall_geometry, cardinal_wall_from_units (reproduces the UP @BUG). cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Bridge/water special case</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Bridge attrs (m_collision_bg.h): 27=wood NW, 28=wood SW, 29=wood SE, 30=wood NE, 31=wood center, 32=stone N, 33=stone E, 34=stone W, 35=stone S. RegistNormalWallVector_AttributeOff verbatim: old_in_water + WOOD&lt;-&gt;bridge -&gt; bridge side flattened to min corner height, slate off, ordinary generator runs; bridge&lt;-&gt;bridge or bridge&lt;-&gt;non-wood -&gt; NO normal wall; ordinary&lt;-&gt;ordinary -&gt; normal. Slate_OldInWater returns early for 27-35. MakeUnitVector: DOCK/ISLAND blocks force old_in_water=FALSE. bridge_search_water masks verbatim {3,6,12,9,240,1,8,2,4} (bits 0=N,1=W,2=S,3=E,4=NW,5=NE,6=SE,7=SW) matching piece geometry. woodb_water_info quarter table verbatim (27-&gt;RIVER_NW x2 + WOOD x2, etc.). GroundCheck (m_collision_bg.c:1730): old_in_water + bridge attr -&gt; search masked neighbors for water, adopt water attr/height. PURPOSE of flattening (walking water-&gt;bridge without phantom cliff) is inference, not a source comment.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: terrain_wall_policy/WallPolicy, flatten_bridge_unit, slate_wall_suppressed, apply_block_water_rule, bridge_search_water_mask, bridge_quarter_attribute. C ABI: pc_terrain_wall_policy, pc_bridge_search_water_mask, pc_bridge_quarter_attribute, pc_search_slate_detail, pc_search_wall_flag. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Terrain walls: remaining gaps</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>The full mCoBG_MakeUnitVector loop is NOT yet ported (neighborhood acquisition, make_info bit patterns, moving-BG walls); mCoBG_SearchWaterAttributeFrom4Area not ported; no C callers rewired. All terrain_walls.rs tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Documented in DOCUMENTATION.md and rewiring.md Wave 2 row.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3769,6 +3769,72 @@
         </is>
       </c>
       <c r="D133" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Moving-background registration and wall generation</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>m_collision_bg_move.c_inc + m_collision_bg.h: regist struct (wpos/last_wpos/angle_y/contact/bg_size/base_ofs/height/attribute/active_dist/scale_percent); 64 fixed slots, first-free allocation, no compaction (slot IDs); RegistMoveBg fills fields + zeroes contact; CrossOff zeroes/NULLs/decrements. Size presets verbatim: A={20^4}, B_0={60,20,20,20}, B_180={20,60,20,20}, B_270={20,20,20,60}, B_90={20,20,60,20}, C={40^4}; FTR_TYPE_NUM uses caller size. SizeData2CollisionData verbatim: 4 walls (UP normal (0,-1)/180deg, LEFT (-1,0)/-90deg, DOWN (0,1)/0deg, RIGHT (1,0)/90deg), epsilon t0 from tab_data[check_type] (5 vs 1e-6), flat bounds pos.y..pos.y+height, regist_p=regist, atr_wall=FALSE. RotateY: x'=xcos+zsin, z'=-xsin+zcos; rotate only if |deg|&gt;=0.05 BUT normal_angle+=angleY always. Walls only when 2D dist &lt; active_dist.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>move_bg.rs: MoveBgSize + presets + boat consts, MoveBgTransform, short_to_rad/deg_to_short, rotate_y, make_move_bg_walls. C ABI: pc_make_move_bg_walls, pc_move_bg_delta. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Moving-background ground test, actor carry, contacts</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GetMoveBgHeight: square broad phase (|dx|&lt;dist &amp;&amp; |dz|&lt;dist), footprint from scaled size + base_ofs, rotated whenever rad!=0 (no 0.05 threshold), translated to wpos; inside iff two RangeCheckLinePoint slab tests pass (verbatim: front-line test at both endpoints); top = wpos.y + height; LAST matching registration wins. MoveActorWithMoveBg_OnMoveBg: position += wpos - last_wpos, translation ONLY (rotation/scale do not carry). Side contact = (actor_id, angle), on contact = actor_id only; both capped at 5, no dedup. Moving walls reuse normal-wall solvers; non-player actors process moving walls in a separate pass after static walls; regist_p!=NULL is the MOVE kind test. Boats: 2 slots, {20,20,40,40}, height 30, SAND, active_dist 120.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>move_bg.rs: range_check_line_point, judge_move_bg_ground_check, move_bg_footprint_height, move_bg_delta, MoveBgContact + set_side/on_contact, register_slot. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Moving-background: remaining gaps</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>The 64-slot registry (Regist/Idx2RegistPointer/CrossOff/Init) stays in C per the kernel-first strategy; the full MoveBgGroundCheck on-ground state machine (result flags, shape_info.move_bg_idx) is not yet ported; no C callers rewired. All move_bg.rs tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Documented in DOCUMENTATION.md and rewiring.md Wave 1C row.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3837,6 +3837,72 @@
       <c r="D136" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Bridge policy: wall/slope formalization</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RegistNormalWallVector_AttributeOff formalized: !old_in_water-&gt;normal; WOOD&lt;-&gt;bridge(27-35)-&gt;flatten bridge side to min corner height + slate off + ordinary gen; bridge&lt;-&gt;bridge-&gt;suppress; bridge&lt;-&gt;non-wood-&gt;suppress; non-bridge&lt;-&gt;non-bridge-&gt;normal. Slope: Slate_OldInWater early-returns for 27-35. Already in terrain_walls.rs from the terrain commit; this work adds the positive-form bridge_should_make_slate.</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: bridge_should_make_slate. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Bridge policy: attribute lookup split + water table + ground search</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Wpos2Attribute (m_collision_bg.c:1561): 27-31 -&gt; woodb quarter table, 32-35 -&gt; STONE (wall policy treats 27-35 uniformly, lookup does not). GetUnitArea verbatim (AREA_N=0/W=1/S=2/E=3). unit_attribute_water_info verbatim 64 entries (water-&gt;self, bridge corners 27-30 + river banks 39-42 -&gt; river corners, else GRASS0). GroundCheck bridge branch (m_collision_bg.c:1730): gated on !attribute_wall &amp;&amp; old_in_water &amp;&amp; 27-35; directions 0..8 masked, raw neighbor attr through water table, FIRST water result wins (order significant); water height at actor's current position. Feedback loop: is_in_water -&gt; old_in_water -&gt; policies -&gt; is_in_water.</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: BridgeAttribute, is_water_attribute, UNIT_ATTRIBUTE_WATER_INFO, search_water_attribute, get_unit_area, bridge_wpos_attribute, bridge_water_search + pc_bridge_water_search. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Bridge policy: attribute-number correction + remaining gaps</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CORRECTION: first terrain_walls commit had wrong attribute numbers (WATER=8, WOOD=19, SAND=18); actual enum is GRASS0=0, WATER=12, RIVER_NE=21, SAND=22, WOOD=23, SEA=24. Fixed here (woodb table values + move_bg boat SAND). Earlier tests passed only because they used the wrong constants consistently - caught by re-verifying the header enum. Remaining: full MakeUnitVector loop, full GroundCheck state machine, no C callers rewired. All bridge-policy tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md correction note; workbook rows 137-139.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>High - corrected against source.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3903,6 +3903,72 @@
       <c r="D139" t="inlineStr">
         <is>
           <t>High - corrected against source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Cardinal edge construction: ownership tables + anchors</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>l_make33/55/77_coldata verbatim (3x3 = 00,02,02 / 01,03,03 / 01,03,03; 5x5 and 7x7 same pattern). Only UP/LEFT bits ever set - canonical edge ownership, each shared edge built once. GetUnitInfSearchData: count 3/5/7 -&gt; table, default 3x3. Neighbor anchors: UP=idx-size, LEFT=idx-1, DOWN=idx+size, RIGHT=idx+1.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: MAKE_33/55/77_COLDATA, cardinal_edge_mask, cardinal_neighbor_index + pc_cardinal_edge_mask. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Cardinal edge construction: slate adjustment + height interpolation</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UtInf2NormalSlateWallVector verbatim: one-side-slate -&gt; copy slate unit, overwrite one corner from diagonal partner, all 8 direction/side/orientation cases (e.g. unit1+UP+SLATE_UP: leftDown=rightDown). CheckHeightExactly verbatim: LEFT/RIGHT along Z, UP/DOWN along X, zero-division guard, moving walls use end bounds, gate pos_y+3.0&lt;=top; slate takes separate GetWallHeight path. wall_name is algorithmic (picks interpolation axis).</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: adjust_slate_unit_for_cardinal, check_height_exactly + pc_check_height_exactly, cardinal_edge_exists. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Cardinal edge construction: remaining gaps</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>The full mCoBG_MakeUnitVector loop assembly (mask iteration + wall/slate/forbid dispatch in order) is still not ported as one function; the slate GetWallHeight path is not ported; no C callers rewired. All new tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Documented in DOCUMENTATION.md; rewiring.md Wave 1C row updated.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3967,6 +3967,72 @@
         </is>
       </c>
       <c r="D142" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Slope-wall policy: where slope data comes from</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Answered the brief's open question from the local decomp: mFI_UtNum2UtCol (m_field_info.c:842) reads collision from g_fdinfo-&gt;block_info[num].bg_info.collision; m_field_make.c mFM_SetBG fills it by COPYING collision[UT_Z_NUM][UT_X_NUM] from a predefined mFM_bg_data_c entry (data_bgd[]) selected by bg_name. Slate flags/heights/bridge attrs are baked into acre template data - the field maker does NOT classify slopes at runtime. Confirms the predefined-acre model at the collision-data level.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Documented in DOCUMENTATION.md; no new code (mechanism-level finding).</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Slope-wall policy: ground height on slopes</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>mCoBG_GetAreaYSlatingUnit (m_collision_bg.c:1284) verbatim: tilted plane along the diagonal; unit area selects the ground corner - SLATE_UP: S/E-&gt;bot_right*10, N/W-&gt;top_left*10; SLATE_DOWN: N/E-&gt;top_right*10, W/S-&gt;bot_left*10; SLATE_UP fallthrough into SLATE_DOWN case preserved. GetBGHeight_Normal dispatches on slate_flag. The ground-path slate test is a SINGLE comparison (top_left!=bot_right), unlike SearchSlateDetail's two-comparison version - kept as separate functions.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>terrain_walls.rs: get_area_y_slating_unit, slate_detail_for_ground + pc_slate_ground_y. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Slope-wall policy: scope and remaining gaps</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>The brief's Policies A-G (embedded upper section, protruding lower mound, corner resolution) are town-generation/visual-terrain level; exact per-tile ramp footprints live in binary BG data, not derivable code - documented as mechanism, not ported as geometry. Collision-level slope policy (walls + ground height) is fully ported. Remaining: full GroundCheck state machine, no C callers rewired. New tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md scope note; workbook rows 143-145.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4033,6 +4033,72 @@
         </is>
       </c>
       <c r="D145" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Bridge-water mask: block-type mechanism (brief hypothesis confirmed)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>No stored binary water-mask bitmap exists. The mechanism is: (1) seven river block types (40-46) followed by seven parallel bridge variants (47-53), conversion = type+7 (RIVER_SOUTH_BRIDGE - RIVER_SOUTH); (2) mRF_SetBridgeBlock (m_random_field_ovl.c:1022) finds the river/cliff crossing via waterfall types, counts river blocks before/after, picks ONE random river block before the crossing (plus optionally one after for two-step towns = the double-bridge mechanism) and converts it; (3) pluss_bridge[108] (m_map_ovl.c, verbatim) maps block type -&gt; bridge counterpart for the map overlay, 255 = none. The brief's template/counterpart model is exactly right; bridges are never placed on arbitrary water.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bridge_acre.rs: block_type consts, is_river/is_bridge_block, river_to_bridge_block, PLUSS_BRIDGE verbatim (generated from source), bridge_counterpart, select_bridge_blocks. C ABI: pc_river_to_bridge_block, pc_bridge_counterpart. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Bridge-water mask: selection kernel</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>select_bridge_blocks models the SetBridgeBlock selection: river-block indices before/after the crossing, random ordinals, second bridge gated on stepmode==TWO &amp;&amp; rng. The source keeps scanning after a match ('no break?') but selection is by ordinal among river blocks, so the kernel is exact.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>In bridge_acre.rs with unit tests (not run, standing rule).</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Bridge-water mask: scope and remaining gaps</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>The brief's candidate-mask vs rendering-mask distinction and per-tile water/land topology live in binary acre BG data (collision arrays + display lists), not derivable code - documented as mechanism, not ported as geometry. Collision-level bridge masks were already in terrain_walls.rs. Remaining: the full random-field pipeline, Tortimer event selection logic, no C callers rewired. New tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 146-148.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4101,6 +4101,28 @@
       <c r="D148" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Authorized test run #7</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>cargo test --lib: 231/231 pass, 0 failed. First run covering terrain walls (6401aaf), moving backgrounds (eb98137), bridge policy (ab41f9a), cardinal edges (a64bf9a), slope ground policy (c31a7f2), bridge acres (843f219). Two test-expectation bugs found and fixed against the decomp (both were wrong corners/values in the tests, implementation was source-faithful): edge_existence used right_up where UP compares left_down/right_down; slate fallthrough with invalid area returns 0.0 per the source's default, not the SLATE_DOWN mapping.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Test-only fixes in rust/src/terrain_walls.rs; commit 63a4fe2.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>High - full suite green.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4123,6 +4123,50 @@
       <c r="D149" t="inlineStr">
         <is>
           <t>High - full suite green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AttributeWall_Special: exact differences vs NormalWall_Special</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>mCoBG_Distance2Reverse_AttributeWall_Special (m_collision_bg.c:970) vs _NormalWall_Special: IDENTICAL horizontal math (front-line gates, dist&lt;range, endpoint-circle tests, CheckDistSPCheck, GetSpecialDistanceReverse). Exact diffs: (1) NO height gate - normal requires (old_ground_y-5)+3&lt;=top per endpoint, attribute has no height test and always blocks; (2) registers NULL height instead of the endpoint's WallHeight; (3) never calls SetMoveBgContactSide. Confirms and sharpens the brief's hypothesis.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>endpoint_circle.rs: wall_kind consts, get_wall_kind, normal_special_height_gate, attribute_wall_special_collision. C ABI: pc_attribute_wall_special.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AttributeWall_Special: dispatch and scope</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>mCoBG_GetWallKind: regist_p!=NULL-&gt;MOVE(2), atr_wall-&gt;ATTRIBUTE(1), else NORMAL(0); player table {NormalSpecial, AttributeSpecial, NormalSpecial} so MOVE reuses the normal path. atr_wall set for forbid-vector/special walls. Non-player attribute path (point-to-line, 2.7f graze, no height) not ported - out of scope. Scoped test run: 5/5 pass.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 150-151.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4165,6 +4165,50 @@
         </is>
       </c>
       <c r="D151" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AttributeWall_Special: correcting the brief's negative result</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>The follow-up brief searched m_collision_bg_wall.c_inc (construction) and concluded AttributeWall_Special is not an upstream name. Wrong file: the function is mCoBG_Distance2Reverse_AttributeWall_Special at m_collision_bg.c:970 (collision resolution) - exactly where the brief said to look next. Already ported in the previous commit; no code change needed.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md correction note.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>High - symbol located in current source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AttributeWall_Special: structural WHY (no WallBounds)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>mCoBG_unit_vec_info_c (m_collision_bg.c:27): start/end, wall_bounds (per-endpoint top/btm), normal, normal_angle, wall_name, regist_p, atr_wall. Ordinary walls populate wall_bounds via JudgeTopAndSet. Attribute walls never do: MakeForbidVectorData (attrs 27-62 via forbid_vector_idx/make_vector_table) and MakeCircleDefenceWall (column pairs) set atr_wall=TRUE with no wall_bounds assignment. This is WHY the attribute path has no height gate - there are no bounds to test. Confirms the brief's structural model.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>endpoint_circle.rs: #[repr(C)] WallVecInfo + WallBounds (verbatim layout) with docs. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4211,6 +4211,50 @@
       <c r="D153" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Height-input trace: exact dataflow (static, from source)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>old_ground_y = last_world_position.y + ground_dist (m_collision_bg.c:1829). Normal player-special: height.top = wall_bounds.start_top/end_top - DISCRETE per-endpoint selection, NO interpolation; gate (old_ground_y-5)+3&lt;=top; radius used ONLY horizontally. Attribute player-special: ZERO height inputs - purely horizontal decision. Non-player normal path: RoughCheckWallHeight ((bot_y+3)&lt;=start_top||end_top) + CheckHeightExactly which DOES interpolate via GetWallHeight, except moving walls (regist_p!=NULL) using end bounds directly. The atr_wall branch is in GetWallKind (dispatch), not in the collision fn. A Dolphin session would only confirm this; it cannot run here (no image/emulator).</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>endpoint_circle.rs: rough_check_wall_height, old_ground_y + tests. cargo check clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>High - traced verbatim from source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Height-input trace: scope</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Answers the brief's Traces 1-5 statically: (1) atr_wall consumed at GetWallKind dispatch; (2) normal-path FPR-equivalent inputs are old_ground_y and the endpoint tops; (3) actor vertical input is last-frame Y + ground_dist (feet-ish reference, not center); (4) radius never enters the vertical gate; (5) player path does NOT interpolate, non-player path does. Remaining: live Dolphin confirmation needs Philip's machine + game image.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 154-155.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>High - source-verified; live-trace pending.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4255,50 @@
       <c r="D155" t="inlineStr">
         <is>
           <t>High - source-verified; live-trace pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Check45Angle: boolean predicate, not a 4-way classifier</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>mCoBG_Check45Angle (m_collision_bg.c:641) is a boolean: ABS(a1-a0)&lt;=8192 (45 deg) || &gt;=57343 (0xDFFF=(u16)(-8193), the wraparound catcher - verbatim off-by-one accepts circular distance up to 8193 ticks). The FRONT/RIGHT/LEFT/BACK classification is the CALLER's else-if chain (mCoBG_SearchColOwnPart): FRONT=Check45Angle(wall+180deg-1tick, actor), RIGHT=wall-90deg, LEFT=wall+90deg, BACK=wall, priority FRONT&gt;RIGHT&gt;LEFT&gt;BACK. Flags to hit_wall/hit_attribute_wall by wall type. Resolves the brief's open question: FRONT = actor faces anti-parallel to the wall normal within 45 deg.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>wall_hit_dir.rs: hit_flag bits, tick consts, check_45_angle (verbatim), search_col_own_part (wrapping rotations), walls_opposing (+/-3 ticks of 180deg), walls_close_angle (&lt;12288 = 67.5deg). C ABI: pc_check_45_angle, pc_hit_wall_dir. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Check45Angle: remaining gaps</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>RegistWallCount's normal-averaging (sin/cos/atan tables) not ported as a kernel - only the probe is modeled. The in_front_wall_angle_y / unk_flag4 bookkeeping and the full MakePartDirectHitWallFlag loop remain C-side. No C callers rewired. New tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 156-157.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4299,6 +4299,50 @@
       <c r="D157" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Line-vs-column sweep: LineWallCheck_Column</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>mCoBG_LineWallCheck_Column (m_collision_bg_column.c_inc:454) verbatim: swept movement vs cylinder columns; XZ circle-line via the already-ported vector-form intersection; nearer intersection wins (strict &lt;); per-axis segment bounds; mult=(len_xz-sqrt(d_sq))/len_xz; rewind scales full XYZ vec_end_start (Y truncated proportionally); accepted iff end.y+rev.y&lt;=col.height; no actor radius; start-inside -&gt; no sweep. F32_IS_ZERO is |v|&lt;0.008 (not exact zero). The tmp_end/reverse per-column accumulation is DEAD CODE (reverse reset each iter, return on accept) - documented, implemented as observable behavior.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: f32_is_zero, Column, line_wall_check_column_one/_column. C ABI: pc_line_wall_check_column_one. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>High - verified verbatim against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Line-vs-column sweep: LineGroundCheck_Column + gaps</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Complementary mCoBG_LineGroundCheck_Column ported: downward plane-crossing gate (start.y&gt;h &amp;&amp; end.y&lt;h), mult=(h-end.y)/(start.y-end.y), verbatim early-out (FALSE immediately when Y gate passes but Y delta ~zero, skipping later columns); static reverse0 is zero-initialized despite the @BUG comment. Different primitive from wall vectors (no normal_angle/WallBounds/atr_wall). Remaining: ColumnCheck_NormalWall / OldOnGround_AttrWall variants, no C callers rewired. New tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: line_ground_check_column_one/_column. C ABI: pc_line_ground_check_column_one. DOCUMENTATION.md section; workbook rows 158-159.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4341,6 +4341,50 @@
         </is>
       </c>
       <c r="D159" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Column sweep follow-up: brief verification + corrections</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>The deeper brief re-derived LineWallCheck_Column - matches the port. Corrections: brief point 23 (cross-column correction carry) is wrong - reverse is reset to zero each iteration and the fn returns on first accept, so tmp_end always equals end_pos (dead code, as documented). The proposed 'next step' (PlaneXZ root ordering) was already resolved: it delegates to the vector-form intersection, cross0=t0=(-b+root)/2a.</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md note; no code change to the sweep kernels.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Column sweep follow-up: column data table</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>mCoBG_MakeOneColumnCollisionData (column.c_inc:136) verbatim: hole (19/0, atr_wall=TRUE, old_on_ground only), small/med/large/full tree (19/30/40/60/80), stump (10 or 18 / 30), rock (19/31.5), mailbox (15/50), sign (19/45), reserve signboard (10/45), flag (19/160). XZ = unit center; pos.y = terrain-center Y at own unit; height = pos.y + object height (holes: height=pos.y). Skips actor's own unit; 16-column cap. IS_ITEM_* ID lists not ported (game data).</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: ColumnKind, column_spec, column_top_height, COLUMN_MAX. cargo check clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4385,6 +4385,50 @@
         </is>
       </c>
       <c r="D161" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Column-derived ground height: GetBGHeight_Column</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>mCoBG_GetBGHeight_Column (column.c_inc:444): one column from the unit's foreground object (old_on_ground=FALSE so holes rejected); XZ footprint test with the exact recovered body (dx²+dz²&lt;=r², XZ only, query Y irrelevant); returns col.height or 0.0 sentinel. Column height is absolute world Y (unit-center terrain Y + object height) - a tree on a slope is a flat horizontal cap.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: get_bg_height_column. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Column-derived ground height: selection + actor adjustment</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>GetBGHeight_NormalColumn (m_collision_bg.c:1689): ground=max(normal, column); ties go to the column (strict &gt;); column win -&gt; zero ground angle (flat cap). Directed-unit exclusion forces column to 0.0. AdjustActorY ground branch: ground_y&gt;=foot_y -&gt; feet exactly on ground, on_ground=TRUE - no separate 'on object' state. Asymmetries: wall uses range+radius vs ground uses raw radius on actor center; ground checks one unit's object vs wall scans 16 columns over the neighborhood. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: get_bg_height_normal_column, adjust_actor_y_ground. C ABI: pc_column_ground_select. DOCUMENTATION.md section; workbook rows 162-163.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4429,6 +4429,50 @@
         </is>
       </c>
       <c r="D163" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Directed-unit suppression: lifecycle + two layers</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>mCoBG_BgCheckControll_RemoveDirectedUnitColumn (m_collision_bg.c:1899): caller passes (ux,uz) -&gt; stored in l_ActorInf._68/_6C by MakeActorInf -&gt; honored by BOTH the wall-column builder (line 1242, MakeOneColumnCollisionData returns FALSE) and the ground query (line 1695, column forced to 0.0) -&gt; reset to (-1,-1) at end. Ordinary BgCheckControll passes (-1,-1). Terminology: NOT 'center unit always ignored' - arbitrary directed unit per check; only center-unit suppression when the caller passes the actor's center unit.</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: DirectedSuppression (none/of/reset/is_excluded). cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>KeepH height family: column anchor, AddColumn, gap, layers, 3-way query</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GetBgY_OnlyCenter_FromWpos2 (bg_info.c_inc:73) = UtKeepH*10+BaseHeight-ground_dist: column bases AND GetLayer use KeepH, not collision-&gt;data.center. Wpos2BgUtCenterHeight_AddColumn (bg_info:59): column top if present else center*10+Base. GetBgHeightGapBetweenNowDefault = AddColumn-FromWpos2; ExistHeightGap = (int)gap!=0 (truncation). Height2GetLayer: &lt;100 L0, &lt;220 L1 (3-step), else L2/L1. GetBgY_AngleS_FromWpos (bg_info:21): max(normal,column,moveBG)-dist with normal winning ties (&gt;=) - different from actor path's strict &gt;; no directed suppression. Directed-API callers untraced (open).</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>column_sweep.rs: bg_y_only_center_from_wpos2, wpos2bg_ut_center_height_add_column, bg_height_gap_between_now_default, exist_height_gap_keep_and_now, layer+height2get_layer, bg_y_angles_from_wpos_select. DOCUMENTATION.md section; workbook rows 164-165. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4475,6 +4475,50 @@
       <c r="D165" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Attribute action-policy table: l_attribute_action_info[64]</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Table generated verbatim from bg_info.c_inc:188 (macro-decoded). Raw 6-bit unit_attribute -&gt; policy byte: bits 0-2 plant (only 0/2/4/7 ever emitted; PLANT1/3 enum-only), bit 3 placement, bit 4 NPC. Consumers: CheckPlace_OrgAttr (bit 3, no mask), Attr2CheckPlaceNpc (bit 4, attr&amp;0x3F mask), Attribute2CheckPlant (FG-field gate; attr 63 -&gt; +Z neighbor redirect + recurse; KILL-&gt;-1), Attr2CheckPoorGround (@unused: poor iff plant in {KILL,PLANT0}). CORRECTION to brief: river-bank asymmetry is attr 62 (NE bank, 0x17), not 61.</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>attribute_action.rs: ATTRIBUTE_ACTION_INFO verbatim, plant/bit consts, attribute_action_info, check_place_org_attr, attr2check_place_npc, attr2check_poor_ground, attribute2check_plant, change2poor_attr. C ABI: pc_check_place_attr, pc_check_npc_attr, pc_check_plant_attr. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Attribute action-policy table: architecture + gaps</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Change2PoorAttr (rewrite.c_inc:159): GRASS0/1-&gt;GRASS2, SOIL0/1-&gt;SOIL2, moving terrain into the PLANT0 policy class. Architecture: action table keyed by RAW collision attribute, independent of Wpos2Attribute() contextual translation; never drives collision geometry or columns. Gaps: field-type gate + attr-63 neighbor redirect need field/collision access (caller-side); CheckPlant/CheckPlace/Wpos2CheckNpc gameplay callers untraced; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 166-167.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4519,6 +4519,50 @@
       <c r="D167" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Water translation deep dive: table re-verified</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>mCoBG_unit_attribute_water_info[64] (m_collision_bg.c:1609) re-verified entry-by-entry against the USA Rev. 0 source; the earlier verbatim port (commit ab41f9a) matches exactly, incl. 55-58 = GRASS0. Water attributes 12-21 survive; wood-bridge corners 27-30 and river banks 39-42 map to river corners NW/SW/SE/NE; everything else -&gt; GRASS0 (incl. SEA=24, waves, slopes). SearchWaterAttributeFrom4Area is a pure raw-attribute lookup (no field/wave/area logic).</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>No code change needed for the table; documented in DOCUMENTATION.md.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>High - source-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Water translation deep dive: GroundCheck branch structure</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Bridge path (attr 63 or 27-62): search runs only when !attribute_wall &amp;&amp; old_in_water &amp;&amp; attr in 27-35; first water neighbor in mask direction order wins (result.unit_attribute = next_unit_attr, water_flag, water_y = GetWaterHeight_File). FIXED earlier port: search-ran-but-no-water leaves result.unit_attribute UNASSIGNED (stale) - the Wpos2Attribute fallback happens only when the search is SKIPPED. Non-bridge path: WATER..RIVER_NE -&gt; water_y = 20 + bg height; SEA -&gt; water_y = 20; else Wpos2Attribute. The brief's SEA/37/38 'dead branch' is a GAFU01 version delta - USA Rev. 0 has no such branch in the bridge loop.</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>bridge_water_search -&gt; BridgeWaterSearch::{Skipped, NoWater, Found}; pc_bridge_water_search returns 0xFF/0xFE/attr. cargo check clean. Tests updated, NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>High - corrected a real fidelity bug; GAFU01 caveat recorded.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:K171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4563,6 +4563,50 @@
       <c r="D169" t="inlineStr">
         <is>
           <t>High - corrected a real fidelity bug; GAFU01 caveat recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Wpos2Attribute: effective-terrain interpreter</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>mCoBG_Wpos2Attribute (m_collision_bg.c:1517) verified branch-by-branch: HOLE-&gt;FLOOR/GRASS2 (cant_dig FALSE); 63-&gt;SearchAttribute area-neighbor recursion (cant_dig inherited); 25-26 dynamic wave (cant_dig FALSE); 27-62 cant_dig=TRUE then 43-62-&gt;FLOOR/GRASS2, 27-31 woodb_water_info[area], 32-35 STONE, 36-38 dynamic wave, 39-42 grass3_water_info[area] with the (mapped&lt;=GRASS3 &amp;&amp; non-FG)?FLOOR:mapped gate; default (attr&lt;=GRASS3 &amp;&amp; non-FG)?FLOOR:attr. Wave classifier: pos_rate=1.1*dist_point/dist, &lt;=0 SEA, &gt;=1.1 SAND, &lt;=phase-rate WAVE else SAND. F32_IS_ZERO=fabsf&lt;0.008 (types.h:146). woodb_water_info row 5 is dead in the source (only rows 0-4 indexed).</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>wpos2attribute.rs: verbatim tables, f32_is_zero, cross_line_and_perpendicular, check_wave_atr_detail, get_wave_dynamic_attr, wpos2attribute_step; attr-63 redirect as redirect:Some(area) for the map-owning caller. C ABI: pc_wpos2attribute_step. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Wpos2Attribute: architecture + gaps</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Key architectural finding confirmed: cant_dig is a raw-attribute-class property (27-62), never derived from the returned effective attribute - a tile can report GRASS2 while undiggable. Wave phase is a global (mCoBG_wave_cos via WaveCos2BgCheck). Gaps: full GroundCheck integration (water_y, AdjustActorY) not ported; CheckWaterAttribute/_OutOfSea classifiers noted, not ported; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 170-171.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K171"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4605,6 +4605,50 @@
         </is>
       </c>
       <c r="D171" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SearchAttribute + slate ground height</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>mCoBG_SearchAttribute (m_collision_bg.c:495) is three lines: y=0, PlussDirectOffset, recurse into Wpos2Attribute - the 'search' is one cardinal neighbor step, local position preserved (no center snapping). PlussDirectOffset guard: direct in 0..8 else no write. SOURCE QUIRK: unit_offset index 5 ('NE') = (-40,+40) and index 7 ('SW') = (+40,-40), transposed vs geometric intuition - preserved verbatim; the attr-63 path only uses indices 0-3 so it is unaffected. GetBGHeight_Normal_SlateGround: orientation from single comparison top_left != bot_right (UP else DOWN); GetAreaYSlatingUnit area-&gt;corner map with the UP-invalid-area fallthrough into the DOWN switch; corner*10 + base height; zeroes caller angle. Dispatch via get_bg_y_normal_proc[slate_flag].</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>wpos2attribute.rs: UNIT_OFFSETS verbatim, pluss_direct_offset, search_attribute_redirect, slate_ground_orientation, area_y_slating_unit, slate_ground_height. C ABI: pc_pluss_direct_offset, pc_search_attribute_redirect, pc_slate_ground_height. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SearchAttribute: architecture + gaps</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Confirmed: slate_flag (physical shape) and unit_attribute==63 (semantic proxy) are independent bitfields; GroundCheck's bridge-water branch needs attr 27-35 so raw 63 never enters it; 63-&gt;bridge-&gt;river/wood composition resolves at the same relative point via the preserved local offset. Gaps: full GroundCheck orchestration (water_y, AdjustActorY, MakeJumpFlag) not ported; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 172-173.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4651,6 +4651,50 @@
       <c r="D173" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Cliff/slate classification: exact symbols recovered</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CORRECTION to brief: mCoBG_CheckCliffAttr and mCoBG_Wpos2CheckSlateCol EXIST verbatim in m_collision_bg_info.c_inc (USA:1040/1088; AUS identical) - the brief searched the wrong files. CheckCliffAttr: TRUE iff attr in 47-54 or 55-58 (purely semantic; used by talk camera m_camera2.c:1124). Wpos2CheckSlateCol(pos, check_attr): TRUE if slate_flag; else if check_attr, TRUE iff attr in {27,28,29,30,37,38,39,40,41,42,55,56,57,58} - note exclusions: bridge center 31, wave_s 36, cliff 47-54, slope 63. Used by snowman with check_attr=FALSE (ac_snowman.c:679) as a pure slate_flag test. WoodSoundEffect (same file): WOOD or 27-31 incl. center.</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>slate_classify.rs: check_cliff_attr, wpos2check_slate_col + SLATE_COL_ATTRS, wood_sound_effect, slate_ground_normal, slate_area_polygon_y. C ABI: pc_check_cliff_attr, pc_wpos2check_slate_col, pc_wood_sound_effect, pc_slate_area_polygon_y. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>High - exact source recovered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Cliff/slate classification: geometry + gaps</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GetAreaPolygon slate branch (line.c_inc:119): area triangle built, then vertex Y equalized toward the lower side per area. SOURCE BUG preserved (USA Rev. 0 unfixed): AREA_W with leftUp&gt;leftDown assigns v0-&gt;y=v1-&gt;y twice (should be v2-&gt;y=v1-&gt;y per source comment); net: v0=v1=leftDown, v2 stays center. GetBgNorm_FromWpos (info.c_inc:81): slate_flag==1 -&gt; straight-up normal (0,100,0); flat non-slate also (0,100,0). Gaps: non-slate GetAreaPolygon branch and GetNormTriangle not ported; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 174-175.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>High - bug preserved deliberately; scope delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4695,6 +4695,50 @@
       <c r="D175" t="inlineStr">
         <is>
           <t>High - bug preserved deliberately; scope delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Talk-request driver: symbol family recovered</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CORRECTION to brief: talk_request_proc EXISTS - it is a per-NPC strategy hook typedef void (*aNPC_TALK_REQUEST_PROC)(ACTOR*, GAME*) (ac_npc.h:254), defaulted from aNPC_ct_data_c (ac_npc_ct.c_inc:315), swappable at runtime. Driver aNPC_talk_request_event_npc: active non-listenable SPEAK/SPEECH/TALK demo -&gt; setup_talk_start directly; else submenu idle (WAIT+timer 0) -&gt; call hook or mDemo_Request(TYPE_TALK) if none; else nothing. Hooks: aCD0_norm_talk_request (TYPE_TALK + msg_base[looks]+RANDOM(3)+term offset), aCD0_force_talk_request (TYPE_SPEAK), quest clip bool gate (aNPC_normal_talk_request), none_proc1 = no-op.</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>talk_request.rs: TalkRequestAction/Inputs, talk_request_dispatch (verbatim), normal_talk_request_gate, countdown_norm_msg_no, TalkSession begin/end. C ABI: pc_talk_request_dispatch, pc_normal_talk_request_gate. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>High - exact source recovered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Talk-request driver: session lifecycle + gaps</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>setup_talk_start: palActor=player, face player iff turn==NORMAL, talk_condition=START, demo flags saved. setup_talk_end: palActor=NULL, ignore timer=600 (if &gt;=0), talk_condition=NONE, force-call cleared, feel=0xFF, demo flags restored. The message flow itself is owned by the demo system (mDemo_Request), only triggered here. Gaps: demo system internals, message flow, choice handling not yet researched; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 176-177.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K177"/>
+  <dimension ref="A1:K178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4739,6 +4739,28 @@
       <c r="D177" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Authorized test run #8</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Philip said 'Run the tests'. cargo test --lib: 255 passed, 0 failed. Two test-only fixes in wall_hit_dir.rs (implementation untouched): (1) i16-unrepresentable literals 57343/-57343 replaced with equivalent in-range values (d=65535 via (-32768, 32767); d=-57343 via (24576, -32767)); (2) the 'no sector' expectation was wrong - the four 45-degree probes tile the circle completely (wraparound clause closes the 1-tick seam), so None is unreachable; actor=10000 is genuinely LEFT, seam tick -24577 is FRONT via the verbatim off-by-one. This clears all tests written since run #7 (wall_hit_dir, column_sweep, attribute_action, wpos2attribute, slate_classify, talk_request).</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>wall_hit_dir.rs test-only fixes; 255/255 pass.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>High - authorized full run.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K178"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4761,6 +4761,50 @@
       <c r="D178" t="inlineStr">
         <is>
           <t>High - authorized full run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Talk topic taxonomy: tables + chooser</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>aQMgr_talk_normal_select_talk (ac_quest_talk_normal_init.c:2145) verified: first-job hint priority (0x0841+hint_type+looks*10, hint_type=hint_count&amp;0x7F); HAPPY-&gt;KI tree, else normal/game tree. Prob tables verbatim: KI {40,30,10,10,10}, normal-1 {70,30}, normal-2 {15,35,35,15}, trade {25,25,25,25}, normal-3 {49,17,17,17}, game {40,60}. Chooser builds 100-entry table, shuffles 30x, picks one - weights exact. All 19 message base tables verified verbatim; every leaf is table[looks]+variant (looks=personality 0-5).</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>talk_topics.rs: verbatim prob/base tables, category enums, decide_idx_prob_table (caller RNG closure), select_talk_kind, leaf formula kernels. C ABI: pc_select_talk_kind, pc_fj_hint_msg_no, pc_weather_time_msg_no. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Talk topic taxonomy: leaf formulas + gaps</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Leaf formulas verified: weather/time base+time*6+weather*2+RANDOM(2) (SAKURA-&gt;CLEAR); normal-3 weather base+weather*5+RANDOM(5|4)+ofs with man-kind adjustment (4,1); season base+add_table[month-1] (add_table={10,11,0..9}); letter base+mail_strategy (not random); memory base+idx*2+(letter?0:1), +8 fallback. Verified fallbacks: KI -1-&gt;KI normal; normal-2 -1-&gt;normal-3. KI money gate: pocket AND wallet&gt;=3000. @BUGs: ret_msg uninitialized in 4 deciders - port uses -1. Gaps: deeper fallback edges, game/event subtree, island taxonomy, greeting layer, message-database semantics; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 179-180.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4803,6 +4803,50 @@
         </is>
       </c>
       <c r="D180" t="inlineStr">
+        <is>
+          <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Force-call state machine</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>aNPC_force_call_req_proc (ac_npc_talk.c_inc:1): generic clip callback, 3 gates (flag==NONE, talk_condition==NONE, mDemo_CAN_ACTOR_TALK); caller supplies msg (e.g. soccer 0x0D8B+looks). aNPC_force_talk_request: stored msg_no -&gt; SPEAK demo; else friendship path needs friendship&gt;128, SEARCH/PLAYER, timer&lt;=0, XZ&lt;80, |Y|&lt;60. chk_avoid_and_search needs same block; &lt;0 AVOID, &gt;128 SEARCH. love_player: sex mismatch + NONE + timer&lt;=0 raises REQUEST (msg_no stays -1); RUN&gt;3u, WALK&gt;1.5u. Auto greeting: mainland 0x075F+looks*3+RANDOM(3), island 0x34AC+looks*3+RANDOM(3). Lifecycle: install-&gt;SET; SET+SPEAK-&gt;START; talk end-&gt;timer=300 (~5s), flag NONE; REQUEST failure falls back to normal talk.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>force_call.rs: force_call/friendship enums, demo_can_actor_talk, force_call_req_proc, chk_avoid_and_search, love_player_request_gate/pace, force_talk_request+ForceTalkPath, auto_greeting_msg_no, set_talk_info_force_call, talk_end_force_call_reset. C ABI: pc_force_call_req_proc, pc_force_talk_request, pc_auto_greeting_msg_no. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Force-call: architecture + gaps</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Three conversation lanes now established: player-initiated quest-manager talk (topic taxonomy), NPC-initiated force calls (this module), event/special-NPC talk. Force calls bypass the normal topic selector entirely. Gap: whether SCENE_NPC_HOUSE adds a house-specific trigger beyond the generic friendship path is unproven; no C callers rewired. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; workbook rows 181-182.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K182"/>
+  <dimension ref="A1:K184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4849,6 +4849,50 @@
       <c r="D182" t="inlineStr">
         <is>
           <t>High - scope honestly delimited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>NPC AI: daily schedules</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>m_npc_schedule.c: six hard-coded tables indexed by looks (girl/ko_girl/boy/sport_man/grim_man/naniwa_lady) ported verbatim. manager_sub: walk until end_time&gt;now_sec -&gt; saved_type; forced_timer&gt;0 -&gt; current=forced_type w/ decrement, else current=saved. First Job or Halloween active -&gt; ALL animals FIELD (sub0). check_chg_schedule: step match + type change + talk_condition==NONE. FIELD steps LEAVE_HOUSE/WANDER/IN_BLOCK/PITFALL; sleep think has only ENTRANCE|OBSTACLE|FATIGUE interrupts; interrupted sleeper forces FIELD (or IN_HOUSE at home) for 7200 frames.</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>npc_ai.rs: SCHEDULE_TABLES, sched enum, schedule_manager_sub, global_schedule_override, check_chg_schedule, field_step, sleep_force_schedule_type. C ABI: pc_schedule_step, pc_schedule_global_override. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>NPC AI: interrupts, wander, reactions, talk throttle</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Interrupt order: talk start, pitfall, hands, uzai-&gt;REACT_TOOL, entrance, moving chain (clap, fatigue, turn, obstacle, ball, insect/fish), friendship LAST; umbrella runs unconditionally before the chain. Wander: verbatim border tables per looks; fatigue/SLEEPY-&gt;WAIT; WALK_WANDER rng&gt;5; RUN downgraded to WALK when forced into FIELD. Uzai: max_uzai_cross={600,240}, max_uzai_tool={3,1} indexed by cross==1. Talk throttle: temperament {unlock_timer, over_impatient_num, talk_num_max} keyed by LOOKS not mood (brief's Mood column + swapped columns corrected); NORMAL looks = 4000/12/15; TalkEndMove 1000-frame timer. NPC-NPC greeting: relation +8 both ways, both HAPPY (catchphrase copy bonus).</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>npc_ai.rs: Interrupt order, WANDER_BORDERS + wander_decide_next, uzai_trigger, TALK_TEMPER + TalkThrottle, GREETING_RELATION_BUMP. C ABI: pc_wander_decide_next, pc_uzai_trigger, pc_talk_patience. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp; three brief corrections documented.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K184"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4893,6 +4893,50 @@
       <c r="D184" t="inlineStr">
         <is>
           <t>High - verified against local decomp; three brief corrections documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Player action: index enum + request arbitration</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>mPlayer_INDEX_* (m_player.h): 121 entries, ported in exact C order. No SWIM / no general CLIMB confirmed: water = WADE/WADE_SNOWBALL, climbing = CLIMBUP_PITFALL only. Request model: Player_actor_request_main_index stores index+priority; admissible only when priority - requested_priority &gt; 0 (plus 2 cancel/reset gates); 45 priority levels.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>player_action.rs: index enum, check_request_main_priority, request_admissible. C ABI: pc_player_request_priority_delta. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Player action: scoop family + wade + pitfall climb</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>DIG_SCOOP: frames 14/15/16 DIG_HOLE 0/1/2, 22 DIG_SCOOP (arg 0 / 3 for GET); stump variant frame 42; hole registration at mod+20 (decal r=19, arg 12). GET_SCOOP: inventory txn in setup; scale &lt;=21-&gt;0, 21-27 lerp, &gt;=27-&gt;0.01; 0x3F-&gt;PUTAWAY, 0x40-&gt;PUTIN (prio 21). FILL_SCOOP: hole out at 18+mod; impacts 13/19/25 args 3/4/5; final at 40. Check_DigScoop = DIG/REFLECT/GET/FILL/PUTIN (not AIR/PUTAWAY). WADE: 18.00001f, 36-frame accel/brake (1.1999999/34.8), camera (9, 36.0), then WALK. CLIMBUP: pit_exit in setup; DERU1/DERU2 by umbrella.</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>player_action.rs: dig/fill/get frame events, check_dig_scoop, wade consts + wade_finished, climbup_pitfall_anim. C ABI: pc_dig_scoop_frame_event, pc_fill_scoop_frame_event, pc_get_scoop_continuation, pc_check_dig_scoop, pc_wade_finished, pc_climbup_pitfall_anim. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K186"/>
+  <dimension ref="A1:K188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4935,6 +4935,50 @@
         </is>
       </c>
       <c r="D186" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Player tools: axe family</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SWING_AXE: frame 10 whoosh; 15 = hit (effect at offset (-7,20,24) rotated; tree_cutcount_check -&gt; &lt;=0 stump via bg_item_fg_sub else shake; fruit drop unless bee tree; bee tree -&gt; bee_counter=5.0; AXE_CUT sound; axe-damage bookkeeping); 16.5 bee attack status; &gt;=17 shock-or-WALK(prio 1). REFLECT_AXE settles 30.5/31, AIR_AXE 35.5/36. Semantic CHOP_TREE/CHOP_PALM_TREE. BROKEN_AXE has reflect/swing request variants.</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>player_tools.rs: swing_axe_frame_event, AXE_HIT_OFFSET, tree_hit_outcome, AXE_BEE_COUNTER, settle frames. C ABI: pc_swing_axe_frame_event, pc_tree_hit_outcome. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Player tools: net + rod families</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Net: READY/READY_WALK_NET -&gt; SWING_NET prio 22. Catch = capsule top_col-&gt;bot_col, len 50 / 60 gold; insects self-register. SWING outcome: check_type 2 -&gt; PULL_NET prio 26 (+sound/vibration); 0 -&gt; STOP_NET prio 26 (+NPC UZAI). PULL_NET demo msg 0xA2C base. Rod: CAST_ROD stroke sound frame 20; RELAX case 5 -&gt; VIB_ROD prio 26; case 6 -&gt; COLLECT_ROD prio 26; VIB_ROD nonzero status -&gt; FLY_ROD prio 27.</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>player_tools.rs: net_catch_length, net_swing_outcome, tool_priority, PULL_NET_MSG_BASE, relax_rod_case, vib_rod_hook, cast_rod_frame_event. C ABI: pc_net_catch_length, pc_net_swing_outcome, pc_relax_rod_case, pc_vib_rod_hook. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K188"/>
+  <dimension ref="A1:K190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4979,6 +4979,50 @@
         </is>
       </c>
       <c r="D188" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Field gen: step mode + rejection sampling</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>mRF_GetRandomStepMode: rng(100)&lt;15 -&gt; 15% three-level / 85% two-level. mRF_MakePerfectBit: 9 bits (SLOPE_LEFT/RIGHT, BRIDGE_UPPER/LOWER, SHRINE, POLICE, MUSEUM, POOL, NEEDLEWORK) = 0x1FF; accept iff perfect_bit == (perfect_bit &amp; bit) — whole-town rejection sampling.</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>field_gen.rs: step_mode, feat bits, perfect_bit, generation_accepted. C ABI: pc_field_step_mode, pc_field_generation_accepted. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Field gen: cliff/river tracer tables + acre height</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Cliff: 7 shape classes, l_cliff_next_direct={E,N,N,E,S,S,E}; successor tables verbatim; start tables A/B/C with rows {0,1}-&gt;A,2-&gt;B,3-&gt;C. River: start X {1,2,4,5}; successor tables verbatim; l_river_next_direct={S,E,W,E,S,W,S}. l_base_blocks 7x10 verbatim. mRF_GetSystemBlockInfo shape-bit mapping verbatim; mRF_GetBlockBase verbatim (per-column z=9..0 scan, ++ on HORIZONTAL/TOP_RIGHT/TOP_LEFT or border transitions). Conversions: slope/pool/bridge offsets verbatim. CheckFieldStep3 = top-left height==3. @BUG in mRF_BgName2RandomConbiNo (GetRandom(0)) documented.</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>field_gen.rs: CLIFF_NEXT_DIRECT/SHAPES, cliff_start_table, RIVER_START_X, RIVER_NEXT_SHAPES/DIRECT, BASE_BLOCKS, block_cliff_shape_bits, acre_height_table, slope/pool/bridge conversions, is_field_step3. C ABI: pc_cliff_next_direct, pc_river_next_direct, pc_acre_height_table, pc_slope/pool/bridge_for_*. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K190"/>
+  <dimension ref="A1:K192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5023,6 +5023,50 @@
         </is>
       </c>
       <c r="D190" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Villager selection + house lots: architecture</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Init order (m_start_data_init.c): mFM_InitFgCombiSaveData @205 -&gt; mNpc_InitNpcAllInfo @225 -&gt; mNpc_Grow -&gt; mNpc_InitNpcData. Terrain exists before villagers; no villager-driven carving. Anmhome_c = block_x/block_z/ut_x/ut_z. SIGN00-SIGN20 (21), mNT_IS_RESERVE. Reserved-list scan covers 7680 FG cells. SetNpcHome: 30-swap lot shuffle, one-to-one assignment, ut_z+1 offset. BuildHouse: 3x3 footprint (ut_d verbatim), house/signboard/RSV_NO pattern, FG layer only.</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>villager_home.rs: HomeInfo, reservation consts, collect_reserved_lots, make_rand_table, assign_homes, HOUSE_FOOTPRINT, house_footprint_in_bounds. C ABI: pc_is_reserve_marker, pc_house_footprint_in_bounds. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Villager selection: identity + growth algorithms</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DecideLivingNpcMax: shuffle NPC defs, STARTER perm + uncovered looks category, count=6. Growth: prob table {40..100} by field rank, RANDOM(100)&lt;prob; gates = pop&lt;15, &gt;=1 day, player from town, talked to all. GetMinLooks: least-populated looks with eligible unseen NPCs (tie bitfield). Candidates: not present + not appeared + STARTER/MOVE_IN, uniform choice.</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>villager_home.rs: decide_living_npc_max, GROW_PROB, check_grow_field_rank, check_grow, min_looks_bitfield, grow_candidate_eligible. C ABI: pc_check_grow_field_rank, pc_check_grow, pc_min_looks_bitfield. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K192"/>
+  <dimension ref="A1:K194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5069,6 +5069,50 @@
       <c r="D192" t="inlineStr">
         <is>
           <t>High - verified against local decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FG data: binary format + parser</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>KEY FINDING: SIGN locations live in fgdata.bin inside forest_1st.arc (game disc), NOT in the decomp source. Format: per record u16 fg_id BE + 256x u16 items BE (z,x row-major) + 4 haniwa bytes = 518 bytes; file is big-endian (PC port byte-swaps on load). SIGN00=0x5810..SIGN20=0x5824 (STRUCTURE_START=0x5800). Parser + SIGN extractor implemented; join logic ready.</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>fg_data.rs: FG_RECORD_SIZE, SIGN_FIRST/LAST, FgRecord, parse_fg_records, sign_locations, build_fg_index. C ABI: pc_fg_parse_count, pc_fg_sign_count. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>High - format verified against m_field_make.h/jsyswrap.cpp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FG data: combination statistics</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>data_combi.c: 368 combinations, 267 distinct FG types (script-derived). Variant counts: FLAT 10 (GRD_S_F_1_2F, GRD_S_F_2..10), BEACH 10, RIVER_SOUTH/EAST/WEST 4, CLIFF_HORIZONTAL 5, TRACKS_RIVER 5, border/ocean mostly FG_TYPE_EMPTY. FLAT's 10 variants are the prime house-lot candidates. OCEAN_5=97 corrected during verification.</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>fg_data.rs: COMBI_COUNTS, house_lot_candidates. cargo check clean. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>High - script-derived from source, not hand-counted.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K194"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5113,6 +5113,50 @@
       <c r="D194" t="inlineStr">
         <is>
           <t>High - script-derived from source, not hand-counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Scene system: architecture + interpreter</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>52 scene IDs -&gt; scene_word_data[52] pointer table -&gt; Scene_Word_u[] manifests -&gt; Scene_ct() walks 8-byte words to END, 11-entry Scene_Proc dispatch. Gameplay_Scene_Read is a selector, not a parser. Gameplay_Scene_Init: zero counts -&gt; 0xA000 exchange arena -&gt; light/door/common reset -&gt; Scene_ct -&gt; mSc_decide_exchange_bank. Manifests installed by pointer (no copy). FIELD_CT endian packing verified (TARGET_PC unpack logic). Scene_Proc_Sound is a stub; scene_data_status unresolved.</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>scene_table.rs: SCENE_NUM, SceneWordType, SceneWord, FieldCtParams + fieldct_unpack, EXCHANGE_ARENA_SIZE. C ABI: pc_fieldct_unpack. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>High - verified against m_play.c/m_scene.c/m_scene.h/m_scene_table.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Scene system: all 52 manifests + sound types</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>All 52 *_info[] manifests extracted programmatically from 51 src/data/scene/ files into a condensed table (sound, doors, arrange_ftr, arrange_room_ct, ctrl_actors, actors, obj_banks, FIELD_CT params). Findings: scenes 8/32 share field_tool_field_info (not 1:1); MY_ROOM_CT unused; museum_entrance has 4 doors; museum_insect 0xB000 disp; ARRANGE_FTR values 1/3/6/8/25/30/32/48; train/player-select draw types. mPl_SceneNo2SoundRoomType fully tabulated (script-verified: 1=MY_ROOM_S; 2=x9 scenes; 3=x8 scenes incl POLICE_BOX; 0 rest).</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>scene_table.rs: SCENE_MANIFESTS (52), SOUND_ROOM_TYPE (52), SCENE_STATUS_SIZE/TOTAL. C ABI: pc_scene_manifest, pc_scene_sound_room_type. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>High - tables machine-verified against source, not hand-transcribed.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K196"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5157,6 +5157,50 @@
       <c r="D196" t="inlineStr">
         <is>
           <t>High - tables machine-verified against source, not hand-transcribed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Weather/seasons/wind systems</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>18-term calendar (end dates; island forces term 7); set_season writes season/term/bgitem_profile/bgitem_bank. 20 weather terms, 10-unit rolls, outcome mapping incl thunder/sakura. @BUG confirmed: sakura probability reads snow field without BUGFIXES. Event weather override precedence (CLEAR/SNOW/SPORTS_FAIR), first-job rain clear, save byte intensity|(weather&lt;&lt;4). Wind: 5 terms, calm/normal/gusty percents, power ranges, Koinobori forces 135deg/power 1.0. Renewal boundary 6 AM.</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>weather_season.rs: CALENDAR_TERMS, term_idx, WEATHER_TERMS/TABLE, weather_term, weather_roll (bugfix flag), event_weather_override, save pack/unpack, WIND_TERMS/PERCENTS/POWER_RANGES, wind_term. C ABI: pc_term_idx, pc_weather_term, pc_weather_roll, pc_event_weather, pc_wind_term. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>High - verified against m_time.c/m_kankyo_weather.c_inc/m_kankyo.h/m_event.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Tool target resolvers (shovel/axe/net/rod)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>mPlib_Check_scoop_after: 8-neighbor angle-first selection, diagonal wall rejection + SQ(63.245553) cutoff, +/-63.245552 vertical, SQ(39) NPC exclusion. mFI_GetDigStatus: golden shovel DIG injection = area gate + RANDOM(10)==1 -&gt; GET_ITEM/ITM_MONEY_100 (0x2103). PUTIN_SCOOP: drop at entry, bury effect frame 18/25, golden demo at end. REFLECT_SCOOP frame 13: speed 4.8 + reversal, strike at 37fwd+2lat. Axe: +1/+3 damage, &gt;=9 advances one wear stage + counter reset. Net: capture after frame 6, sweep 50/60, radial 15/21. Rod: frame&gt;=10, 100-unit projection, 5 samples +/-10, &lt;60 height.</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>tool_resolvers.rs: scoop constants, dig_status, gold-shovel gate/injection, frame constants, axe_apply_damage, net_sweep_length/net_radial_tol, rod_sample_ok. C ABI: pc_gold_shovel_dig, pc_axe_apply_damage, pc_net_geometry, pc_rod_sample_ok. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>High - verified against m_player_lib.c/m_field_info.c/reflect_scoop/putin_scoop/m_player_common.c_inc/swing_net/ready_rod.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5201,6 +5201,50 @@
       <c r="D198" t="inlineStr">
         <is>
           <t>High - verified against m_player_lib.c/m_field_info.c/reflect_scoop/putin_scoop/m_player_common.c_inc/swing_net/ready_rod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Trace loops: frame/game/actor/collision ordering</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>graph_proc outer/inner loops; dt accumulation with 4-frame cap (speedhack multiplies). graph_main: input -&gt; game_main -&gt; draw -&gt; audio. game_main: draw_first -&gt; mTM_time -&gt; exec -&gt; mBGM_main. Game_play_move: CollisionCheck_OC -&gt; clear -&gt; Actor_info_call_actor (collision staged before actors). Actor loop: partitions x linked lists, 4 branches (ct_proc/DMA-fail/no-mv_proc/normal), player metrics, status clear. OC pairwise col1p+1 with dispatch table; OCC mco_work x table, cap 10.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>frame_loops.rs: DT_MAX_FRAMES, clamp_dt_frames, phase enums, actor_branch, OCC_WORK_CAP. C ABI: pc_clamp_dt_frames. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>High - verified against graph.c/game.c/m_play.c/m_actor.c/m_collision_obj.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Trace loops: line trace + NPC route + tool triangles</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Line trace: 3x3 unit ground trace (4 polygons/unit), moving-BG quads, FG column wall/ground traces, reverse accumulation (wall/wall-col/ground/ground-col summed), water = 19-21 band or underwater. Axe triangle: +31Y, 35 units, +/-8.0255deg; hit = TRIS_HIT flag. NPC route: avoid_direction cursor, FALSE = action complete. Four trace meanings separated.</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>frame_loops.rs: axe constants, LINE_TRACE_UNITS/AREAS, water_crossing, reverse_slot, npc_route_step. C ABI: pc_water_crossing, pc_npc_route_step. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>High - verified against m_collision_bg_line/column.c_inc, m_player_common.c_inc, ac_npc2_action.c_inc.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K200"/>
+  <dimension ref="A1:K202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5245,6 +5245,50 @@
       <c r="D200" t="inlineStr">
         <is>
           <t>High - verified against m_collision_bg_line/column.c_inc, m_player_common.c_inc, ac_npc2_action.c_inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Collision temporal lifecycle</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Frame: OC/OCC -&gt; clear (containers only) -&gt; actor consume -&gt; draw re-register. Two clear families: setOC-&gt;OCClear (clears COLLIDED/collided_actor/PLAYER_WAS_HIT/elem HIT); setOCC-&gt;OCCClear (clears collided_actor/DONT_UPDATE_POS/elem t). Flag values verified. Tool triangles: draw(N) -&gt; OCC(N+1) -&gt; consume(N+1), one frame delay. Multiple OCC hits: last collider wins. Status_c cleared per-actor separately.</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>collision_temporal.rs: flag constants, oc_clear_*/occ_clear_flags0, frame_phase, lifecycle simulation. C ABI: pc_oc_clear, pc_occ_clear_flags0, pc_tris_hit. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>High - verified against m_collision_obj.c/m_play.c/m_actor.c/m_player_common.c_inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TRIS_HIT anomaly (unresolved)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TRIS_HIT set in exactly one place (setOCC_HitInfo), read in two (axe/net); NO ~ClObj_FLAG2_TRIS_HIT anywhere in src/ or include/. After an OCC hit the next setOCC clears collided_actor but TRIS_HIT persists -&gt; hit=TRUE with hit_actor=NULL is reachable in current source. Flagged as decomp/retail question needing static.dol assembly comparison, NOT proven retail behavior.</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>collision_temporal.rs documents the anomaly; tris_hit_survives_setocc() returns true per current source. Tests NOT run (standing rule). DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Medium - source-verified absence of clear; retail behavior unproven.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K202"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5289,6 +5289,50 @@
       <c r="D202" t="inlineStr">
         <is>
           <t>Medium - source-verified absence of clear; retail behavior unproven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Albumin: river x cliff combination table</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>mRF_RiverAlbuminCliff: group-gated (CLIFF 15-21, RIVER 40-46), 7x7 table with 3 real rows + 4 all-NONE corner-river rows. 17 valid cells (7+5+5). Exact rows verified verbatim. Group ranges: RIVER_CLIFF_ANY 22..38, _1 22..28, _2 29..33, _3 34..38 (corrected from brief's 34..36).</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>albumin.rs: ALBUMIN table, river_albumin_cliff, group ranges, albumin_valid_count. C ABI: pc_river_albumin_cliff. cargo check clean.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c; enum values script-extracted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Albumin: merge semantics + trace legality</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>DecideRiverAlbuminCliff writes merged type into cliff_blocks; river without albumin copies as ordinary river; no river leaves unchanged. River tracer uses albumin as legality test: incompatible -&gt; return FALSE (whole attempt rejected). Step-3 bypasses. Combined types feed height calc + RIVER_CLIFF_ANY checks.</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>albumin.rs: decide_albumin_cell. C ABI: pc_decide_albumin_cell. DOCUMENTATION.md section added. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:K206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5333,6 +5333,50 @@
       <c r="D204" t="inlineStr">
         <is>
           <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Placement: pipeline + acceptance loop</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>9-bit acceptance loop (SLOPE_LEFT/RIGHT, BRIDGE_UPPER/LOWER, SHRINE, POLICE, MUSEUM, POOL, NEEDLEWORK); full pass order from mRF_MakeRandomField_ovl; player house (3,2) is a hard obstacle; step-mode 15% three-step. Placement = monotonic acre-type replacement.</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>placement.rs: grid dims, bit enum, PERFECT_BITS, is_step_three. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Placement: beach/bridge/slope/building/pond passes</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Beach z=6 FLAT-&gt;BEACH, RIVER_SOUTH-&gt;BEACH_RIVER, ocean borders. Bridges: 7 waterfall anchors, upper mandatory, lower conditional (offset 7), beach-mouth fallback. Slopes: contour split at river, SLOPE_HORIZONTAL+idx, one per side. Shrine/Police/Museum order+side prefs. Shop/Post railroad bx=1+R(2)/4+R(2). Wharf (5,6) PORT, needlework RANDOM(3)-th beach. Pond: pure rivers only, offset 29.</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>placement.rs: marin_cell, bridge_variant, lower_bridge_ok, slope_variant, pool_variant, is_pure_river, wharf/rail constants. C ABI: 5 entry points. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c; block ids script-extracted.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K206"/>
+  <dimension ref="A1:K208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5377,6 +5377,50 @@
       <c r="D206" t="inlineStr">
         <is>
           <t>High - verified against m_random_field_ovl.c; block ids script-extracted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Albumin geometry: 17 outputs -&gt; BG/FG assets</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>All 17 albumin types traced to data_combi_table entries (programmatic extraction). Primary BG: GRD_S_C*_R1/R2/R3 families; variants 1-3 per type. SelectBlock picks randomly among a type's variants. Brief's table matched exactly.</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>albumin_geometry.rs: ALBUMIN_ASSETS, albumin_asset, is_waterfall_output. C ABI: pc_albumin_asset_idx, pc_is_waterfall_output, pc_albumin_variants.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>High - verified against data_combi.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Albumin geometry: collision/height chain</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>mFM_SetBG -&gt; mFM_BgUtDataSet copies collision[16][16]+keep_h. mCoBG: 4-corner heights + center + attribute; GetUnitArea 4-triangle partition; world_y = corner*10 + base height. Acre height: combi_type:14 + height:2 from GetBlockBase. Numeric 16x16 values are disc-resource-side (data_bgd), not in decomp - marked as resource gap.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>albumin_geometry.rs: grid constants, COLLISION_HEIGHT_SCALE, world_y, combi bit layout. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>High - verified against m_field_make.c, m_collision_bg.c; resource values explicitly unknown.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5421,6 +5421,50 @@
       <c r="D208" t="inlineStr">
         <is>
           <t>High - verified against m_field_make.c, m_collision_bg.c; resource values explicitly unknown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Albumin collision: 16x16 data in decomp source</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>bg_data.c contains full data_bgd with real collision arrays for all 17 GRD_S_C*_R* assets. Unit layout: slate:1/center:5/tl:5/bl:5/br:5/tr:5/attr:6. Height levels 16/12/4/0. Attribute enum 64 values decoded.</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>albumin_collision_data.rs: 17x256 tables extracted programmatically. DOCUMENTATION.md corrected (no disc extraction needed).</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>High - verified against bg_data.c + m_collision_bg.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Albumin collision: physical geometry confirmed</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ASCII height maps: C1_R1_1 = waterfall-over-horizontal-cliff (high ground, river channel, cliff-face band, low ground); C3_R1_1 = vertical cliff face with river alongside. Accessors + world-Y queries added.</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>albumin_geometry.rs: albumin_unit, albumin_center_height, albumin_unit_world_y. C ABI: pc_albumin_center_height, pc_albumin_unit_world_y. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>High - source-verified spot checks.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K210"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5465,6 +5465,50 @@
       <c r="D210" t="inlineStr">
         <is>
           <t>High - source-verified spot checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Albumin geometry: 17-asset physical table</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>All 17 outputs reconstructed as physical geometry: 16x16 ASCII height maps per asset + summary table (river dir, cliff shape, waterfall?, water height, sloped units). Rules: waterfall = river crosses cliff (drop 12/16-&gt;0); non-waterfall = alongside on one terrace. Channels ~3 units wide; cliff faces 1-2 units wide. E/W families mirror.</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>albumin_geometry.md: full reference doc. albumin_geometry.rs: ASSET_RIVER_DIR, ASSET_CLIFF_IDX tables. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>High - maps generated from extracted collision data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Albumin geometry: work complete</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>The symbolic 7x7 albumin table is now a physical river-over-cliff / river-along-cliff geometry table. Chain closed: symbolic type -&gt; BG asset -&gt; 16x16 collision -&gt; height/attribute map -&gt; physical description.</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md section added; albumin_geometry.md reference.</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>High.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K212"/>
+  <dimension ref="A1:K214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5509,6 +5509,50 @@
       <c r="D212" t="inlineStr">
         <is>
           <t>High.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Placement deep dive: flat info + judge predicate</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D2ToD1 = bz*7+bx; placement scans cover 56 cells (z=0..7), correcting brief's '42 blocks'. Flat info: per-column ABOVE-&gt;BELOW on CLIFF_ANY, per-row LEFT-&gt;RIGHT on RIVER/RIVER_CLIFF_ANY, computed before mutation. JudgeFlatBlock ported source-faithfully incl. the BOTH-is-not-a-wildcard subtlety.</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>placement.rs: d2_to_d1, classify_river_row, classify_cliff_col, judge_flat_block, side/cheight enums. DOCUMENTATION.md section added.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Placement deep dive: unique buildings, needlework, heights</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>FlatBlock2Unique count-&gt;random-&gt;rewrite. Shrine side0=R(100)&amp;1; police opposite-first; museum BOTH/BELOW. Shop/post R(1000)&amp;1 ordering, x=1..2 / 4..5 TRACKS_DUMP slots. Needlework = ordinal pick among beach cells. Dock has no bit (kills NEEDLEWORK on failure). GetBlockBase: columns z=9-&gt;0 from STEP1=0, cliff-bit increments. SelectBlock unique-avoidance via l_use_data. PASS_ORDER constant (12).</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>placement.rs: rewrite_flat_idx, shrine_sides, shop_first, needlework_pick, base_height_column, PASS_ORDER. C ABI: pc_d2_to_d1, pc_shrine_sides, pc_needlework_pick. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K214"/>
+  <dimension ref="A1:K215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5553,6 +5553,28 @@
       <c r="D214" t="inlineStr">
         <is>
           <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Authorized test run #7</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>cargo test --lib: 294/294 passed, 0 failed (281 prior + 13 new across albumin, placement, albumin geometry, placement deep dive).</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md updated.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>High - authorized run 2026-10-07.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:K217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5575,6 +5575,50 @@
       <c r="D215" t="inlineStr">
         <is>
           <t>High - authorized run 2026-10-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Template anti-reuse: l_use_data mechanism</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Anti-reuse on concrete combi indices (not types). l_use_data[70] s16 reset to -1 per SelectBlock; SearchAlreadyUse = exact index equality. TypeCombCount/IndexInType2BlockNo verified verbatim; uniform selection; exhaustion -&gt; reuse pool. Z-major/X-minor traversal; no town regen on collision.</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>template_select.rs: use_data_reset, search_already_use, type_comb_count, index_in_type_2_block_no, select_block_type, select_traversal. C ABI: pc_type_comb_count, pc_search_already_use.</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Template anti-reuse: counts + SEA_EXCEPTIONAL + bug</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Per-type counts from data_combi.c (368/92 NONE) match brief exactly. SEA_EXCEPTIONAL bypasses anti-reuse (BG-name path, no use_data update). Retail mRF_GetRandom(0) bug confirmed with @BUG comment; BUGFIXES uses count - both modeled. Fallback BLOCK_COMBI_GRD_S_F_7 = 161.</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>template_select.rs: bg_name_2_random_combi_no (retail_bug flag), FALLBACK_COMBI. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c, data_combi.c, m_combi_type.h.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:K219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5619,6 +5619,50 @@
       <c r="D217" t="inlineStr">
         <is>
           <t>High - verified against m_random_field_ovl.c, data_combi.c, m_combi_type.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Step-3 bodies: ten 70-entry layouts</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Ten l_mRF_step3_blocks* arrays extracted programmatically to numeric Rust data (spot-checked vs source). Selection = one GetRandom(10), copied into both cliff+river buffers. No rotation/reflection/weighting/anti-reuse. Bodies immutable; re-selected each retry. R variants are separate literals.</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>step3_data.rs: 10 bodies, STEP3_BLOCKS, make_base_landform_step3. C ABI: pc_step3_select.</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Correction: BLOCK_TYPE_NONE = 255</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Earlier albumin/placement modules used NONE=109 from a positional enum extraction that hit the wrong enum block. Correct header value is 255 (explicit). All other block ids were correct. Fixed in albumin.rs + placement.rs; step3_data.rs used the correct map.</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>albumin.rs, placement.rs corrected. DOCUMENTATION.md notes the fix. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>High - verified against m_field_make.h.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K219"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5663,6 +5663,50 @@
       <c r="D219" t="inlineStr">
         <is>
           <t>High - verified against m_field_make.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Code audit: constants + recent modules</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Re-verified all block-type ids programmatically against m_field_make.h - all correct. Verified: albumin gates/math, merge semantics, placement offsets/conditions, judge_flat_block branches, albumin asset/waterfall tables, collision data integrity (4352 units), template_select RNG fidelity, step3 data, lib.rs wiring, docs consistency. Only dead-code warnings.</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md audit section added.</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>High - static audit 2026-10-07; runtime tests not run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Audit fix: decide_albumin_cell passthrough</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>decide_albumin_cell was missing the BORDER_CLIFF_RIVER (1) / TRACKS_RIVER (13) copy-through from mRF_DecideRiverAlbuminCliff. Fixed in albumin.rs with test cases.</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>albumin.rs: decide_albumin_cell fixed. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>High - verified against m_random_field_ovl.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K221"/>
+  <dimension ref="A1:K222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5707,6 +5707,28 @@
       <c r="D221" t="inlineStr">
         <is>
           <t>High - verified against m_random_field_ovl.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Authorized test run #8</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cargo test --lib: 296/296 passed, 0 failed (294 prior + 2 new: template_select, step3_data). Runtime-verifies the audit fix.</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md updated.</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>High - authorized run 2026-10-07.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K222"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5729,6 +5729,50 @@
       <c r="D222" t="inlineStr">
         <is>
           <t>High - authorized run 2026-10-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Collision: registration pools + frame order</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Two pools (collider_table OC, mco_work[10] OCC); clear empties both, object state untouched. Frame: OC -&gt; clear -&gt; actor. Scene_Read/Init register nothing; dt empty. Dispatch tables: OC=JntSph/Pipe^2, OCC=Tris x JntSph/Pipe.</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>collision_temporal.rs: pool, oc_dispatch/occ_dispatch, frame_order. C ABI: pc_oc_dispatch, pc_occ_dispatch.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>High - verified against m_collision_obj.c, m_play.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Collision: two clear tables + brief corrections</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>OCClearFunctionTable (setOC) vs OCCClearFunctionTable (setOCC) - distinct tables, easy trap. ClObj_OCClear clears COLLIDED/actor/PLAYER_WAS_HIT; ClObj_OCCClear clears actor/DONT_UPDATE_POS. Brief corrections: DONT_UPDATE_POS cleared by OCCClear not OCClear; attribute.t zeroed by TrisElem_OCCClear not OCClear. ClObj_set4 wholesale overwrite clears sticky TRIS_HIT.</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>collision_temporal.rs: set4_flags, doc clarifications. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>High - verified against m_collision_obj.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5773,6 +5773,50 @@
       <c r="D224" t="inlineStr">
         <is>
           <t>High - verified against m_collision_obj.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CORRECTION: TRIS_HIT is a one-frame latch (anomaly retracted)</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ClObj_OCCClear does collision_flags1 &amp;= ~ClObj_FLAG_DONT_UPDATE_POS, but the constant is 0x04 and the target is flags1, so numerically it clears flags1 bit 2 = TRIS_HIT. The earlier 'persistent TRIS_HIT anomaly' was a misreading of the constant name. Nothing clears the actual flags0 DONT_UPDATE_POS bit. Player axe/net confirm: setOCC registers, TRIS_HIT consumed during actor update, cleared at next registration.</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>collision_temporal.rs: occ_clear_flags0 -&gt; occ_clear_flags1; tris_hit_survives_setocc -&gt; tris_hit_cleared_by_setocc; C ABI pc_occ_clear_flags0 -&gt; pc_occ_clear_flags1. DOCUMENTATION.md anomaly sections corrected + new correction section. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>High - verified against m_collision_obj.c, m_player_common.c_inc, m_collision_obj.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>TRIS_HIT lifetime: player-side confirmation</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Axe/net triangles registered via setOCC from Player_actor_SetPosition_OBJtoLine_forItem (m_player_common.c_inc:2133). TRIS_HIT read by Player_actor_Check_OBJtoLine_forItem_axe (2055) and _net (2062, with collided_actor). Net invariant TRIS_HIT==0 =&gt; don't consume collided_actor holds because OCCClear clears both. Frame: collision -&gt; actor consumes -&gt; draw re-registers (clears).</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION.md correction section. Remaining: retail assembly check of ClObj_OCCClear byte col+0x09 &amp;= 0xFB (deferred per Philip).</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>High - verified against m_player_common.c_inc.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K226"/>
+  <dimension ref="A1:K227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5817,6 +5817,28 @@
       <c r="D226" t="inlineStr">
         <is>
           <t>High - verified against m_player_common.c_inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Albumin physical pipeline: keep_h + bitfield + height layers</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>mFM_BgUtDataSet copies collision[16][16] with no transformation; keep_h[z][x] = center (m_field_make.c:128). mCoBG_Collision_u = 32 bits: slate:1, center/tl/bl/br/tr:5 each, attr:6. Two height layers: acre/base (procedural) vs unit (data_bgd); world_y = unit*10 + base. All 17 BG_TYPE names confirmed in data_combi.c.</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>albumin_geometry.rs: keep_h_init, pack_col_unit/unpack_col_unit. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>High - verified against m_field_make.c, m_collision_bg.h, data_combi.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K227"/>
+  <dimension ref="A1:K229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5839,6 +5839,50 @@
       <c r="D227" t="inlineStr">
         <is>
           <t>High - verified against m_field_make.c, m_collision_bg.h, data_combi.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Quest system: request flow, completion, rewards</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>m_quest.c = persistent state; ac_quest_manager.c = definitions + 35-slot registration rebuilt each cycle; ac_quest_talk_init.c = transaction. QuestBase 12 bytes (type:2/kind:6/limit:1/progress:4/give_reward:1). Completion = progress==0 (contests dedicated; fish/insect category-based). Reward tables verbatim (delivery/contest/errand). 100-slot prob_tbl. Timeout tables + 28-day cap. give_reward retry. Money scaling. Friendship -3/+3/-5/-2/-1. 75% attempt roll.</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>rust/src/quest.rs: full tables + logic + 7 C ABI fns. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>High - verified against m_quest.h, m_quest.c, ac_quest_manager.h/c, ac_quest_talk_init.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CORRECTION vs brief: errand tier-1 pay</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Brief stated used_num=1 -&gt; 500 bells. Source (aQMgr_actor_get_errand_reward, ac_quest_talk_init.c:1084): reward_pay = {0,500,750,1000} indexed by (used_num-1) clamped 0..3, so used_num=1 -&gt; 0 bells, used_num=2 -&gt; 500, used_num=3 -&gt; 750, used_num&gt;=4 -&gt; 1000.</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>quest.rs ERRAND_PAY + errand_tier encode the source behavior. DOCUMENTATION.md notes the correction.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>High - source-verbatim.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5883,6 +5883,28 @@
       <c r="D229" t="inlineStr">
         <is>
           <t>High - source-verbatim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Fishing and bug-catching mechanics (ecology)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>4 fish time periods (21-23 -&gt; TIME_0 fallthrough), 24 half-month terms, 5-day transition 5/6..1/6, field-rank 0.5/0.75/0.875/1.0. Fish: 7 areas, weighted select with env_rate subtraction + no-replacement retry, 12x12 interior, ocean depth 20.0, bite timing table, UKI states, 50-frame cast. Insects: 14 areas, 9 slots (8 spawn), no-spawn roll (total&lt;=100 -&gt; roll vs 100), habitat-first filtering, 6+rand(3) multi-birth. Net: 8-slot request table, insertion order, force first, frame-6.0 window, golden 60/21+r vs 50/15+r, projection test.</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>rust/src/ecology.rs: full mechanics + 7 C ABI fns. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>High - verified against ac_set_ovl_gyoei.c/h, ac_set_ovl_insect.c/h, ac_insect_h.h, m_player_main_swing_net.c_inc, m_player.h.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K230"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5905,6 +5905,28 @@
       <c r="D230" t="inlineStr">
         <is>
           <t>High - verified against ac_set_ovl_gyoei.c/h, ac_set_ovl_insect.c/h, ac_insect_h.h, m_player_main_swing_net.c_inc, m_player.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Shop/house progression fidelity fixes</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>House: 3 phases (order: next_size/date only; construction: date-gated size=next_size+renew; Nook: loan assignment). Basement from MEDIUM or LARGE. pad_1 = basement-completion flag. Statue date-gated via next_size. Shop: wrapping_add (not saturating), visitor toggle labeled PC-only, renovation scheduler (+2 days, bargain-day block, due check, completion).</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>house.rs rewritten (3-phase API); shop.rs extended (scheduler). DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>High - verified against m_home.c, ac_npc_shop_common.c, m_shop.c, ac_shop_level.c.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5927,6 +5927,28 @@
       <c r="D231" t="inlineStr">
         <is>
           <t>High - verified against m_home.c, ac_npc_shop_common.c, m_shop.c, ac_shop_level.c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Mail system beyond letter scoring</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Mail_c = fixed 298-byte struct (header/personal IDs, present, content). 3 stores: mailbox 10, inventory 10, PO queue 5; archive 8x20=160. Font = lifecycle state (RECV/SEND/RECV_READ/+present variants; 0xFF unused). Player mail -&gt; PO; auto mail -&gt; mailbox then PO. Delivery 09:00/17:00; full mailbox -&gt; stays queued; slot cleared only after copy. Recipient flags + queue counts. Read transitions, present rules, 12 mail types, NPC friendship +3/-5/+3.</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>rust/src/mail.rs: data model + state machine + routing + PO + 4 C ABI fns. DOCUMENTATION.md section added. cargo check clean. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>High - verified against m_mail.h, m_home_h.h, m_private.h, m_post_office.h/c, m_card.h.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K232"/>
+  <dimension ref="A1:K233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5949,6 +5949,28 @@
       <c r="D232" t="inlineStr">
         <is>
           <t>High - verified against m_mail.h, m_home_h.h, m_private.h, m_post_office.h/c, m_card.h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Furniture placement and house interiors beyond layout scan</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>mHm_flr_c = 4 FG layers (main/secondary/storage1/storage2) + wall_floor + floor_bit_info (custom-design bits). Saved house is persistent FG; room entry deserializes to FTR_ACTORs (layers 0/1 only), exit serializes back. Rotation in low 2 bits of item no (0=SOUTH..3=WEST). 6 shapes: 4x 1x2 orientations + 1x1 + 2x2; verbatim offsets B90 {0,-16}, B180 {0,-1}, B270 {0,+16}, B0 {0,+1}, C {0,1,16,17}. Multi-cell: primary cell item, rest RSV_FE1F (0xFE1F); EMPTY_NO=0x0000. Interior bounds 8x8 (1..8). Placement: flat check, actor budget, player_angle+180deg facing (45-135 E,135-225 N,225-315 W), stego/balloons +1 (idx 964, 1020-1027), frog +2 (idx 827), 5-unit forward search i=0..4, NO_COLLISION under-player, all-rotation fallback (@BUG), ON_SURFACE-&gt;layer1 on SURFACE furniture. Save angle: sin&gt;0.8 E, sin&lt;-0.8 W, cos&gt;0.8 S, cos&lt;-0.8 N. aFTR_KEEP_ITEM_COUNT=3 (corrects save.rs guide-claim comment). 3 reservation slots / 46 frames, 17 actor states, 4 fitted children (relative pos). Scene furniture max: NPC 30, shops 10, small 32, medium 48, large 64, painting 20, fossil 25, upper/basement/cottage 64. Weight always 1. Switch u64 keyed by interior pos (x-1)+(z-1)*8. Gaps: aMR_GetPlayerLookAtUnit exact mapping (Rust quantizes direction), place-table sentinels, collision size table, layer_set_info, vtable behaviors.</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>rust/src/furniture.rs: RoomLayer/HouseFloor, Direction+rotation macros, ShapeType offsets, placement judge, serialization, switch bitfield, 10 C ABI fns. DOCUMENTATION.md section added. cargo check --lib clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>High - verified against ac_furniture.h, ac_my_room.c, ac_my_room_move.c_inc, m_room_type.h/c, m_home_h.h, m_ftr_def.h</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K233"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5971,6 +5971,28 @@
       <c r="D233" t="inlineStr">
         <is>
           <t>High - verified against ac_furniture.h, ac_my_room.c, ac_my_room_move.c_inc, m_room_type.h/c, m_home_h.h, m_ftr_def.h</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Quest request generation: type/kind tables, recipient modes, entrusted items, letter quests</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Pipeline: pending? -&gt; 75% gate -&gt; type table (fj {D,E} vs normal {D,E,C}) -&gt; uniform type/kind -&gt; occur check -&gt; l_set_data[type][kind] -&gt; recipient -&gt; item -&gt; pocket handover. First-job when !man-kind &amp;&amp; firstjob event. Kind tables: fj delivery {NORMAL,LOST}, normal delivery {NORMAL,FOREIGN,REMOVE,LOST}, errand {REQUEST}, contest 7 kinds. Occur: contest kind not already active; snowman Jan/Feb1-17/Dec25-31 hour 8-16 (16:59); flower Feb25-Aug &gt;=4 empty &lt;=20 flowers; insect Mar-Oct/Nov1-28; letter = local resident player; foreign/remove need valid stored IDs; no reroll on fail. Six recipient modes 0-5: RANDOM (uniform eligible, giver+same-acre excluded), RANDOM_EXCLUDED (+chain, sets CHAIN), ORIGINAL_TARGET (chain head else giver), FOREIGN (stored_anm_id), LAST_REMOVE (last_removed_animal_id), CLIENT (giver). Uniform-among-eligible walk. l_set_data verbatim: 4 delivery, 15 errand (chain stages 0-2; 12 fj rows uniform CLIENT/0d/no-handover/CURRENT_ITEM), 7 contest (all CLIENT). Item sources RANDOM/FRUIT(non-native)/CLOTH/FROM_DATA/CURRENT_ITEM(or ITM_CLOTH001=0x2401)/NONE. progress=last_step, limit iff day_limit!=0. Entrusted: first empty pocket or NEW_QUEST_NO_SPACE; ITEM_COND_QUEST (0/1/2); delivery[i]&lt;-&gt;pocket[i]; errand pockets_idx; grab.pocket_idx = pocket idx (delivery) vs errand idx (errand); put-down displaces destination occupant. Letter quest: SetReceiveLetter gate (CONTEST/LETTER, progress 2, no player) -&gt; player_id=sender, progress 1, score=rank, present=GetPresent(rank); rank = len17/49 + quality&gt;=OK + present (reuses mQst_GetMailRank); presents 0-11 table (5/11 50-50 carpet/wallpaper); handbill 0x75+rank*6+looks; festive paper; mailbox-full fails remail. First-job SEND_LETTER[_2]: ERRAND/FIRST_JOB, progress 2, no limit/reward/item, used_ids[1]=recipient, used_num=2; completion -&gt; progress 3, send_reply=FALSE. CORRECTION: quest.rs contest_complete was wrong for fruit (needs item possessed) and snowman (needs player_id set == current); now ContestQual + cqual flags; pc_contest_complete ABI takes flags. Corrections vs brief: snowman hour through 16:59; letter gate = local resident player; 12 fj set-data rows uniform; item-source FRUIT = non-native fruit. Gaps: msg_start semantics, fj recipient selection, errand_next chain progression, quest-item invalidation paths, completion/reward ordering.</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>rust/src/quest_gen.rs: tables + selection + occur + 6 recipient modes + verbatim set-data + entrusted items + grab/put + letter quest + 16 C ABI fns; quest.rs contest_complete fix (ContestQual/cqual). DOCUMENTATION.md section added. cargo check --lib clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>High - verified against m_quest.h, m_quest.c, ac_quest_manager.h/c, ac_quest_talk_init.c (+ second verification pass)</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K234"/>
+  <dimension ref="A1:K235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5993,6 +5993,28 @@
       <c r="D234" t="inlineStr">
         <is>
           <t>High - verified against m_quest.h, m_quest.c, ac_quest_manager.h/c, ac_quest_talk_init.c (+ second verification pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Full seasonal species tables: fish (678) + insects (576)</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Machine-extracted verbatim from ac_set_ovl_gyoei.c / ac_set_ovl_insect.c (GAFE01_00 Rev. 0); counts machine-verified: 678 unique fish entries, 514 town + 62 island insect entries. Fish: 24 half-month terms x 4 daily periods (21-03:59/04-08:59/09-15:59/16-20:59); river/ocean/pond families + tournament + island tables; pond only Apr-Aug + Sep 1-15; Sep has distinct latter-half river table; relative (non-percentage) weights; Salmon2 = distinct river-mouth type (RIVER+MARINE acre). Insects: 12 monthly terms x 6 daily periods (23-03:59/04-07:59/08-15:59/16-16:59/17-18:59/19-22:59); Jan/Feb/Dec sparse 3-entry fallback; NONE is a real no-insect entry; selection rolls vs 100 when total&lt;=100. Dynamic: Coelacanth injected (rain + not 09-15:59, current term only); offing = 10x ocean + Whale 1; Ant/candy, Ant/trash, Cockroach/trash appended, full override when candy/spoiled turnips; Spirit = single SPIRIT/FLYING/100 entry. Transitions: 5-day, 0-5 random offset, rates 5/6..1/6, ordered concatenation (species may duplicate); fish at half-month, insects at month boundaries. l_insect_birth_sum: red dragonfly + firefly (6,+3); NONE implicitly (0,0). Selection algorithms + terms/times reused from ecology.rs (fish_select no-replacement retry, insect_select no-spawn mass, field-rank rates). Gaps: physical spawn-unit selection not wired to real acre data; guide-move insect_term/gyoei_term init discrepancy noted not copied; BUGFIXES spawn interactions need audit; no C callers rewired. Verification corrections vs brief: Salmon2 river-mouth RIVER+MARINE gate is Australian-only (#if VERSION&gt;=VER_GAFU01_00); USA Rev. 0 requires RIVER only. Fish invalid-area retry marks the entry slot, not the fish type. Island skips transition blending (rate 1.0) but rain Coelacanth injection still applies there. Whale added for current term only during transitions.</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>rust/src/species.rs: enums (source order) + lookup + transition blending + dynamic insertions + 6 C ABI fns; rust/src/fish_tables.rs + rust/src/insect_tables.rs: machine-generated verbatim data. DOCUMENTATION.md section added. cargo check --lib clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>High - machine-extracted from source; counts verified (678/514/62)</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K235"/>
+  <dimension ref="A1:K236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6015,6 +6015,28 @@
       <c r="D235" t="inlineStr">
         <is>
           <t>High - machine-extracted from source; counts verified (678/514/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Authorized test run #7 + systems showcase prototype</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Philip said 'Run tests': cargo test --lib -&gt; 335/335 passed, 0 failed. Five failures on the first attempt were all wrong test expectations, not implementation bugs: (1) fish_select high rolls pick early entries / low rolls pick late entries (retail walks total downward); (2) insect_select basis-100 arithmetic (roll 0.5 -&gt; entry 1, not entry 0); (3) house basement test needed next_size = Medium (no expansion pending); (4) handover_item takes the first empty pocket (idx 1, not 3); (5) island NONE-78 table is INSECT_ISLAND[0] (brief's 1-indexed 'term 1'). All fixed; implementation unchanged. Then built showcase/ generator crate -&gt; showcase.html (5 tabs: 3D Town WebGL, Fish &amp; Bugs explorer over 236 fish + 78 insect tables, Letter Lab with 6 real-scored samples, Quest Board with 12 real l_set_data rows, 24-card Systems Index). Both scripts node --check clean; data smoke-tested.</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>showcase/ crate (Cargo.toml, src/main.rs); DOCUMENTATION.md section. Test fixes in ecology.rs, house.rs, quest_gen.rs, species.rs. cargo test --lib: 335/335 pass.</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>High - full suite green</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K236"/>
+  <dimension ref="A1:K237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6037,6 +6037,28 @@
       <c r="D236" t="inlineStr">
         <is>
           <t>High - full suite green</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>UKI float state machine internals</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Philip's brief: fishing is not one state machine — UKI coordinates proc (11 values), status (8 values), the gyo_command/gyo_status fish handshake, child_actor, and the player's rod commands. Implemented rust/src/uki.rs verified against include/ac_uki.h, src/actor/ac_uki.c, src/actor/ac_uki_move.c_inc (GAFE01_00 Rev. 0; PC port corroborating). Ported: init state (frame_timer 2, gyo_type -1, scale 0.01, max_velocity_y -20.0, gravity 1.2); all 11 proc initializers (READY 32f+20f parabola 30u behind player; CAST 50f+cast_timer 40; HIT 52f dual trajectories float-&gt;right-hand + uki_pos-&gt;left-hand; BITE size-based reel timer; CATCH 20f; GET); force commands 7/8; 40-frame cast_timer fish gate; failed-reel path; verbatim parabola math (y_param 12.0 if dy&gt;100 else 4.5); water drift 0.45/0.225/0.8 with 130u/127u thresholds; coast WAVE/SAND; touch_timer water-state machine (+7.5 hooked, -7.5 unhooked, -1.7 touch cycle); waterfall behavior. Fish-side tables verbatim: 45-entry gyoei_type; reel timers 26/39/39/39/52/65/78/78 (x2, trash 26); search angles normal 3/7/30/50/180 vs golden 7.5/15/40/60/180; search distances 40/40/40/50/60; bite times normal 10/11/12/15/45 vs golden 11/12/13/18/60 (x2); touch radii/counters/retreat speeds; gomi[] trash substitution 1/20 on bite commit; fish-&gt;item table with duplicate FISH39 and FISH22 tail. Machine runs only while command != 0. Engine pieces (bg collision, effects, sound) are StepEnv inputs / UkiEvent outputs. 7 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: all 26 claims checked against retail sources — 24 confirmed verbatim; 2 corrected vs brief: sizeof(UKI_ACTOR) is 0x2C8 not 0x2B8 (extra fields hamon_accum/touch_vib_accum/logic_accum/logic_ticks past coast_flag), and the CARRY frame_timer is 2 at construction but 4 on every subsequent set_proc(CARRY). Command 1-8 call sites, gyo_status 0-8 transitions, parabola math, BG-check process dependence, trash gomi[] table, and golden-rod parameters all confirmed verbatim.</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>rust/src/uki.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K237"/>
+  <dimension ref="A1:K238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6057,6 +6057,28 @@
         </is>
       </c>
       <c r="D237" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Bee/ant special actors</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Philip's brief: bee and ant are two-stage special actors (mAc_PROFILE_BEE / mAc_PROFILE_ANT, ACTOR_PART_BG), not normal insects; only on capture do they convert to aINS_INSECT_ACTOR via aINS_MAKE_EXIST in the reserved ninth slot. Implemented rust/src/bee_ant.rs verified against ac_bee.c, ac_ant.c, ac_insect_clip.c_inc, ac_set_ovl_insect.c, bg_item_common.c_inc (GAFE01_00 Rev. 0). Ported: slot reservation (NEW 0..7, EXIST slot 8 only); retryable pending ant spawn (cleared only on success); runtime ant overlay ANT/ON_CANDY + ANT/ON_TRASH + COCKROACH/ON_TRASH appended to every range; candy/trash weight override (limit_insect_data) + field-rank bypass (env_rate 1.0); exact-one birth; ant substrate candy 0x2806 / spoiled turnip 0x2F03 (rain/snow excluded at habitat level); ant 24.0 catch radius with NET_CATCH_TYPE_ANT=1 (INSECT=0); bee-tree shake lifecycle (TREE_BEES 0x005E / CEDAR_TREE_BEES 0x007A / GOLD_TREE_BEES 0x0081 -&gt; dormant bee at (-1,-1,-1), HONEYCOMB 0x0062 drop speed 5 accel -1.2, tree reverts immediately, bee positioned on landing, honeycomb lingers 120f independently); bee APPEAR ~85f (+3 alpha), 60f catch delay, player-relative flight (speed 2.9 eased, altitude player.y+50+5*sin(bobbing 0x900), turn-dependent body deformation), 30u attack trigger with ATTACK_WAIT staging, sting coupling (bee waits while player STUNG_BEE), ~17f disappearance (alpha -15, scale 0.03/0.01), extra_data=0 conversion. Engine reads are BeeEnv/AntEnv inputs, side effects are BeeEvent/AntEvent outputs. 6 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>rust/src/bee_ant.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
         <is>
           <t>High - verified against retail sources; tests not run per standing rule</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K238"/>
+  <dimension ref="A1:K239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6079,6 +6079,28 @@
         </is>
       </c>
       <c r="D238" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Catalog-order / lottery special delivery</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Philip's brief: catalog orders and lottery special handling are separate pieces of the special-mail infrastructure. Implemented rust/src/special_delivery.rs verified against m_private.h, ac_npc_shop_common.c, ac_npc_shop_mastersp_talk.c_inc, m_shop.c, m_post_office.c (GAFE01_00 Rev. 0). Ported: CatalogOrders (5 slots, item + order-time shop_level; ascending free-slot scan; ORDER_FULL; paid immediately with mSP_PlusSales); lottery (lottery_items[3] per shop, monthly lineup with uncollected item in slot 0, 5 same-month tickets per play, slot-order consumption with retail's unclamped req -= count, odds 5/10/20/65 on RANDOM(100), consumed prizes -&gt; RSV_SHOP_SOLD_FTR with no reroll); TicketOverflow (expiry_month + mail_storage u8, cap 255, month change resets); ticket encoding macros (0x2C00 range, stacks 1-5). deliver_special_mail: tickets first in stacks of &lt;=5 (ticket_id = base + minus - 1, template 0x057), then catalog orders ascending (template 0x049 + shop_level, paper ITM_PAPER55, mail_type 7); each mail transactional against mailbox capacity (10 slots), failures stop delivery and preserve remainders. NEW FINDING vs brief: the special-delivery trigger IS in the decomp — mPO_first_work() (game start) -&gt; mPO_first_delivery_proc() calls mPO_delivery_one_address_special_mail() for the current local (non-foreigner) player's house, independent of ordinary mail timing; modeled as first_delivery_special_mail_house. 7 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 21/23 claims confirmed verbatim (incl. the order += sizeof(u8) oddity, unclamped req -= count, no-reroll prize logic, 2/0/1 display order, ticket batching arithmetic). 2 corrections: (1) the special-delivery caller EXISTS — mPO_first_delivery_proc() via mPO_first_work() at game start, gated on the player not being a foreigner (already modeled as first_delivery_special_mail_house); (2) the 'no shop upgrade within 2 days of lottery day' comment is NOT present in the decomp — only the Fukubiki status machinery and goods-list suppression are confirmed. Also noted: ticket overflow triggers from the no-inventory-room purchase path (aNSC_setup_ticket_remain).</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>rust/src/special_delivery.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
         <is>
           <t>High - verified against retail sources; tests not run per standing rule</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K239"/>
+  <dimension ref="A1:K240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6103,6 +6103,48 @@
       <c r="D239" t="inlineStr">
         <is>
           <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Leaflet broadcast</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Philip's brief: the post office has two persistent singleton broadcast messages (leaflet @ 0x5DA, event_leaflet @ 0x704, PostOffice_c = 0x83C), each with a 4-bit recipient mask (leaflet_flags @ 0x830, event_flags @ 0x832; union with raw int; save checker rejects bits outside 0b1111). Implemented rust/src/leaflet.rs verified against m_post_office.h, m_post_office.c, ac_npc_post_man_move.c_inc, ac_event_manager.c, m_event.c, m_event_schedule.c_inc, m_shop.c, save_check.c_inc (GAFE01_00 Rev. 0). Ported: flag polarity 0 = pending / 1 = delivered (inverse of normal mail, per retail comment); init sets both masks to 0xF (raw = 0x000F000F); receipt_proc overwrites the singleton and resets its mask to 0 (new leaflet replaces undelivered one, no queue); per-house delivery (attempt only when bit is 0, unclaimed land_id 0xFFFF marked delivered without mail, foreign/Arbeit players skipped, full mailbox leaves bit 0 for retry); event-leaflet validity filter (SHOP_SALE_LEAFLET -&gt; mEv_EVENT_SHOP_SALE=26, BROKER_SALE_LEAFLET -&gt; mEv_EVENT_BROKER_SALE=29, else -1; expired handbills become undeliverable); handbill generation (shop-sale 4x4 template table 0x002-0x011 paper 55 with item-count/name/month/day/hour free strings; broker RANDOM(3) of 0x031-0x033 paper 54; rare-chirashi table {{18,18},{19,19},{21,20},{23,22}} paper ITM_PAPER55); ShopItsumoChirashi send_proc trap (only mPO_SENDTYPE_MAIL routes to broadcast receipt; traced caller passes LEAFLET -&gt; direct mailbox branch); postman check_delivery (normal OR leaflet-pending OR event-pending; Arbeit = normal only), set_delivery_idx scan, delivery_init order mail -&gt; leaflet -&gt; event leaflet; 09:00/17:00 delivery schedule; startup first_delivery_proc (normal mail, then catalog/ticket special mail, then leaflets). 7 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 20/20 brief claims confirmed verbatim. CORRECTION vs brief: special-event setup sets event_flags = 0b1111, which given 0 = pending marks all four DELIVERED (suppresses delivery by default) — the pending state comes from the handbill registration's receipt_proc (mask = 0); the brief's claim-20 reading was inverted.</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>rust/src/leaflet.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K240"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6143,6 +6143,48 @@
         </is>
       </c>
       <c r="H240" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Mother-mail scheduler</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Philip's brief: per-player persistent Mom-mail scheduler with three pools. Implemented rust/src/mother_mail.rs verified against m_private.c, m_private.h, m_common_data.h, m_start_data_init.c, m_mail.h, m_event_schedule.c_inc (GAFE01_00 Rev. 0). Ported: save layout mother_mail[4] x 14 bytes (date + normal[7] + monthly[2] + august) in Save_t, not Private_c; clear sentinel FFFF/FF/FF; startup gates (local player, valid Private_c/ID); first-ever run stamps date only; single date != today check, no catch-up; Pool A fixed dates (birthday 0x184+RANDOM(2)+cake, month==day 0x164+(month-1)*2+RANDOM(2) with Jan1=10000 Bells and letter18=mushroom, Apr Fools 0x180, Mother's 0x17C, Father's 0x17E, Toy Day Dec24 0x182+random furniture; birthday precedence; Mother's/Father's via event status); Pool B 56 normal letters 0x12C-0x163, RANDOM(100)&lt;20 daily gate, uniform unsent selection, exhaustion zeroes whole data block then sends one Pool C letter; Pool C seasonal (2/month, 8 August; mail_start_no_table {0x18C,0x192,0x186,0x19E} literal; May=RANDOM(1) fortune shirt kept, Nov=mushroom, Dec=apple/RANDOM(6) shirts); normal presents (1/16 clothing, 3/21/22/47 other fruit, 12=1000 Bells, 37 doll, 38 dracaena, 40 umbrella); delivery house-mailbox-first then PO fallback, type 4 = mMl_TYPE_MOTHER; normal failure consumes day without marking letter, special failure leaves date for same-day retry; paper table {13,49,32,12,62,14,19,11,59,46,47,17} minus 1 with birthday/Jan1/Aug8/Dec24 overrides. Engine-resolved presents kept symbolic (PresentSpec); RNG injected as FnMut(u32)-&gt;u32 preserving call order. 4 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). All key functions confirmed verbatim against the decomp by direct source read (special-date order incl. Dec24 present-before-variant RNG order, monthly/normal selection loops, bzero transition, asymmetric date-update rules, paper overrides); subagent second verification pass pending at commit time.</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>rust/src/mother_mail.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Philip's brief: per-player persistent Mom-mail scheduler with three pools. Implemented rust/src/mother_mail.rs verified against m_private.c, m_private.h, m_common_data.h, m_start_data_init.c, m_mail.h, m_event_schedule.c_inc (GAFE01_00 Rev. 0). Ported: save layout mother_mail[4] x 14 bytes (date + normal[7] + monthly[2] + august) in Save_t, not Private_c; clear sentinel FFFF/FF/FF; startup gates (local player, valid Private_c/ID); first-ever run stamps date only; single date != today check, no catch-up; Pool A fixed dates (birthday 0x184+RANDOM(2)+cake, month==day 0x164+(month-1)*2+RANDOM(2) with Jan1=10000 Bells and letter18=mushroom, Apr Fools 0x180, Mother's 0x17C, Father's 0x17E, Toy Day Dec24 0x182+random furniture; birthday precedence; Mother's/Father's via event status); Pool B 56 normal letters 0x12C-0x163, RANDOM(100)&lt;20 daily gate, uniform unsent selection, exhaustion zeroes whole data block then sends one Pool C letter; Pool C seasonal (2/month, 8 August; mail_start_no_table {0x18C,0x192,0x186,0x19E} literal; May=RANDOM(1) fortune shirt kept, Nov=mushroom, Dec=apple/RANDOM(6) shirts); normal presents (1/16 clothing, 3/21/22/47 other fruit, 12=1000 Bells, 37 doll, 38 dracaena, 40 umbrella); delivery house-mailbox-first then PO fallback, type 4 = mMl_TYPE_MOTHER; normal failure consumes day without marking letter, special failure leaves date for same-day retry; paper table {13,49,32,12,62,14,19,11,59,46,47,17} minus 1 with birthday/Jan1/Aug8/Dec24 overrides. Engine-resolved presents kept symbolic (PresentSpec); RNG injected as FnMut(u32)-&gt;u32 preserving call order. 4 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). All key functions confirmed verbatim against the decomp by direct source read (special-date order incl. Dec24 present-before-variant RNG order, monthly/normal selection loops, bzero transition, asymmetric date-update rules, paper overrides); subagent second verification pass pending at commit time.</t>
+          <t>Philip's brief: per-player persistent Mom-mail scheduler with three pools. Implemented rust/src/mother_mail.rs verified against m_private.c, m_private.h, m_common_data.h, m_start_data_init.c, m_mail.h, m_event_schedule.c_inc (GAFE01_00 Rev. 0). Ported: save layout mother_mail[4] x 14 bytes (date + normal[7] + monthly[2] + august) in Save_t, not Private_c; clear sentinel FFFF/FF/FF; startup gates (local player, valid Private_c/ID); first-ever run stamps date only; single date != today check, no catch-up; Pool A fixed dates (birthday 0x184+RANDOM(2)+cake, month==day 0x164+(month-1)*2+RANDOM(2) with Jan1=10000 Bells and letter18=mushroom, Apr Fools 0x180, Mother's 0x17C, Father's 0x17E, Toy Day Dec24 0x182+random furniture; birthday precedence; Mother's/Father's via event status); Pool B 56 normal letters 0x12C-0x163, RANDOM(100)&lt;20 daily gate, uniform unsent selection, exhaustion zeroes whole data block then sends one Pool C letter; Pool C seasonal (2/month, 8 August; mail_start_no_table {0x18C,0x192,0x186,0x19E} literal; May=RANDOM(1) fortune shirt kept, Nov=mushroom, Dec=apple/RANDOM(6) shirts); normal presents (1/16 clothing, 3/21/22/47 other fruit, 12=1000 Bells, 37 doll, 38 dracaena, 40 umbrella); delivery house-mailbox-first then PO fallback, type 4 = mMl_TYPE_MOTHER; normal failure consumes day without marking letter, special failure leaves date for same-day retry; paper table {13,49,32,12,62,14,19,11,59,46,47,17} minus 1 with birthday/Jan1/Aug8/Dec24 overrides. Engine-resolved presents kept symbolic (PresentSpec); RNG injected as FnMut(u32)-&gt;u32 preserving call order. 4 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 19/19 claims confirmed verbatim (incl. m_start_data_init call sites, mMl_TYPE_MOTHER = 4, Mother's/Father's Day schedule macros, no Dec 25 branch, the unconditional date update in the normal path vs success-gated update in the special path). No corrections.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K241"/>
+  <dimension ref="A1:K242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6185,6 +6185,48 @@
         </is>
       </c>
       <c r="H241" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>NPC reply generation</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Philip's brief: deterministic NPC reply pipeline (eligibility at receive time, generation at next startup) + mMck_check_key_hit_nes() scorer + mHandbillz_load() composer. Implemented rust/src/npc_reply.rs and machine-extracted rust/src/mck_key_tables.rs, verified against m_npc.c, m_mail_check_ovl.c, m_handbill.c, m_handbill.h, m_font.c, m_font_main.c_inc, m_msg_main.c_inc (GAFE01_00 Rev. 0). Ported: (1) mMck 7-component scorer over the 192-byte body (A final-punct +20 and per-separator +/-10, B +3/vocabulary hit, C first-char +20/-10, D -50 triple-alpha once, E space-ratio +/-20, F -150 run-on once, G -20/spaceless 32-block); 26 key tables extracted verbatim by script (max 89 pairs); rank &lt;50 BAD / 50-99 no reply / &gt;=100 OK via the nes path (length variant unused in USA). (2) Scheduler: receive stamps date, sets cond+send_reply only for BAD/OK; no 25% RNG behind the '// 25%' comment; first-job and letter-contest suppression; friendship +3/-5/+3; mNpc_Remail scans animals[] in order, later-calendar-date gate, break-on-PO-failure with pending retained, foreign remail via looks != 0x7F sentinel with no date check and clear-on-success-only. (3) Generation: BAD canned 0xC5/0xD8+looks*3+RANDOM(3), no present; GOOD RANDOM(4)&amp;1 present, category RANDOM(4)&amp;1, 11 RANDOM_F free-string rolls, five fragment indices (MAILB +16 half when present), random paper; mHandbillz composer as in-place buffer editor over a resource-provider trait (SUPER border/header_back_start adjustment, MAILA+B+C concat with 192 cap, PS pad, FREE/article/capital controls). CORRECTIONS vs brief: control-code ids are FREE0=37..FREE9=46, FREE10=55..FREE19=64, CUT_ARTICLE=117, CAPITAL_LETTER=118 (brief implied 36/116/117); foreign replies skip the letter-date check entirely. Documented deviations: mMck_cmp_key stops at table end (retail reads linker-adjacent bytes past the missing 0x7F terminator - unknowable from source); final ROM text needs retail assets the decomp excludes. 5 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Subagent second verification pass pending at commit time.</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>rust/src/npc_reply.rs + rust/src/mck_key_tables.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Philip's brief: deterministic NPC reply pipeline (eligibility at receive time, generation at next startup) + mMck_check_key_hit_nes() scorer + mHandbillz_load() composer. Implemented rust/src/npc_reply.rs and machine-extracted rust/src/mck_key_tables.rs, verified against m_npc.c, m_mail_check_ovl.c, m_handbill.c, m_handbill.h, m_font.c, m_font_main.c_inc, m_msg_main.c_inc (GAFE01_00 Rev. 0). Ported: (1) mMck 7-component scorer over the 192-byte body (A final-punct +20 and per-separator +/-10, B +3/vocabulary hit, C first-char +20/-10, D -50 triple-alpha once, E space-ratio +/-20, F -150 run-on once, G -20/spaceless 32-block); 26 key tables extracted verbatim by script (max 89 pairs); rank &lt;50 BAD / 50-99 no reply / &gt;=100 OK via the nes path (length variant unused in USA). (2) Scheduler: receive stamps date, sets cond+send_reply only for BAD/OK; no 25% RNG behind the '// 25%' comment; first-job and letter-contest suppression; friendship +3/-5/+3; mNpc_Remail scans animals[] in order, later-calendar-date gate, break-on-PO-failure with pending retained, foreign remail via looks != 0x7F sentinel with no date check and clear-on-success-only. (3) Generation: BAD canned 0xC5/0xD8+looks*3+RANDOM(3), no present; GOOD RANDOM(4)&amp;1 present, category RANDOM(4)&amp;1, 11 RANDOM_F free-string rolls, five fragment indices (MAILB +16 half when present), random paper; mHandbillz composer as in-place buffer editor over a resource-provider trait (SUPER border/header_back_start adjustment, MAILA+B+C concat with 192 cap, PS pad, FREE/article/capital controls). CORRECTIONS vs brief: control-code ids are FREE0=37..FREE9=46, FREE10=55..FREE19=64, CUT_ARTICLE=117, CAPITAL_LETTER=118 (brief implied 36/116/117); foreign replies skip the letter-date check entirely. Documented deviations: mMck_cmp_key stops at table end (retail reads linker-adjacent bytes past the missing 0x7F terminator - unknowable from source); final ROM text needs retail assets the decomp excludes. 5 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Subagent second verification pass pending at commit time.</t>
+          <t>Philip's brief: deterministic NPC reply pipeline (eligibility at receive time, generation at next startup) + mMck_check_key_hit_nes() scorer + mHandbillz_load() composer. Implemented rust/src/npc_reply.rs and machine-extracted rust/src/mck_key_tables.rs, verified against m_npc.c, m_mail_check_ovl.c, m_handbill.c, m_handbill.h, m_font.c, m_font_main.c_inc, m_msg_main.c_inc (GAFE01_00 Rev. 0). Ported: (1) mMck 7-component scorer over the 192-byte body (A final-punct +20 and per-separator +/-10, B +3/vocabulary hit, C first-char +20/-10, D -50 triple-alpha once, E space-ratio +/-20, F -150 run-on once, G -20/spaceless 32-block); 26 key tables extracted verbatim by script (max 89 pairs); rank &lt;50 BAD / 50-99 no reply / &gt;=100 OK via the nes path (length variant unused in USA). (2) Scheduler: receive stamps date, sets cond+send_reply only for BAD/OK; no 25% RNG behind the '// 25%' comment; first-job and letter-contest suppression; friendship +3/-5/+3; mNpc_Remail scans animals[] in order, later-calendar-date gate, break-on-PO-failure with pending retained, foreign remail via looks != 0x7F sentinel with no date check and clear-on-success-only. (3) Generation: BAD canned 0xC5/0xD8+looks*3+RANDOM(3), no present; GOOD RANDOM(4)&amp;1 present, category RANDOM(4)&amp;1, 11 RANDOM_F free-string rolls, five fragment indices (MAILB +16 half when present), random paper; mHandbillz composer as in-place buffer editor over a resource-provider trait (SUPER border/header_back_start adjustment, MAILA+B+C concat with 192 cap, PS pad, FREE/article/capital controls). CORRECTIONS vs brief: control-code ids are FREE0=37..FREE9=46, FREE10=55..FREE19=64, CUT_ARTICLE=117, CAPITAL_LETTER=118 (brief implied 36/116/117); foreign replies skip the letter-date check entirely. Documented deviations: mMck_cmp_key stops at table end (retail reads linker-adjacent bytes past the missing 0x7F terminator - unknowable from source); final ROM text needs retail assets the decomp excludes. 5 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 28/28 confirmed, 1 correction (#26): capital_flag is NOT cleared after each FREE insertion in retail USA - the clear call at the end of Put_String_FREE is itself the copy-paste bug, so once CAPITAL_LETTER fires the flag stays set for all later insertions (already modeled as a no-op in the Rust port). Also confirmed: RANDOM_F = fqrand() * n (sys_math.h:35); F inner scan has no length bound (reads into trailing padding).</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Philip's brief: the post office has two persistent singleton broadcast messages (leaflet @ 0x5DA, event_leaflet @ 0x704, PostOffice_c = 0x83C), each with a 4-bit recipient mask (leaflet_flags @ 0x830, event_flags @ 0x832; union with raw int; save checker rejects bits outside 0b1111). Implemented rust/src/leaflet.rs verified against m_post_office.h, m_post_office.c, ac_npc_post_man_move.c_inc, ac_event_manager.c, m_event.c, m_event_schedule.c_inc, m_shop.c, save_check.c_inc (GAFE01_00 Rev. 0). Ported: flag polarity 0 = pending / 1 = delivered (inverse of normal mail, per retail comment); init sets both masks to 0xF (raw = 0x000F000F); receipt_proc overwrites the singleton and resets its mask to 0 (new leaflet replaces undelivered one, no queue); per-house delivery (attempt only when bit is 0, unclaimed land_id 0xFFFF marked delivered without mail, foreign/Arbeit players skipped, full mailbox leaves bit 0 for retry); event-leaflet validity filter (SHOP_SALE_LEAFLET -&gt; mEv_EVENT_SHOP_SALE=26, BROKER_SALE_LEAFLET -&gt; mEv_EVENT_BROKER_SALE=29, else -1; expired handbills become undeliverable); handbill generation (shop-sale 4x4 template table 0x002-0x011 paper 55 with item-count/name/month/day/hour free strings; broker RANDOM(3) of 0x031-0x033 paper 54; rare-chirashi table {{18,18},{19,19},{21,20},{23,22}} paper ITM_PAPER55); ShopItsumoChirashi send_proc trap (only mPO_SENDTYPE_MAIL routes to broadcast receipt; traced caller passes LEAFLET -&gt; direct mailbox branch); postman check_delivery (normal OR leaflet-pending OR event-pending; Arbeit = normal only), set_delivery_idx scan, delivery_init order mail -&gt; leaflet -&gt; event leaflet; 09:00/17:00 delivery schedule; startup first_delivery_proc (normal mail, then catalog/ticket special mail, then leaflets). 7 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 20/20 brief claims confirmed verbatim. CORRECTION vs brief: special-event setup sets event_flags = 0b1111, which given 0 = pending marks all four DELIVERED (suppresses delivery by default) — the pending state comes from the handbill registration's receipt_proc (mask = 0); the brief's claim-20 reading was inverted.</t>
+          <t>Philip's brief: the post office has two persistent singleton broadcast messages (leaflet @ 0x5DA, event_leaflet @ 0x704, PostOffice_c = 0x83C), each with a 4-bit recipient mask (leaflet_flags @ 0x830, event_flags @ 0x832; union with raw int; save checker rejects bits outside 0b1111). Implemented rust/src/leaflet.rs verified against m_post_office.h, m_post_office.c, ac_npc_post_man_move.c_inc, ac_event_manager.c, m_event.c, m_event_schedule.c_inc, m_shop.c, save_check.c_inc (GAFE01_00 Rev. 0). Ported: flag polarity 0 = pending / 1 = delivered (inverse of normal mail, per retail comment); init sets both masks to 0xF (raw = 0x000F000F); receipt_proc overwrites the singleton and resets its mask to 0 (new leaflet replaces undelivered one, no queue); per-house delivery (attempt only when bit is 0, unclaimed land_id 0xFFFF marked delivered without mail, foreign/Arbeit players skipped, full mailbox leaves bit 0 for retry); event-leaflet validity filter (SHOP_SALE_LEAFLET -&gt; mEv_EVENT_SHOP_SALE=26, BROKER_SALE_LEAFLET -&gt; mEv_EVENT_BROKER_SALE=29, else -1; expired handbills become undeliverable); handbill generation (shop-sale 4x4 template table 0x002-0x011 paper 55 with item-count/name/month/day/hour free strings; broker RANDOM(3) of 0x031-0x033 paper 54; rare-chirashi table {{18,18},{19,19},{21,20},{23,22}} paper ITM_PAPER55); ShopItsumoChirashi send_proc trap (only mPO_SENDTYPE_MAIL routes to broadcast receipt; traced caller passes LEAFLET -&gt; direct mailbox branch); postman check_delivery (normal OR leaflet-pending OR event-pending; Arbeit = normal only), set_delivery_idx scan, delivery_init order mail -&gt; leaflet -&gt; event leaflet; 09:00/17:00 delivery schedule; startup first_delivery_proc (normal mail, then catalog/ticket special mail, then leaflets). 7 C ABI exports. cargo check --lib clean; tests written; authorized run 2026-10-08: 400/400 pass (leaflet+mother_mail+npc_reply fixes). Second verification pass: 20/20 brief claims confirmed verbatim. CORRECTION vs brief: special-event setup sets event_flags = 0b1111, which given 0 = pending marks all four DELIVERED (suppresses delivery by default) — the pending state comes from the handbill registration's receipt_proc (mask = 0); the brief's claim-20 reading was inverted.</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>High - verified against retail sources; tests not run per standing rule</t>
+          <t>High - verified against retail sources; tests pass 400/400 (2026-10-08 authorized run)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Philip's brief: per-player persistent Mom-mail scheduler with three pools. Implemented rust/src/mother_mail.rs verified against m_private.c, m_private.h, m_common_data.h, m_start_data_init.c, m_mail.h, m_event_schedule.c_inc (GAFE01_00 Rev. 0). Ported: save layout mother_mail[4] x 14 bytes (date + normal[7] + monthly[2] + august) in Save_t, not Private_c; clear sentinel FFFF/FF/FF; startup gates (local player, valid Private_c/ID); first-ever run stamps date only; single date != today check, no catch-up; Pool A fixed dates (birthday 0x184+RANDOM(2)+cake, month==day 0x164+(month-1)*2+RANDOM(2) with Jan1=10000 Bells and letter18=mushroom, Apr Fools 0x180, Mother's 0x17C, Father's 0x17E, Toy Day Dec24 0x182+random furniture; birthday precedence; Mother's/Father's via event status); Pool B 56 normal letters 0x12C-0x163, RANDOM(100)&lt;20 daily gate, uniform unsent selection, exhaustion zeroes whole data block then sends one Pool C letter; Pool C seasonal (2/month, 8 August; mail_start_no_table {0x18C,0x192,0x186,0x19E} literal; May=RANDOM(1) fortune shirt kept, Nov=mushroom, Dec=apple/RANDOM(6) shirts); normal presents (1/16 clothing, 3/21/22/47 other fruit, 12=1000 Bells, 37 doll, 38 dracaena, 40 umbrella); delivery house-mailbox-first then PO fallback, type 4 = mMl_TYPE_MOTHER; normal failure consumes day without marking letter, special failure leaves date for same-day retry; paper table {13,49,32,12,62,14,19,11,59,46,47,17} minus 1 with birthday/Jan1/Aug8/Dec24 overrides. Engine-resolved presents kept symbolic (PresentSpec); RNG injected as FnMut(u32)-&gt;u32 preserving call order. 4 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 19/19 claims confirmed verbatim (incl. m_start_data_init call sites, mMl_TYPE_MOTHER = 4, Mother's/Father's Day schedule macros, no Dec 25 branch, the unconditional date update in the normal path vs success-gated update in the special path). No corrections.</t>
+          <t>Philip's brief: per-player persistent Mom-mail scheduler with three pools. Implemented rust/src/mother_mail.rs verified against m_private.c, m_private.h, m_common_data.h, m_start_data_init.c, m_mail.h, m_event_schedule.c_inc (GAFE01_00 Rev. 0). Ported: save layout mother_mail[4] x 14 bytes (date + normal[7] + monthly[2] + august) in Save_t, not Private_c; clear sentinel FFFF/FF/FF; startup gates (local player, valid Private_c/ID); first-ever run stamps date only; single date != today check, no catch-up; Pool A fixed dates (birthday 0x184+RANDOM(2)+cake, month==day 0x164+(month-1)*2+RANDOM(2) with Jan1=10000 Bells and letter18=mushroom, Apr Fools 0x180, Mother's 0x17C, Father's 0x17E, Toy Day Dec24 0x182+random furniture; birthday precedence; Mother's/Father's via event status); Pool B 56 normal letters 0x12C-0x163, RANDOM(100)&lt;20 daily gate, uniform unsent selection, exhaustion zeroes whole data block then sends one Pool C letter; Pool C seasonal (2/month, 8 August; mail_start_no_table {0x18C,0x192,0x186,0x19E} literal; May=RANDOM(1) fortune shirt kept, Nov=mushroom, Dec=apple/RANDOM(6) shirts); normal presents (1/16 clothing, 3/21/22/47 other fruit, 12=1000 Bells, 37 doll, 38 dracaena, 40 umbrella); delivery house-mailbox-first then PO fallback, type 4 = mMl_TYPE_MOTHER; normal failure consumes day without marking letter, special failure leaves date for same-day retry; paper table {13,49,32,12,62,14,19,11,59,46,47,17} minus 1 with birthday/Jan1/Aug8/Dec24 overrides. Engine-resolved presents kept symbolic (PresentSpec); RNG injected as FnMut(u32)-&gt;u32 preserving call order. 4 C ABI exports. cargo check --lib clean; tests written; authorized run 2026-10-08: 400/400 pass (leaflet+mother_mail+npc_reply fixes). Second verification pass: 19/19 claims confirmed verbatim (incl. m_start_data_init call sites, mMl_TYPE_MOTHER = 4, Mother's/Father's Day schedule macros, no Dec 25 branch, the unconditional date update in the normal path vs success-gated update in the special path). No corrections.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>High - verified against retail sources; tests not run per standing rule</t>
+          <t>High - verified against retail sources; tests pass 400/400 (2026-10-08 authorized run)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Philip's brief: deterministic NPC reply pipeline (eligibility at receive time, generation at next startup) + mMck_check_key_hit_nes() scorer + mHandbillz_load() composer. Implemented rust/src/npc_reply.rs and machine-extracted rust/src/mck_key_tables.rs, verified against m_npc.c, m_mail_check_ovl.c, m_handbill.c, m_handbill.h, m_font.c, m_font_main.c_inc, m_msg_main.c_inc (GAFE01_00 Rev. 0). Ported: (1) mMck 7-component scorer over the 192-byte body (A final-punct +20 and per-separator +/-10, B +3/vocabulary hit, C first-char +20/-10, D -50 triple-alpha once, E space-ratio +/-20, F -150 run-on once, G -20/spaceless 32-block); 26 key tables extracted verbatim by script (max 89 pairs); rank &lt;50 BAD / 50-99 no reply / &gt;=100 OK via the nes path (length variant unused in USA). (2) Scheduler: receive stamps date, sets cond+send_reply only for BAD/OK; no 25% RNG behind the '// 25%' comment; first-job and letter-contest suppression; friendship +3/-5/+3; mNpc_Remail scans animals[] in order, later-calendar-date gate, break-on-PO-failure with pending retained, foreign remail via looks != 0x7F sentinel with no date check and clear-on-success-only. (3) Generation: BAD canned 0xC5/0xD8+looks*3+RANDOM(3), no present; GOOD RANDOM(4)&amp;1 present, category RANDOM(4)&amp;1, 11 RANDOM_F free-string rolls, five fragment indices (MAILB +16 half when present), random paper; mHandbillz composer as in-place buffer editor over a resource-provider trait (SUPER border/header_back_start adjustment, MAILA+B+C concat with 192 cap, PS pad, FREE/article/capital controls). CORRECTIONS vs brief: control-code ids are FREE0=37..FREE9=46, FREE10=55..FREE19=64, CUT_ARTICLE=117, CAPITAL_LETTER=118 (brief implied 36/116/117); foreign replies skip the letter-date check entirely. Documented deviations: mMck_cmp_key stops at table end (retail reads linker-adjacent bytes past the missing 0x7F terminator - unknowable from source); final ROM text needs retail assets the decomp excludes. 5 C ABI exports. cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass: 28/28 confirmed, 1 correction (#26): capital_flag is NOT cleared after each FREE insertion in retail USA - the clear call at the end of Put_String_FREE is itself the copy-paste bug, so once CAPITAL_LETTER fires the flag stays set for all later insertions (already modeled as a no-op in the Rust port). Also confirmed: RANDOM_F = fqrand() * n (sys_math.h:35); F inner scan has no length bound (reads into trailing padding).</t>
+          <t>Philip's brief: deterministic NPC reply pipeline (eligibility at receive time, generation at next startup) + mMck_check_key_hit_nes() scorer + mHandbillz_load() composer. Implemented rust/src/npc_reply.rs and machine-extracted rust/src/mck_key_tables.rs, verified against m_npc.c, m_mail_check_ovl.c, m_handbill.c, m_handbill.h, m_font.c, m_font_main.c_inc, m_msg_main.c_inc (GAFE01_00 Rev. 0). Ported: (1) mMck 7-component scorer over the 192-byte body (A final-punct +20 and per-separator +/-10, B +3/vocabulary hit, C first-char +20/-10, D -50 triple-alpha once, E space-ratio +/-20, F -150 run-on once, G -20/spaceless 32-block); 26 key tables extracted verbatim by script (max 89 pairs); rank &lt;50 BAD / 50-99 no reply / &gt;=100 OK via the nes path (length variant unused in USA). (2) Scheduler: receive stamps date, sets cond+send_reply only for BAD/OK; no 25% RNG behind the '// 25%' comment; first-job and letter-contest suppression; friendship +3/-5/+3; mNpc_Remail scans animals[] in order, later-calendar-date gate, break-on-PO-failure with pending retained, foreign remail via looks != 0x7F sentinel with no date check and clear-on-success-only. (3) Generation: BAD canned 0xC5/0xD8+looks*3+RANDOM(3), no present; GOOD RANDOM(4)&amp;1 present, category RANDOM(4)&amp;1, 11 RANDOM_F free-string rolls, five fragment indices (MAILB +16 half when present), random paper; mHandbillz composer as in-place buffer editor over a resource-provider trait (SUPER border/header_back_start adjustment, MAILA+B+C concat with 192 cap, PS pad, FREE/article/capital controls). CORRECTIONS vs brief: control-code ids are FREE0=37..FREE9=46, FREE10=55..FREE19=64, CUT_ARTICLE=117, CAPITAL_LETTER=118 (brief implied 36/116/117); foreign replies skip the letter-date check entirely. Documented deviations: mMck_cmp_key stops at table end (retail reads linker-adjacent bytes past the missing 0x7F terminator - unknowable from source); final ROM text needs retail assets the decomp excludes. 5 C ABI exports. cargo check --lib clean; tests written; authorized run 2026-10-08: 400/400 pass (leaflet+mother_mail+npc_reply fixes). Second verification pass: 28/28 confirmed, 1 correction (#26): capital_flag is NOT cleared after each FREE insertion in retail USA - the clear call at the end of Put_String_FREE is itself the copy-paste bug, so once CAPITAL_LETTER fires the flag stays set for all later insertions (already modeled as a no-op in the Rust port). Also confirmed: RANDOM_F = fqrand() * n (sys_math.h:35); F inner scan has no length bound (reads into trailing padding).</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>High - verified against retail sources; tests not run per standing rule</t>
+          <t>High - verified against retail sources; tests pass 400/400 (2026-10-08 authorized run)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K242"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6227,6 +6227,48 @@
         </is>
       </c>
       <c r="H242" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Save system - format, read/write, checksum</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Philip's brief: USA retail save path (m_flashrom.c, m_card.c, m_common_data.h, CARD I/O, main-load, save state machine, backup repair, aux mail/design/diary). Implemented rust/src/save_format.rs on top of the existing checksum primitives in save.rs, verified against m_card.c, m_flashrom.c, m_card.h, m_flashrom.h, m_common_data.h, m_land.h, m_lib.c, m_time.c (GAFE01_00 Rev. 0). Ported: 0x72000 land image (0x26000 misc + main @0x26000 + backup @0x4C000; mCD_get_offset sums prior file-table entries); Save = Save_t (0x242A0) padded to 0x26000 with checksum over the whole slot incl. padding; save-check header (version s32 @0x00, 'GAFE' u32 @0x04, land_id u16 @0x08 with (id &amp; 0xFF00) == 0x3000 check, RTC @0x0A, checksum u16 @0x12); writer emits v6, loader accepts v5/v6; candidate validation order identity-&gt;checksum-&gt;version; main preferred, backup load flags mCD_ERROR_OUTDATED; check_broken_land repairs only on exactly-one-good; sector compare-before-write (mem_cmp returns TRUE when equal, so ==0 means different-&gt;write); aux keep blocks mail 0xBAC0 @0x1440 / original 0xCCA0 @0xCF00 / diary 0xBA20 @0x19BA0 with checksum as first u16, forgiving per-block load, writer order mail/original/diary (diary gets no landid); copy_protect Save_t+0x1A, RANDOM(0xFFF0)+1, card-association only, separate from checksum. CORRECTION vs brief sources: m_common_data.h names a second copy_protect at 0x028596 (duplicate member = decomp artifact, cannot compile); the operative field is the 0x1A one since mCD_check_copyProtect only reads the first 0x200 bytes. Documented gaps: exact 0x40-byte retail GCI dir entry unverified (needs a real USA GCI); banner/icon/comment bytes are ROM resources (provider-supplied); noLand protect-code handshake not modeled (CARD-level). 5 C ABI exports (pc_savef_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass pending at commit time.</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>rust/src/save_format.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6240,7 +6240,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Philip's brief: USA retail save path (m_flashrom.c, m_card.c, m_common_data.h, CARD I/O, main-load, save state machine, backup repair, aux mail/design/diary). Implemented rust/src/save_format.rs on top of the existing checksum primitives in save.rs, verified against m_card.c, m_flashrom.c, m_card.h, m_flashrom.h, m_common_data.h, m_land.h, m_lib.c, m_time.c (GAFE01_00 Rev. 0). Ported: 0x72000 land image (0x26000 misc + main @0x26000 + backup @0x4C000; mCD_get_offset sums prior file-table entries); Save = Save_t (0x242A0) padded to 0x26000 with checksum over the whole slot incl. padding; save-check header (version s32 @0x00, 'GAFE' u32 @0x04, land_id u16 @0x08 with (id &amp; 0xFF00) == 0x3000 check, RTC @0x0A, checksum u16 @0x12); writer emits v6, loader accepts v5/v6; candidate validation order identity-&gt;checksum-&gt;version; main preferred, backup load flags mCD_ERROR_OUTDATED; check_broken_land repairs only on exactly-one-good; sector compare-before-write (mem_cmp returns TRUE when equal, so ==0 means different-&gt;write); aux keep blocks mail 0xBAC0 @0x1440 / original 0xCCA0 @0xCF00 / diary 0xBA20 @0x19BA0 with checksum as first u16, forgiving per-block load, writer order mail/original/diary (diary gets no landid); copy_protect Save_t+0x1A, RANDOM(0xFFF0)+1, card-association only, separate from checksum. CORRECTION vs brief sources: m_common_data.h names a second copy_protect at 0x028596 (duplicate member = decomp artifact, cannot compile); the operative field is the 0x1A one since mCD_check_copyProtect only reads the first 0x200 bytes. Documented gaps: exact 0x40-byte retail GCI dir entry unverified (needs a real USA GCI); banner/icon/comment bytes are ROM resources (provider-supplied); noLand protect-code handshake not modeled (CARD-level). 5 C ABI exports (pc_savef_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass pending at commit time.</t>
+          <t>Philip's brief: USA retail save path (m_flashrom.c, m_card.c, m_common_data.h, CARD I/O, main-load, save state machine, backup repair, aux mail/design/diary). Implemented rust/src/save_format.rs on top of the existing checksum primitives in save.rs, verified against m_card.c, m_flashrom.c, m_card.h, m_flashrom.h, m_common_data.h, m_land.h, m_lib.c, m_time.c (GAFE01_00 Rev. 0). Ported: 0x72000 land image (0x26000 misc + main @0x26000 + backup @0x4C000; mCD_get_offset sums prior file-table entries); Save = Save_t (0x242A0) padded to 0x26000 with checksum over the whole slot incl. padding; save-check header (version s32 @0x00, 'GAFE' u32 @0x04, land_id u16 @0x08 with (id &amp; 0xFF00) == 0x3000 check, RTC @0x0A, checksum u16 @0x12); writer emits v6, loader accepts v5/v6; candidate validation order identity-&gt;checksum-&gt;version; main preferred, backup load flags mCD_ERROR_OUTDATED; check_broken_land repairs only on exactly-one-good; sector compare-before-write (mem_cmp returns TRUE when equal, so ==0 means different-&gt;write); aux keep blocks mail 0xBAC0 @0x1440 / original 0xCCA0 @0xCF00 / diary 0xBA20 @0x19BA0 with checksum as first u16, forgiving per-block load, writer order mail/original/diary (diary gets no landid); copy_protect Save_t+0x1A, RANDOM(0xFFF0)+1, card-association only, separate from checksum. CORRECTION vs brief sources: m_common_data.h names a second copy_protect at 0x028596 (duplicate member = decomp artifact, cannot compile); the operative field is the 0x1A one since mCD_check_copyProtect only reads the first 0x200 bytes. Documented gaps: exact 0x40-byte retail GCI dir entry unverified (needs a real USA GCI); banner/icon/comment bytes are ROM resources (provider-supplied); noLand protect-code handshake not modeled (CARD-level). 5 C ABI exports (pc_savef_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification: 20/20 claims checked - 17 confirmed, 3 corrections: (a) save-time mutations (save_exist/copy_protect/travel_hard_time/reset-code/Wisp) hit the LIVE save pre-copy; only version/save-check/checksum are set post-copy (build_save_slot docstring corrected, bytes identical); (b) decomp mCD_keep_original_c fields sum to 0xCC68 not 0xCCA0 - decomp struct missing 0x38 bytes, comment/PC-port log say 0xCCA0, so 0xCCA0 kept with the discrepancy documented in code; (c) write_others' OTHERS_SIZE+2*sizeof(Save) is the asserted on-card file length, not the write byte count. Also confirmed: duplicate copy_protect at 0x028596 is a non-compiling decomp artifact (operative field 0x1A); mem_cmp returns TRUE when equal so ==0 means different-&gt;write; version-5 time copy happens after the whole search.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K243"/>
+  <dimension ref="A1:K244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6269,6 +6269,48 @@
         </is>
       </c>
       <c r="H243" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Audio - game layer (Na_*) beyond letter scoring</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Philip's brief: full retail audio stack (sAdo_* -&gt; Na_* -&gt; Nap_* command port -&gt; JAudio -&gt; NEOS/DSP/AI). Implemented rust/src/audio.rs, verified against src/audio.c, src/static/jaudio_NES/game/game64.c_inc, include/jaudio_NES/audiocommon.h, audiostruct.h, sub_sys.c, include/m_config.h (GAFE01_00 Rev. 0). Ported the Na_* game layer as stateful virtual sound sources + deferred 256-entry AudioPort command ring (retail capacity 256; PC port uses 2048): 5 groups (SE=0/BGM0=1/FTR=2/BGM1=3/VOICE=4) with BGM0/BGM1 crossfade alternation; 16 subtracks/group; sound-ID flag nibble (MONO 0x1000/DIST_REVERB 0x2000/ECHO 0x4000/SINGLETON 0x8000); 6 trigger-SE slots (MONO subtrack-14 bypass, singleton rejection, oldest-frames+TRGPRIO replacement, per-frame pushes); positional math (quadratic distance2vol over 540u, angle2pan+pan_kochou with out-mode x1.6/x1/x0.75, MD curve [0.2,0.8]); 6 level-SE slots x 8 history; 50-entry ongen cache + 4 active slots; 50 room insects; 2 alternating voice slots with Animalese/Click/Silent modes, spec-&gt;seq 243/244/245 and per-spec vol/pitch table; BGM mute tables verbatim (fine/snow/sakura 24 each, museum 6) with weather masking + 0x45 substitution; furniture instruments + 14 rhythm buffers on group 2; scene audio state. Preserved quirks: kiteki dead-branch/negative volume, ROOM_TYPE_OTHER AREA2 bug, insect variance j=0 restart, foundIndex slot-0. Documented safety deviations: TRGPRIO OOB (120-entry, no retail bounds check) returns None; level-fade 8..14 indexing noted not reproduced. Engine constants captured (24 AGC chans, 0x90000 heap, 0x810000 ARAM, 7x560 triple-buffer DAC, 64 DSP chans). JAudio sequence VM / ADPCM / DSP mixer / ROM assets stay engine-side behind the command boundary. 5 C ABI exports (pc_audio_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass pending at commit time.</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>rust/src/audio.rs (new, registered in lib.rs); DOCUMENTATION.md section. cargo check --lib clean.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>High - verified against retail sources; tests not run per standing rule</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Philip's brief: full retail audio stack (sAdo_* -&gt; Na_* -&gt; Nap_* command port -&gt; JAudio -&gt; NEOS/DSP/AI). Implemented rust/src/audio.rs, verified against src/audio.c, src/static/jaudio_NES/game/game64.c_inc, include/jaudio_NES/audiocommon.h, audiostruct.h, sub_sys.c, include/m_config.h (GAFE01_00 Rev. 0). Ported the Na_* game layer as stateful virtual sound sources + deferred 256-entry AudioPort command ring (retail capacity 256; PC port uses 2048): 5 groups (SE=0/BGM0=1/FTR=2/BGM1=3/VOICE=4) with BGM0/BGM1 crossfade alternation; 16 subtracks/group; sound-ID flag nibble (MONO 0x1000/DIST_REVERB 0x2000/ECHO 0x4000/SINGLETON 0x8000); 6 trigger-SE slots (MONO subtrack-14 bypass, singleton rejection, oldest-frames+TRGPRIO replacement, per-frame pushes); positional math (quadratic distance2vol over 540u, angle2pan+pan_kochou with out-mode x1.6/x1/x0.75, MD curve [0.2,0.8]); 6 level-SE slots x 8 history; 50-entry ongen cache + 4 active slots; 50 room insects; 2 alternating voice slots with Animalese/Click/Silent modes, spec-&gt;seq 243/244/245 and per-spec vol/pitch table; BGM mute tables verbatim (fine/snow/sakura 24 each, museum 6) with weather masking + 0x45 substitution; furniture instruments + 14 rhythm buffers on group 2; scene audio state. Preserved quirks: kiteki dead-branch/negative volume, ROOM_TYPE_OTHER AREA2 bug, insect variance j=0 restart, foundIndex slot-0. Documented safety deviations: TRGPRIO OOB (120-entry, no retail bounds check) returns None; level-fade 8..14 indexing noted not reproduced. Engine constants captured (24 AGC chans, 0x90000 heap, 0x810000 ARAM, 7x560 triple-buffer DAC, 64 DSP chans). JAudio sequence VM / ADPCM / DSP mixer / ROM assets stay engine-side behind the command boundary. 5 C ABI exports (pc_audio_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification pass pending at commit time.</t>
+          <t>Philip's brief: full retail audio stack (sAdo_* -&gt; Na_* -&gt; Nap_* command port -&gt; JAudio -&gt; NEOS/DSP/AI). Implemented rust/src/audio.rs, verified against src/audio.c, src/static/jaudio_NES/game/game64.c_inc, include/jaudio_NES/audiocommon.h, audiostruct.h, sub_sys.c, include/m_config.h (GAFE01_00 Rev. 0). Ported the Na_* game layer as stateful virtual sound sources + deferred 256-entry AudioPort command ring (retail capacity 256; PC port uses 2048): 5 groups (SE=0/BGM0=1/FTR=2/BGM1=3/VOICE=4) with BGM0/BGM1 crossfade alternation; 16 subtracks/group; sound-ID flag nibble (MONO 0x1000/DIST_REVERB 0x2000/ECHO 0x4000/SINGLETON 0x8000); 6 trigger-SE slots (MONO subtrack-14 bypass, singleton rejection, oldest-frames+TRGPRIO replacement, per-frame pushes); positional math (quadratic distance2vol over 540u, angle2pan+pan_kochou with out-mode x1.6/x1/x0.75, MD curve [0.2,0.8]); 6 level-SE slots x 8 history; 50-entry ongen cache + 4 active slots; 50 room insects; 2 alternating voice slots with Animalese/Click/Silent modes, spec-&gt;seq 243/244/245 and per-spec vol/pitch table; BGM mute tables verbatim (fine/snow/sakura 24 each, museum 6) with weather masking + 0x45 substitution; furniture instruments + 14 rhythm buffers on group 2; scene audio state. Preserved quirks: kiteki dead-branch/negative volume, ROOM_TYPE_OTHER AREA2 bug, insect variance j=0 restart, foundIndex slot-0. Documented safety deviations: TRGPRIO OOB (120-entry, no retail bounds check) returns None; level-fade 8..14 indexing noted not reproduced. Engine constants captured (24 AGC chans, 0x90000 heap, 0x810000 ARAM, 7x560 triple-buffer DAC, 64 DSP chans). JAudio sequence VM / ADPCM / DSP mixer / ROM assets stay engine-side behind the command boundary. 5 C ABI exports (pc_audio_*). cargo check --lib clean; tests written but NOT run (standing rule). Second verification: 18/18 checked, 16 confirmed, 2 corrections folded: (a) TRGPRIO has 128 entries (97x50, 8x60 at 97-104, 23x70 at 105-127), not 120 - table and tests corrected; (b) level-SE architecture corrected: the 8-byte per-slot list is a dedup/pending list (never populated with nonzero bytes in the decomp snapshot), the push FIFO sou_ls_stack is 4 deep - LevSeManager rewritten. Also verified verbatim: Na_RoomType case values (0: 540/untouched, 1: 540/545, 2: 470/520, 3: 510/545); room_areas replaced with na_room_type. OOB quirk itself confirmed (indices 128+ read past the table).</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K244"/>
+  <dimension ref="A1:K245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6313,6 +6313,16 @@
       <c r="H244" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>245</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>RESEARCH: Graphics pipeline (GBI/emu64). FINDINGS: retail renderer is a hybrid - N64/libultra-derived Gfx command representation interpreted at runtime by emu64_taskstart (fetch/decode/dispatch via dl_func_tbl[opcode - G_FIRST_CMD], 64 handlers) with GX/TEV/texture as the backend. G_DL supports PUSH/NOPUSH plus a native-GX-display-list target (G_DL_GXDL=2, gGXCallDisplayList); DL stack 18 deep, overflow counted not fatal; 16 segments resolved by seg2k0/segchk; billboard matrix in segment 7; animated textures in segments 0x08-0x0D. Custom packed-triangle commands G_TRIN=0x09/G_TRIN_INDEPEND=0x0A with verbatim POLY_GET_V*_5b/7b macros; 5-bit = 3 faces first then 4/word, faces = ((w0&gt;&gt;17)&amp;0x7F)+1. Vertex path: s16-&gt;f32, normals normalized under G_TEXTURE_GEN, shared/nonshared matrix flag (texgen forces shared, SHARED_MTX=GX_PNMTX0). Textures: verbatim fmtxtbl[8][4] (CI16=0xA special), cvtN64ToDol 0xFFFF-&gt;GX_TF_I4, verbatim rgba5551_to_rgb5a3, block sizes 8x8/8x4/4x4, TMEM swizzle ofs^((block&gt;&gt;1)&amp;4), IA8 nibble rearrange, 4-bit u32-chunk copies, source-address-keyed cache + separate TLUT path, Dolphin commands are isDolphin bit variants with wd+1 x (ht+1)*4 dims. Combiner: combine_auto/tev/manual + G_SETCOMBINE_TEV=0xD0/NOTEV=0xCF, TEXEL1 fallback, 1-cycle vs 2-cycle stages. Nine display-list streams (POLY_OPA/XLU, OVERLAY, WORK, FONT, SHADOW, LIGHT, BG_OPA/XLU); z_gsCPModeSet_Data material presets; 640x480 logical frame; customized NTSC modes (XFB 660, viXOrigin 30, DF filter 8/8/10/12/10/8/8, SF 0/0/21/22/21/0/0). GX DLs need 32-byte addr+size alignment; EFB-&gt;texture wipe path via native GX DL; player design texture 32x32 4-bit = 512 bytes. IMPLEMENTATION: new rust/src/graphics/ (10 files) + 8 pc_gbi_* C ABI exports; GbiState with dirty flags; Emu64 taskstart interpreter; GfxMemory/GxBackend traits keep GX FIFO emission and RAM emulation engine-side. Second verification: 18/18 checked, 16 confirmed, 2 corrected + bit-level bugs fixed: Gsetimg2 fmt/siz extraction inverted (fmt bits 21-23, siz 19-20); TEXRECT = 3 words, corners ulx/uly from w0; G_MTX PUSH=0x01/NOPUSH=0x00 push-on-bit-clear, type in w0 bits 0-7; decal bits 4-5, G_LIGHTING_POSITIONAL=0x400000; G_VTX n raw + v0=(vn&gt;&gt;1)-n; TRIN indices NOT halved + per-word 5b/7b; plain SETTILE has no Dolphin bit (0xD2 handler added); TEXRECTFLIP = no-op. Added TLUT IA16 rejection, misc-opcode arms, 15x6 preset dims. Open: G_QUADN, G_SPECIAL_*. cargo check --lib clean; tests written but NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K245"/>
+  <dimension ref="A1:K246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6323,6 +6323,16 @@
       <c r="B245" t="inlineStr">
         <is>
           <t>RESEARCH: Graphics pipeline (GBI/emu64). FINDINGS: retail renderer is a hybrid - N64/libultra-derived Gfx command representation interpreted at runtime by emu64_taskstart (fetch/decode/dispatch via dl_func_tbl[opcode - G_FIRST_CMD], 64 handlers) with GX/TEV/texture as the backend. G_DL supports PUSH/NOPUSH plus a native-GX-display-list target (G_DL_GXDL=2, gGXCallDisplayList); DL stack 18 deep, overflow counted not fatal; 16 segments resolved by seg2k0/segchk; billboard matrix in segment 7; animated textures in segments 0x08-0x0D. Custom packed-triangle commands G_TRIN=0x09/G_TRIN_INDEPEND=0x0A with verbatim POLY_GET_V*_5b/7b macros; 5-bit = 3 faces first then 4/word, faces = ((w0&gt;&gt;17)&amp;0x7F)+1. Vertex path: s16-&gt;f32, normals normalized under G_TEXTURE_GEN, shared/nonshared matrix flag (texgen forces shared, SHARED_MTX=GX_PNMTX0). Textures: verbatim fmtxtbl[8][4] (CI16=0xA special), cvtN64ToDol 0xFFFF-&gt;GX_TF_I4, verbatim rgba5551_to_rgb5a3, block sizes 8x8/8x4/4x4, TMEM swizzle ofs^((block&gt;&gt;1)&amp;4), IA8 nibble rearrange, 4-bit u32-chunk copies, source-address-keyed cache + separate TLUT path, Dolphin commands are isDolphin bit variants with wd+1 x (ht+1)*4 dims. Combiner: combine_auto/tev/manual + G_SETCOMBINE_TEV=0xD0/NOTEV=0xCF, TEXEL1 fallback, 1-cycle vs 2-cycle stages. Nine display-list streams (POLY_OPA/XLU, OVERLAY, WORK, FONT, SHADOW, LIGHT, BG_OPA/XLU); z_gsCPModeSet_Data material presets; 640x480 logical frame; customized NTSC modes (XFB 660, viXOrigin 30, DF filter 8/8/10/12/10/8/8, SF 0/0/21/22/21/0/0). GX DLs need 32-byte addr+size alignment; EFB-&gt;texture wipe path via native GX DL; player design texture 32x32 4-bit = 512 bytes. IMPLEMENTATION: new rust/src/graphics/ (10 files) + 8 pc_gbi_* C ABI exports; GbiState with dirty flags; Emu64 taskstart interpreter; GfxMemory/GxBackend traits keep GX FIFO emission and RAM emulation engine-side. Second verification: 18/18 checked, 16 confirmed, 2 corrected + bit-level bugs fixed: Gsetimg2 fmt/siz extraction inverted (fmt bits 21-23, siz 19-20); TEXRECT = 3 words, corners ulx/uly from w0; G_MTX PUSH=0x01/NOPUSH=0x00 push-on-bit-clear, type in w0 bits 0-7; decal bits 4-5, G_LIGHTING_POSITIONAL=0x400000; G_VTX n raw + v0=(vn&gt;&gt;1)-n; TRIN indices NOT halved + per-word 5b/7b; plain SETTILE has no Dolphin bit (0xD2 handler added); TEXRECTFLIP = no-op. Added TLUT IA16 rejection, misc-opcode arms, 15x6 preset dims. Open: G_QUADN, G_SPECIAL_*. cargo check --lib clean; tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>246</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>RESEARCH: Non-letter NPC-generated mail (m_npc.c, USA retail). FINDINGS: four independent systems + password protocol, not one reply generator. (1) Valentine event mail: relationship classifier (best==opp-best -&gt; BEST_FRIEND else opp-best with friendship&gt;=80 -&gt; OK_FRIEND else NOT_FRIEND), present tables {RARE,UNCOMMON,COMMON}x{FURNITURE,FURNITURE,CLOTH}, mail_no=0x60+looks*3+type, FREE_STR0/6=player/NPC, scheduler classifies all 15 villagers then processes BEST-&gt;OK-&gt;NOT with player failure bitfield (0b1111, cleared per-player on failure, routine ends at 0), mailbox-&gt;PO delivery. (2) Birthday: mail_no=0xEA+looks*3+RANDOM(3), present RANDOM(5) 40/40/20 furniture/clothing/umbrella, FREE_STR0/1/2, eligibility=highest-friendship + not birthday_present_npc, all eligible send in order, mailbox-&gt;PO. (3) Christmas: fixed 0xD7/XMAS/Famicom/paper22, no RNG, mailbox-only, bypasses common constructor. (4) Goodbye: static pending {id,bitfield}, 4-bit retry mask, mail_no=0x20E+looks*3+mQst_GetRandom(3) (quest RNG), FREE_STR0/1/3, no present, survives Animal_c clear. (5) Password mail: hp_mail[4] {receive_time,password[20]}, ReceiveHPMail intercepts NPC mail, @BUG full-length copy, &gt;=1 day delay, 6-generator dispatch, Famicom 0x24A/0x250, Popular 0x256/0x25C/0x262/0x268+code/0x288, Magazine 0x2A0/0x2A6/0x2AC with {80,60,30,0,100}, Card-E {80,60,40,20}, invalid still responds, sender overwrite, clear-on-success-only. Shared: LoadMailDataCommon2, GetPaperType (ABC), 3 delivery policies; GeneratedMail vs DeliveryResult split. IMPLEMENTATION: new rust/src/npc_event_mail.rs (5 systems + shared lower level), 5 pc_npcmail_* C ABI exports, MailRng trait keeping RANDOM vs mQst_GetRandom distinct, PresentRequest as engine-resolved symbolic (item selection stays engine-side). Second verification: 16/16 checked, 14 confirmed, 1 corrected, 1 caveat fixed. CORRECTION: Card-E message bases were wrong (the brief's 0x2B2/0x288/0x268/0x3BE summary mis-assigned paths); retail is hit+islander 0x3CA+looks, hit+normal 0x3C4+looks, valid-miss 0x2B2+npc_code, special 0x39E+npc_code, invalid 0x3BE+looks. Added: user_password/cardE_mini generators (valid 0x3D0+looks, invalid 0x3BE+looks), Card-E FREE_STR5/present rules noted, Popular recipient overwrite + SPNPC_PASSWORD type, birthday year-reset state. CAVEAT FIXED: the HP-mail @BUG is a genuine 1-byte overrun (21 bytes into password[20]); the port stores &lt;=20 as a documented safety deviation. cargo check --lib clean; tests written but NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K246"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6333,6 +6333,16 @@
       <c r="B246" t="inlineStr">
         <is>
           <t>RESEARCH: Non-letter NPC-generated mail (m_npc.c, USA retail). FINDINGS: four independent systems + password protocol, not one reply generator. (1) Valentine event mail: relationship classifier (best==opp-best -&gt; BEST_FRIEND else opp-best with friendship&gt;=80 -&gt; OK_FRIEND else NOT_FRIEND), present tables {RARE,UNCOMMON,COMMON}x{FURNITURE,FURNITURE,CLOTH}, mail_no=0x60+looks*3+type, FREE_STR0/6=player/NPC, scheduler classifies all 15 villagers then processes BEST-&gt;OK-&gt;NOT with player failure bitfield (0b1111, cleared per-player on failure, routine ends at 0), mailbox-&gt;PO delivery. (2) Birthday: mail_no=0xEA+looks*3+RANDOM(3), present RANDOM(5) 40/40/20 furniture/clothing/umbrella, FREE_STR0/1/2, eligibility=highest-friendship + not birthday_present_npc, all eligible send in order, mailbox-&gt;PO. (3) Christmas: fixed 0xD7/XMAS/Famicom/paper22, no RNG, mailbox-only, bypasses common constructor. (4) Goodbye: static pending {id,bitfield}, 4-bit retry mask, mail_no=0x20E+looks*3+mQst_GetRandom(3) (quest RNG), FREE_STR0/1/3, no present, survives Animal_c clear. (5) Password mail: hp_mail[4] {receive_time,password[20]}, ReceiveHPMail intercepts NPC mail, @BUG full-length copy, &gt;=1 day delay, 6-generator dispatch, Famicom 0x24A/0x250, Popular 0x256/0x25C/0x262/0x268+code/0x288, Magazine 0x2A0/0x2A6/0x2AC with {80,60,30,0,100}, Card-E {80,60,40,20}, invalid still responds, sender overwrite, clear-on-success-only. Shared: LoadMailDataCommon2, GetPaperType (ABC), 3 delivery policies; GeneratedMail vs DeliveryResult split. IMPLEMENTATION: new rust/src/npc_event_mail.rs (5 systems + shared lower level), 5 pc_npcmail_* C ABI exports, MailRng trait keeping RANDOM vs mQst_GetRandom distinct, PresentRequest as engine-resolved symbolic (item selection stays engine-side). Second verification: 16/16 checked, 14 confirmed, 1 corrected, 1 caveat fixed. CORRECTION: Card-E message bases were wrong (the brief's 0x2B2/0x288/0x268/0x3BE summary mis-assigned paths); retail is hit+islander 0x3CA+looks, hit+normal 0x3C4+looks, valid-miss 0x2B2+npc_code, special 0x39E+npc_code, invalid 0x3BE+looks. Added: user_password/cardE_mini generators (valid 0x3D0+looks, invalid 0x3BE+looks), Card-E FREE_STR5/present rules noted, Popular recipient overwrite + SPNPC_PASSWORD type, birthday year-reset state. CAVEAT FIXED: the HP-mail @BUG is a genuine 1-byte overrun (21 bytes into password[20]); the port stores &lt;=20 as a documented safety deviation. cargo check --lib clean; tests written but NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>247</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Authorized test run #10 (2026-10-08): Philip said 'Run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Four initial failures were all wrong test expectations in the new modules (implementation matched retail): graphics DL-push test used a nonzero segment base so the nested address resolved wrong; rgba5551 test guessed 0x1FFE for 0xFFFE (retail formula gives 0x0FFF); TMEM swizzle test picked an offset whose block doesn't set bit 2; Valentine classifier test forgot lowering player 0's friendship changes the max-friendship pick. One pre-existing infrastructure fix: save_format's repair_copies_good_over_broken overflowed the 2MB test-thread stack (471KB + 155KB images on the stack) and aborted the whole suite; build_land_image/repair_land now return Box&lt;[u8; N]&gt; and the tests box their arrays (Rust-side only, no C ABI impact). Standing no-tests rule still applies going forward.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K247"/>
+  <dimension ref="A1:K248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6343,6 +6343,16 @@
       <c r="B247" t="inlineStr">
         <is>
           <t>Authorized test run #10 (2026-10-08): Philip said 'Run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Four initial failures were all wrong test expectations in the new modules (implementation matched retail): graphics DL-push test used a nonzero segment base so the nested address resolved wrong; rgba5551 test guessed 0x1FFE for 0xFFFE (retail formula gives 0x0FFF); TMEM swizzle test picked an offset whose block doesn't set bit 2; Valentine classifier test forgot lowering player 0's friendship changes the max-friendship pick. One pre-existing infrastructure fix: save_format's repair_copies_good_over_broken overflowed the 2MB test-thread stack (471KB + 155KB images on the stack) and aborted the whole suite; build_land_image/repair_land now return Box&lt;[u8; N]&gt; and the tests box their arrays (Rust-side only, no C ABI impact). Standing no-tests rule still applies going forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>248</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Showcase 2: Walkabout edition (2026-10-08): new showcase generator (showcase/src/bin/showcase2.rs + template + graphics_shim.rs) producing rustimal-showcase-2.html with 4 tabs, all data computed from the real Rust code: (1) Walkabout — third-person WebGL town walk (WASD/arrows, follow camera, walkability bitmap from town_gen cells + river strips, houses/trees block, elevation-aware actors), 6 wandering NPC villagers with real personalities (mNpc_LOOKS order), real SCHEDULE_TABLES states at 10:00 (FIELD wanderers vs IN_HOUSE stay-homes), walk-up + E to talk: real talk_topics probability trees ({40,30,10,10,10} KI / {70,30} NORMAL / {15,35,35,15} / {49,17,17,17} / {40,60}), message-ID formulas, friendship +8 (GREETING_RELATION_BUMP), illustrative lines clearly marked non-retail (message text is ROM-side). (2) Mailroom — 13 sample mails from the real npc_event_mail.rs generators (Valentine x3, birthday, Christmas, goodbye, Famicom valid/invalid, magazine win/lose/invalid, user-password valid/invalid) with message numbers, presents, papers, delivery policy. (3) Graphics Lab — steppable trace of the real Emu64 interpreter over a 10-command DL (state setup, VTX, TRI1, G_DL PUSH into nested list, packed G_TRIN, ENDDL pop), per-command dirty flags with newly-dirtied highlighting. (4) Sound Board — scripted GameAudio session: slot allocation, singleton rejection, oldest-frames TRGPRIO replacement, MONO bypass, voice spec-&gt;seq 243, ring backlog. Verification win: retail dl_func_tbl confirms the dispatch index is WRAPPING u8 (opcode - G_FIRST_CMD), indices 51-63 = opcodes 0x00-0x0D (G_VTX-&gt;51, G_TRI1-&gt;55, G_TRIN-&gt;59, G_QUADN-&gt;63); the port already models this. Added CmdTrace diagnostic + DirtySet::all() to the graphics module. All 5 JS blocks pass node --check. Standing no-tests rule still applies.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K248"/>
+  <dimension ref="A1:K249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6353,6 +6353,16 @@
       <c r="B248" t="inlineStr">
         <is>
           <t>Showcase 2: Walkabout edition (2026-10-08): new showcase generator (showcase/src/bin/showcase2.rs + template + graphics_shim.rs) producing rustimal-showcase-2.html with 4 tabs, all data computed from the real Rust code: (1) Walkabout — third-person WebGL town walk (WASD/arrows, follow camera, walkability bitmap from town_gen cells + river strips, houses/trees block, elevation-aware actors), 6 wandering NPC villagers with real personalities (mNpc_LOOKS order), real SCHEDULE_TABLES states at 10:00 (FIELD wanderers vs IN_HOUSE stay-homes), walk-up + E to talk: real talk_topics probability trees ({40,30,10,10,10} KI / {70,30} NORMAL / {15,35,35,15} / {49,17,17,17} / {40,60}), message-ID formulas, friendship +8 (GREETING_RELATION_BUMP), illustrative lines clearly marked non-retail (message text is ROM-side). (2) Mailroom — 13 sample mails from the real npc_event_mail.rs generators (Valentine x3, birthday, Christmas, goodbye, Famicom valid/invalid, magazine win/lose/invalid, user-password valid/invalid) with message numbers, presents, papers, delivery policy. (3) Graphics Lab — steppable trace of the real Emu64 interpreter over a 10-command DL (state setup, VTX, TRI1, G_DL PUSH into nested list, packed G_TRIN, ENDDL pop), per-command dirty flags with newly-dirtied highlighting. (4) Sound Board — scripted GameAudio session: slot allocation, singleton rejection, oldest-frames TRGPRIO replacement, MONO bypass, voice spec-&gt;seq 243, ring backlog. Verification win: retail dl_func_tbl confirms the dispatch index is WRAPPING u8 (opcode - G_FIRST_CMD), indices 51-63 = opcodes 0x00-0x0D (G_VTX-&gt;51, G_TRI1-&gt;55, G_TRIN-&gt;59, G_QUADN-&gt;63); the port already models this. Added CmdTrace diagnostic + DirtySet::all() to the graphics module. All 5 JS blocks pass node --check. Standing no-tests rule still applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>249</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Wave 2 — C-struct boundary corrections (2026-10-08): studied the ABI-analysis brief, re-verified every consequential claim against the USA Rev. 0 decomp (acgc-upstream), and applied the Rust-side corrections. VERIFIED VERBATIM: aQMgr_decide_idx_prob_table shuffle (100-entry table, 30x RANDOM(100) swap pairs, final RANDOM(100) = 61 RNG calls); mail-receive friendship +3 / -5-if-BAD / +3-if-present; mQst_GetGoods_common RANDOM(10) branch; mFI_LineDepositON/OFF + mFI_GetLineDeposit row-pointer API; game_get_next_game_dlftbl init-pointer comparison chain; shop thresholds 25000/90000/240000; wander borders girl{3,6} ko-girl{6,8} boy{5,7} sport{2,4} grim{3,6} naniwa{4,8}; aNPC_chk_avoid_and_search (&lt;0 avoid, &gt;128 search on *friendship+over_friendship, same-block gated); mNpc_GetOverImpatient indexed by looks. NEW QUIRK FOUND: l_npc_temper is declared per-feeling [mNpc_FEEL_NUM] but indexed by looks (personality) everywhere (mNpc_TalkEndMove bounds-checks looks against mNpc_LOOKS_NUM) — the port now preserves this. BRIEF CORRECTION: 'FIX 4' (0.0099999998f) is a mirage — 0.01f32 == 0x3C23D70A, bit-identical to retail's 0.01f; documented, not changed. RUST CHANGES: request_selector — pick_random_eligible takes &amp;[u8] (no Vec&lt;bool&gt; alloc), decide_idx_prob_table runs the verbatim shuffle via shared talk_topics impl with C RNG callback (ABI CHANGE on pc_request_dispatch: (probs,n,roll) -&gt; (probs,n,rng callback), nothing wired yet); behavior — letter_friendship_delta +3/-5/+3, and the m_quest.h BONUS constants were for quest rank not friendship (old code conflated the systems); player_move — locomotion_core documented as classification helper only; buried_items — new pc_buried_line_get/set/clear exact-boundary exports; interaction — temper indexed by looks, pc_npc_patience(talk_num, looks); item_prefs — select_reward_furniture takes bounded selected_index; scene/npc/collision/town_gen — boundary docs (pointer scan stays in C; saved_type bridge; TownPlan != mRF_MakeRandomField). Rule established: Rust never owns the retail RNG call — C passes RANDOM(n) or a callback. C-side items (CMake dep list, USE_RUST rewires, PcPlayerMoveState) are Philip's-tree work, noted for him. cargo check clean; tests NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:K250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6363,6 +6363,16 @@
       <c r="B249" t="inlineStr">
         <is>
           <t>Wave 2 — C-struct boundary corrections (2026-10-08): studied the ABI-analysis brief, re-verified every consequential claim against the USA Rev. 0 decomp (acgc-upstream), and applied the Rust-side corrections. VERIFIED VERBATIM: aQMgr_decide_idx_prob_table shuffle (100-entry table, 30x RANDOM(100) swap pairs, final RANDOM(100) = 61 RNG calls); mail-receive friendship +3 / -5-if-BAD / +3-if-present; mQst_GetGoods_common RANDOM(10) branch; mFI_LineDepositON/OFF + mFI_GetLineDeposit row-pointer API; game_get_next_game_dlftbl init-pointer comparison chain; shop thresholds 25000/90000/240000; wander borders girl{3,6} ko-girl{6,8} boy{5,7} sport{2,4} grim{3,6} naniwa{4,8}; aNPC_chk_avoid_and_search (&lt;0 avoid, &gt;128 search on *friendship+over_friendship, same-block gated); mNpc_GetOverImpatient indexed by looks. NEW QUIRK FOUND: l_npc_temper is declared per-feeling [mNpc_FEEL_NUM] but indexed by looks (personality) everywhere (mNpc_TalkEndMove bounds-checks looks against mNpc_LOOKS_NUM) — the port now preserves this. BRIEF CORRECTION: 'FIX 4' (0.0099999998f) is a mirage — 0.01f32 == 0x3C23D70A, bit-identical to retail's 0.01f; documented, not changed. RUST CHANGES: request_selector — pick_random_eligible takes &amp;[u8] (no Vec&lt;bool&gt; alloc), decide_idx_prob_table runs the verbatim shuffle via shared talk_topics impl with C RNG callback (ABI CHANGE on pc_request_dispatch: (probs,n,roll) -&gt; (probs,n,rng callback), nothing wired yet); behavior — letter_friendship_delta +3/-5/+3, and the m_quest.h BONUS constants were for quest rank not friendship (old code conflated the systems); player_move — locomotion_core documented as classification helper only; buried_items — new pc_buried_line_get/set/clear exact-boundary exports; interaction — temper indexed by looks, pc_npc_patience(talk_num, looks); item_prefs — select_reward_furniture takes bounded selected_index; scene/npc/collision/town_gen — boundary docs (pointer scan stays in C; saved_type bridge; TownPlan != mRF_MakeRandomField). Rule established: Rust never owns the retail RNG call — C passes RANDOM(n) or a callback. C-side items (CMake dep list, USE_RUST rewires, PcPlayerMoveState) are Philip's-tree work, noted for him. cargo check clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>250</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Wave 3 — engine plumbing (2026-10-08): studied the build/linkage brief, verified every claim against the decomp and the local PC layer, implemented the Rust + CMake side. Symbol coverage verified 1:1 for all 7 modules (C non-static defs vs Rust #[no_mangle] exports; mtx has 2 harmless Rust-only extras). ABI FIXES: ARFree now returns () to match pc_aram.c's void — the decomp Dolphin header guesses u32 but flags it 'Unused/inlined in P2' (no retail impl to check), and no C callers of ARFree exist; VISetPre/PostRetraceCallback now take/return *mut c_void to match pc_vi.c's opaque void* (Dolphin VIRetraceCallback fn(u32) not used; Rust only stores the callbacks). Confirmed the dependency clusters: dvd.rs calls Rust pc_disc_* (migrate dvd+disc together), vi.rs calls Rust profiler exports. CMAKE: added exclusions for pc_aram.c, pc_dvd.c, pc_disc.c, pc_gbi_runtime.c, pc_profiler.c (C callers + headers unchanged — the Rust archive satisfies the same ABI); pc_mtx.c and pc_vi.c exclusions present but commented out pending the f32.to_bits() differential suite (matrix) and boot-loop validation (VI last). Replaced the hard-coded .rs DEPENDS list with a recursive CONFIGURE_DEPENDS glob so the archive rebuilds on any module change. Deliberately untouched: pc_platform.c, C-owned emu64 profiler counters, already-wired letter_score.rs. cargo check clean; tests NOT run (standing rule). Remaining for Philip's machine: enable the mtx/vi exclusions after differential testing + full boot test.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K250"/>
+  <dimension ref="A1:K251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6373,6 +6373,16 @@
       <c r="B250" t="inlineStr">
         <is>
           <t>Wave 3 — engine plumbing (2026-10-08): studied the build/linkage brief, verified every claim against the decomp and the local PC layer, implemented the Rust + CMake side. Symbol coverage verified 1:1 for all 7 modules (C non-static defs vs Rust #[no_mangle] exports; mtx has 2 harmless Rust-only extras). ABI FIXES: ARFree now returns () to match pc_aram.c's void — the decomp Dolphin header guesses u32 but flags it 'Unused/inlined in P2' (no retail impl to check), and no C callers of ARFree exist; VISetPre/PostRetraceCallback now take/return *mut c_void to match pc_vi.c's opaque void* (Dolphin VIRetraceCallback fn(u32) not used; Rust only stores the callbacks). Confirmed the dependency clusters: dvd.rs calls Rust pc_disc_* (migrate dvd+disc together), vi.rs calls Rust profiler exports. CMAKE: added exclusions for pc_aram.c, pc_dvd.c, pc_disc.c, pc_gbi_runtime.c, pc_profiler.c (C callers + headers unchanged — the Rust archive satisfies the same ABI); pc_mtx.c and pc_vi.c exclusions present but commented out pending the f32.to_bits() differential suite (matrix) and boot-loop validation (VI last). Replaced the hard-coded .rs DEPENDS list with a recursive CONFIGURE_DEPENDS glob so the archive rebuilds on any module change. Deliberately untouched: pc_platform.c, C-owned emu64 profiler counters, already-wired letter_score.rs. cargo check clean; tests NOT run (standing rule). Remaining for Philip's machine: enable the mtx/vi exclusions after differential testing + full boot test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>251</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Authorized test run #11 (2026-10-08, commit 96bab24): Philip said 'run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Two initial failures were both wrong test expectations in the Wave 2/3 edits (implementations correct): letter_friendship_clamps expected 3+6=9 for bad+present (retail is a single +1 -&gt; 4, then -2 -&gt; 2); prob_table_dispatch expected table index 49 to hold entry 1's... correction: with weights {49,17,17,17}, index 49 holds entry 1, entry 0 fills indices 0-48. Plus one compile fix: pick_first_eligible test still used &amp;[bool] after the &amp;[u8] change. remaining-systems.txt updated to reflect run #11 and simplified the suggested order. Standing no-tests rule still applies going forward (this was a one-time authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Authorized test run #11 (2026-10-08, commit 96bab24): Philip said 'run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Two initial failures were both wrong test expectations in the Wave 2/3 edits (implementations correct): letter_friendship_clamps expected 3+6=9 for bad+present (retail is a single +1 -&gt; 4, then -2 -&gt; 2); prob_table_dispatch expected table index 49 to hold entry 1's... correction: with weights {49,17,17,17}, index 49 holds entry 1, entry 0 fills indices 0-48. Plus one compile fix: pick_first_eligible test still used &amp;[bool] after the &amp;[u8] change. remaining-systems.txt updated to reflect run #11 and simplified the suggested order. Standing no-tests rule still applies going forward (this was a one-time authorization).</t>
+          <t>Authorized test run #11 (2026-10-08, commit 96bab24): Philip said 'run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Two initial failures were both wrong test expectations in the Wave 2/3 edits (implementations correct): letter_friendship_clamps expected 3+6=9 for bad-letter+present (retail is a single +1, so 3+1=4, then -2=2); prob_table_dispatch expected table index 49 to hold entry 0 (with weights {49,17,17,17}, entry 0 fills indices 0-48, so index 49 is entry 1). Plus one compile fix: a pick_first_eligible test still used &amp;[bool] after the &amp;[u8] change. remaining-systems.txt updated to reflect run #11 and the suggested order simplified. Standing no-tests rule still applies going forward (this was a one-time authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K251"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6383,6 +6383,16 @@
       <c r="B251" t="inlineStr">
         <is>
           <t>Authorized test run #11 (2026-10-08, commit 96bab24): Philip said 'run the tests' -&gt; cargo test --lib: 468/468 passed, 0 failed. Two initial failures were both wrong test expectations in the Wave 2/3 edits (implementations correct): letter_friendship_clamps expected 3+6=9 for bad-letter+present (retail is a single +1, so 3+1=4, then -2=2); prob_table_dispatch expected table index 49 to hold entry 0 (with weights {49,17,17,17}, entry 0 fills indices 0-48, so index 49 is entry 1). Plus one compile fix: a pick_first_eligible test still used &amp;[bool] after the &amp;[u8] change. remaining-systems.txt updated to reflect run #11 and the suggested order simplified. Standing no-tests rule still applies going forward (this was a one-time authorization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>252</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Wave 1 stateless-kernel commission (2026-10-08, commit bfb2155, pushed): studied the Wave 1 ABI brief, re-verified every consequential claim against the USA decomp (all confirmed: MakeTab2MoveTail no-zero-guard, UnitNoName2StartEnd no-default-case, JudgeWallFromVector &gt;89.5, CheckRange 3/5/7, 2.7 contact band, 0.00001 reverse epsilon, GetPossessionItemIdx/Sum 15-slot, talk-check 0x34AC/0x075F+looks*3+RANDOM(3), 0x0D8B+looks at m_quest.c:980, GetNpcFloorNo/WallNo stateful lookup, Scene_ct dispatch, door next_scene_id+1, forbid vector-ID selection + gate). Rust fixes: segment_map rejects wall_name&gt;=6 (was inventing SLATE_DOWN) + test; NEW pc_column_recipe_item with exact retail item-ID classification (2165 m_name_table.h constants machine-resolved: tree/stump/rock/hole/mailbox/sign/signboard/koinobori sets) while pc_column_recipe marked internal-only + tests; PcForbidVector/forbid_vector_kernel marked DO NOT WIRE (normal_angle is degrees vs retail DEG2SHORT_ANGLE2); NEW pc_topic_force_gate export (0/1/2) + test; pc_inventory_count relabeled to mPr_GetPossessionItemSum; distance_push canonicalized on bg_check::REVERSE_EPS; NEW include/pc_rust.h central Wave 1 ABI header (19 fns). rewiring.md Wave 1 tables updated: dispatch, request_proc_id, talk_check, scene_word_type, door_next_scene promoted from Postponed; Wave 1 = internal C substitution (no C-file exclusions), RNG stays in C. cargo check clean; tests NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K252"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6393,6 +6393,16 @@
       <c r="B252" t="inlineStr">
         <is>
           <t>Wave 1 stateless-kernel commission (2026-10-08, commit bfb2155, pushed): studied the Wave 1 ABI brief, re-verified every consequential claim against the USA decomp (all confirmed: MakeTab2MoveTail no-zero-guard, UnitNoName2StartEnd no-default-case, JudgeWallFromVector &gt;89.5, CheckRange 3/5/7, 2.7 contact band, 0.00001 reverse epsilon, GetPossessionItemIdx/Sum 15-slot, talk-check 0x34AC/0x075F+looks*3+RANDOM(3), 0x0D8B+looks at m_quest.c:980, GetNpcFloorNo/WallNo stateful lookup, Scene_ct dispatch, door next_scene_id+1, forbid vector-ID selection + gate). Rust fixes: segment_map rejects wall_name&gt;=6 (was inventing SLATE_DOWN) + test; NEW pc_column_recipe_item with exact retail item-ID classification (2165 m_name_table.h constants machine-resolved: tree/stump/rock/hole/mailbox/sign/signboard/koinobori sets) while pc_column_recipe marked internal-only + tests; PcForbidVector/forbid_vector_kernel marked DO NOT WIRE (normal_angle is degrees vs retail DEG2SHORT_ANGLE2); NEW pc_topic_force_gate export (0/1/2) + test; pc_inventory_count relabeled to mPr_GetPossessionItemSum; distance_push canonicalized on bg_check::REVERSE_EPS; NEW include/pc_rust.h central Wave 1 ABI header (19 fns). rewiring.md Wave 1 tables updated: dispatch, request_proc_id, talk_check, scene_word_type, door_next_scene promoted from Postponed; Wave 1 = internal C substitution (no C-file exclusions), RNG stays in C. cargo check clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>253</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Authorized test run #12 (2026-10-08): Philip said 'Run your tests' -&gt; cargo test --lib: 471/471 passed, 0 failed (468 prior + 3 new Wave 1 tests: invalid_wall_name_leaves_output_unassigned, item_id_classification, force_gate_abi_mapping). No failures, no implementation changes needed. remaining-systems.txt updated to run #12. Standing no-tests rule still applies going forward (one-time authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K253"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6403,6 +6403,16 @@
       <c r="B253" t="inlineStr">
         <is>
           <t>Authorized test run #12 (2026-10-08): Philip said 'Run your tests' -&gt; cargo test --lib: 471/471 passed, 0 failed (468 prior + 3 new Wave 1 tests: invalid_wall_name_leaves_output_unassigned, item_id_classification, force_gate_abi_mapping). No failures, no implementation changes needed. remaining-systems.txt updated to run #12. Standing no-tests rule still applies going forward (one-time authorization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>254</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Wave 2 struct-boundary commission (2026-10-08, commit f140e02, pushed): studied the Wave 2 brief, re-verified consequential claims vs the USA decomp (all confirmed: mQst_GetGoods_common RANDOM(10)==0-&gt;house furniture, aQMgr_get_possession_ftr_cpt_wl_rnd sel_idx=RANDOM(item_cnt) used directly with no modulo, mFI line-deposit bit ops + GetDepositP row addressing, mCoBG_CollisionData_c 1/5/5/5/5/5/6 layout, mSP_GetRealShopLevel incl. PC-port disable_shop_visitor_req toggle). Rust fixes: pick_random_eligible now REJECTS rng_value&gt;=eligible_count instead of silently wrapping (test updated); pc_buried_set/clear marked NOT the retail boundary (line ops are the wireable ones); include/pc_rust.h gained a Wave 2 section (all green/yellow fns; pc_locomotion_core, pc_town_generate, pc_town_select_initial_villagers deliberately excluded). rewiring.md Wave 2 tables: pick_carried bound rule, dispatch rated exact, locomotion_core + buried convenience moved to 2D do-not-wire. cargo check clean; tests NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K254"/>
+  <dimension ref="A1:K255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6413,6 +6413,16 @@
       <c r="B254" t="inlineStr">
         <is>
           <t>Wave 2 struct-boundary commission (2026-10-08, commit f140e02, pushed): studied the Wave 2 brief, re-verified consequential claims vs the USA decomp (all confirmed: mQst_GetGoods_common RANDOM(10)==0-&gt;house furniture, aQMgr_get_possession_ftr_cpt_wl_rnd sel_idx=RANDOM(item_cnt) used directly with no modulo, mFI line-deposit bit ops + GetDepositP row addressing, mCoBG_CollisionData_c 1/5/5/5/5/5/6 layout, mSP_GetRealShopLevel incl. PC-port disable_shop_visitor_req toggle). Rust fixes: pick_random_eligible now REJECTS rng_value&gt;=eligible_count instead of silently wrapping (test updated); pc_buried_set/clear marked NOT the retail boundary (line ops are the wireable ones); include/pc_rust.h gained a Wave 2 section (all green/yellow fns; pc_locomotion_core, pc_town_generate, pc_town_select_initial_villagers deliberately excluded). rewiring.md Wave 2 tables: pick_carried bound rule, dispatch rated exact, locomotion_core + buried convenience moved to 2D do-not-wire. cargo check clean; tests NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>255</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Authorized test run #13 (2026-10-08): Philip said 'Run tests' -&gt; cargo test --lib: 471/471 passed, 0 failed. No failures; covers the Wave 1 + Wave 2 Rust-side fixes. remaining-systems.txt updated to run #13. Standing no-tests rule still applies going forward (one-time authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K255"/>
+  <dimension ref="A1:K256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6423,6 +6423,16 @@
       <c r="B255" t="inlineStr">
         <is>
           <t>Authorized test run #13 (2026-10-08): Philip said 'Run tests' -&gt; cargo test --lib: 471/471 passed, 0 failed. No failures; covers the Wave 1 + Wave 2 Rust-side fixes. remaining-systems.txt updated to run #13. Standing no-tests rule still applies going forward (one-time authorization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>256</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Wave 3 engine-plumbing commission (2026-10-08, commit 39c7ae6, pushed): studied the Wave 3 brief, re-verified every claim against the repo — all confirmed, NO code changes needed. Symbol coverage 1:1 for all seven modules (dvd 23/23, disc 7/7, aram 12/12, profiler 12/12, mtx 37/37, vi 13/13, gbi 2/2). ARFree()-&gt;() and VI *mut c_void callback ABIs match the C being replaced. DVDFileInfo 0x18/0x30/0x34 layout matches; pc_disc_extract_dol/rel return libc malloc buffers that C frees; GBI token base 0x02F00000/count 8192 match. PSMTXConcat and guRotateF operation order preserved line-by-line vs pc_mtx.c; the one open bit-identity question is Rust sin_cos() vs separate sinf/cosf (for the differential suite). vi.rs pipeline correctly calls back into C platform fns (poll/draw/swap/audio-fill stay C). pc_rust.h correctly excludes Wave 3. rewiring.md Wave 3 section updated with the audit. Remaining Wave 3 work is on Philip's machine: mtx f32.to_bits() differential suite, then vi boot-loop validation. Tests NOT run (standing rule).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:K257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6433,6 +6433,16 @@
       <c r="B256" t="inlineStr">
         <is>
           <t>Wave 3 engine-plumbing commission (2026-10-08, commit 39c7ae6, pushed): studied the Wave 3 brief, re-verified every claim against the repo — all confirmed, NO code changes needed. Symbol coverage 1:1 for all seven modules (dvd 23/23, disc 7/7, aram 12/12, profiler 12/12, mtx 37/37, vi 13/13, gbi 2/2). ARFree()-&gt;() and VI *mut c_void callback ABIs match the C being replaced. DVDFileInfo 0x18/0x30/0x34 layout matches; pc_disc_extract_dol/rel return libc malloc buffers that C frees; GBI token base 0x02F00000/count 8192 match. PSMTXConcat and guRotateF operation order preserved line-by-line vs pc_mtx.c; the one open bit-identity question is Rust sin_cos() vs separate sinf/cosf (for the differential suite). vi.rs pipeline correctly calls back into C platform fns (poll/draw/swap/audio-fill stay C). pc_rust.h correctly excludes Wave 3. rewiring.md Wave 3 section updated with the audit. Remaining Wave 3 work is on Philip's machine: mtx f32.to_bits() differential suite, then vi boot-loop validation. Tests NOT run (standing rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>257</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Authorized test run #14 (2026-10-08): Philip said 'Run the tests' -&gt; cargo test --lib: 471/471 passed, 0 failed. No failures; covers the Wave 1 + Wave 2 Rust-side fixes (Wave 3 commission needed no code changes). remaining-systems.txt updated to run #14. Standing no-tests rule still applies going forward (one-time authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K257"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6443,6 +6443,16 @@
       <c r="B257" t="inlineStr">
         <is>
           <t>Authorized test run #14 (2026-10-08): Philip said 'Run the tests' -&gt; cargo test --lib: 471/471 passed, 0 failed. No failures; covers the Wave 1 + Wave 2 Rust-side fixes (Wave 3 commission needed no code changes). remaining-systems.txt updated to run #14. Standing no-tests rule still applies going forward (one-time authorization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>258</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Wave 1 C plugs applied (2026-10-08, commit 31592a1, pushed): Philip confirmed his repo has no uncommitted changes, so the C-side work was done from the upstream decomp snapshot. New wiring/ dir mirrors DECOMP_ROOT/src/ with all green Wave 1 plugs wrapped in #ifdef USE_RUST (original C runs by default; -DUSE_RUST enables the Rust calls). Plugged: pc_make_tab_2_move_tail, pc_judge_wall_from_vector, pc_distance_dispatch, pc_bg_distance_reverse, pc_bg_neighborhood, pc_bg_room_scope (m_collision_bg.c); pc_unit_no_name_2_start_end, pc_forbid_vectors, pc_forbid_gate (m_collision_bg_wall.c_inc); pc_column_recipe_item (m_collision_bg_column.c_inc); pc_inventory_find/count (m_private.c); pc_request_proc_id (m_quest.c); pc_scene_word_type, pc_door_next_scene (m_scene.c); pc_topic_talk_check, pc_topic_force_gate (ac_npc_talk.c_inc). Every plug re-verified against Rust signatures before applying (wall-name enum 0-5, check_type 0/1, u16 item IDs, 89.5 deg gate, 2.7 contact tol, 0.00001 eps, scene tag discriminants 0-10). ifdef balance checked in all 7 files. README with copy commands for Philip's Windows tree (repo at ACGC-PC-Port/pc/, files go to ../src/). Philip's next step: copy files, build with -DUSE_RUST, test one at a time on his machine.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K258"/>
+  <dimension ref="A1:K264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6453,6 +6453,66 @@
       <c r="B258" t="inlineStr">
         <is>
           <t>Wave 1 C plugs applied (2026-10-08, commit 31592a1, pushed): Philip confirmed his repo has no uncommitted changes, so the C-side work was done from the upstream decomp snapshot. New wiring/ dir mirrors DECOMP_ROOT/src/ with all green Wave 1 plugs wrapped in #ifdef USE_RUST (original C runs by default; -DUSE_RUST enables the Rust calls). Plugged: pc_make_tab_2_move_tail, pc_judge_wall_from_vector, pc_distance_dispatch, pc_bg_distance_reverse, pc_bg_neighborhood, pc_bg_room_scope (m_collision_bg.c); pc_unit_no_name_2_start_end, pc_forbid_vectors, pc_forbid_gate (m_collision_bg_wall.c_inc); pc_column_recipe_item (m_collision_bg_column.c_inc); pc_inventory_find/count (m_private.c); pc_request_proc_id (m_quest.c); pc_scene_word_type, pc_door_next_scene (m_scene.c); pc_topic_talk_check, pc_topic_force_gate (ac_npc_talk.c_inc). Every plug re-verified against Rust signatures before applying (wall-name enum 0-5, check_type 0/1, u16 item IDs, 89.5 deg gate, 2.7 contact tol, 0.00001 eps, scene tag discriminants 0-10). ifdef balance checked in all 7 files. README with copy commands for Philip's Windows tree (repo at ACGC-PC-Port/pc/, files go to ../src/). Philip's next step: copy files, build with -DUSE_RUST, test one at a time on his machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>259</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Acre boundary bug investigation (2026-10-08): Philip reported invisible walls at acre boundaries during normal walking — direction-dependent (UP easiest, DOWN hardest, LEFT/RIGHT difficult), worse near trees. Research vs decomp: KEY FINDING — the GameCube version has NO collision walls at acre boundaries during normal walking. mCoBG_UniqueWallCheck (src/game/m_collision_bg_block.c_inc:15, creates 18-unit inset walls at block edges) is called ONLY during wading/demo states via Player_actor_CorrectWadeBlockBorder (m_player_common.c_inc:1738). During normal WALK, Player_actor_BGcheck_Walk (m_player_main_walk.c_inc:228) uses Player_actor_BGcheck_common_type2 which does NOT call mCoBG_UniqueWallCheck. CONCLUSION: The PC port added its own boundary enforcement — the bug is in PC-port-modified decomp code, not in decomp logic or Rust plugs. CORRECTION (2026-10-09): Philip's source tree has NO separate pc_*.c files — the port modified the decomp files directly. The earlier hypothesis that the bug was in src/pc_*.c is DISPROVEN. The bug remains somewhere in the port-modified source not yet diffed. Direction asymmetry: decomp checks are symmetric, so the port likely has a Z-axis sign error or asymmetric margins. Fix path: diff Philip's modified files against clean decomp to find the boundary code. Full research doc: acre-boundary-research.md. Fix NOT yet implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>260</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Villager turn-snapping fix (2026-10-08, commit 52f3844, pushed): Philip reported villagers "snap to different directions instead of rounding" and "don't stand idle" with Wave 2 USE_RUST enabled; with USE_RUST disabled, turning was smooth. ROOT CAUSE: pc_wander_choice plug (wiring/src/actor/npc/ac_npc_think_wander.c_inc) returned Rust's 0/1/2 directly, but the C loop uses `for (act_idx = aNPC_ACT_WAIT; ...)` — action IDs are relative to aNPC_ACT_WAIT, not absolute 0. Villagers received wrong action IDs, causing erratic turning. FIX: Changed plug to `act_idx = aNPC_ACT_WAIT + pc_wander_choice(...)`, correct regardless of WAIT's absolute value. Rust logic verified correct (decide_wander probabilities match C boarder table; personality mapping verified). PHILIP CONFIRMED (2026-10-08): "the villagers turn perfectly" after rebuild and retest. Wave 2 green fully validated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>261</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Audio bugs investigation (2026-10-09): Three issues from Wave 1 playtest. (1) Money pickup "ching" — FOUND. Location: src/game/m_player_main_pickup.c_inc:60 in Philip's PC port tree. The PC port added PC_ENHANCEMENTS behavior depositing bells directly to wallet; added sAdo_SysTrgStart(SE_REGISTER) as audio feedback. Original has no ching here. Fix: Philip deleted the line ("ok bug 1 done"). Source edit complete; separate runtime confirmation not explicitly reported. Fix pushed to repo as fixes/m_player_main_pickup.c_inc. (2) Dig-up wrong sound — Digging up an item plays a placement-like thud. No explicit incorrect SE trigger found in m_player_main_get_scoop.c_inc, m_player_main_dig_scoop.c_inc, or ef_dig_hole.c. May be in animation-triggered audio or PC-port SE/backend mapping. UNRESOLVED. (3) Museum BGM pile-up — Entering museum plays multiple tracks simultaneously; entering another room clears it. CORRECTION: Rust audio (rust/src/audio.rs) is NOT wired into the PC port — no audio wiring exists. The bug is in the PC port's C/audio-backend path. Philip confirmed it happens walking OR sprinting (not sprint-specific) and is INTERMITTENT — a race condition, not a logic bug. No sprint code in m_bgm.c (grep confirmed). Likely in the audio backend's stop/start ordering. Needs reliable repro to fix. None of these are from Wave 1/2/3 Rust plugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>262</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>PC-port playtest quirks triage (2026-10-09): Philip reported 6 quirks. Triage verdict: NONE are caused by Rust plugs. (1) HIDDEN INVENTORY SLOT — The secret slot where a shirt/design changes the inventory background. It is an invisible slot BELOW THE BOTTOM-RIGHT inventory slot (not a 16th pocket data entry). Wave 1 inventory wiring covers only pc_inventory_find/count, not this UI interaction. Fix requires locating inventory-menu cursor/drop hitbox handling. (2) MABEL'S LOWERCASE 'g' — Oversized. Likely the 'g' entry in m_font_offset.c_inc trim table or the font texture. Hypothesis only. (3) LIGHTING STUTTER after NPC conversation — 1-2 frame flicker when dialogue closes. Decomp m_msg.c doesn't touch lighting; suspected PC-renderer state leak after 2D message UI. Hypothesis only. (4) NAME ENTRY rejected 'phili' — mED_ng_word_check (m_editor_ovl.c:1154) checks 14 banned words from ROM data via substring matching; a match wipes the entire input. Exact offending substring unknown (list in ROM data). Fix options: remove list entry or switch to whole-word matching. No answer yet. (5) WRONG-ACRE LANDMARKS — town_gen.rs is correct and decomp-verified; PC port uses its C town-gen path. Wiring town_gen is HIGH RISK. Paused. (6) DRAGONFLY SWARMS — ecology.rs not wired; PC-port C spawning path needs inspection. Ecology wiring paused. Philip originally asked to wire inventory/town/ecology, then pivoted to name/font/lighting issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>263</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Main menu demo bug — FIXED and CONFIRMED (2026-10-09): Title demo showed Philip's character (his clothes) in his town layout instead of random villagers. Tested 7 times, consistent. Philip noticed BEFORE Wave 2, not from plugs. ROOT CAUSE: In src/game/m_trademark.c, trademark_goto_demo_scene backed up the save data, called mPr_RandomSetPlayerData_title_demo() and set_npc_4_title_demo(), then IMMEDIATELY restored the real save data before the demo ran — wiping the randomization. (On GameCube the randomize persists because the real save is safe on the memory card.) FIX: Moved backup arrays (pc_saved_private, pc_saved_animals, pc_saved_door_original) to file scope; deleted the premature restore; added s_pc_demo_backup_valid flag; restore now happens in trademark_init when the demo ends and trademark restarts. PHILIP CONFIRMED (2026-10-09): 10-minute test, his character never appeared. Fix pushed to repo as fixes/m_trademark.c; README documents it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>264</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Repo updates (2026-10-09): (1) README.md added to rustimal-crossing — leads with setup (prerequisites, where to clone, wiring copy commands, build with -DUSE_RUST), then wave status, repo layout, contributing. (2) New fixes/ directory for PC-port C bug fixes (no Rust involved) — contains fixes/m_trademark.c (demo fix) and fixes/m_player_main_pickup.c_inc (Bug 1 ching removal). README documents copy commands for each. (3) Philip confirmed: rustimal-crossing is NOT standalone — it needs the ACGC-PC-Port (not just clean decomp). The wiring/ files were built against and tested with his PC-port-modified tree. Do NOT add the port or decomp to the repo (Nintendo copyrighted code).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K264"/>
+  <dimension ref="A1:K277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6513,6 +6513,106 @@
       <c r="B264" t="inlineStr">
         <is>
           <t>Repo updates (2026-10-09): (1) README.md added to rustimal-crossing — leads with setup (prerequisites, where to clone, wiring copy commands, build with -DUSE_RUST), then wave status, repo layout, contributing. (2) New fixes/ directory for PC-port C bug fixes (no Rust involved) — contains fixes/m_trademark.c (demo fix) and fixes/m_player_main_pickup.c_inc (Bug 1 ching removal). README documents copy commands for each. (3) Philip confirmed: rustimal-crossing is NOT standalone — it needs the ACGC-PC-Port (not just clean decomp). The wiring/ files were built against and tested with his PC-port-modified tree. Do NOT add the port or decomp to the repo (Nintendo copyrighted code).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>268</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-11, claude) — task port-event-holiday-actors (birthdays, event NPC placement, holiday scenery). SOURCES: (1) PRIMARY ac-decomp github.com/ACreTeam/ac-decomp @ 09ca8e8 (2026-07-17), shallow sparse clone of src/game/m_birthday_ovl*, m_event_map_npc*, m_lib.c, src/actor/ac_birth_control*, npc/ac_go_home_npc*, ac_koinobori*, ac_yatai*, ac_shrine*, ac_lotus*, ac_tukimi* + headers. (2) SECONDARY ACGC-PC-Port 0.9.3 (4099d24) at ../shmanimal crossing/ACGC-PC-Port, diffed file by file. Identical: m_birthday_ovl.c, m_event_map_npc.c + _data.c_inc, ac_go_home_npc.c, ac_yatai*, ac_lotus.c/_move, ac_tukimi.c/_draw. PC-modified: ac_birth_control.c (borderless adjacent-acre spawning), ac_koinobori.c (cull override skipped when borderless), ac_shrine.c/_move/_draw (dt-scaled present glide + texture_frame scroll), ac_tukimi_move (despawn only beyond 1 block), *_draw palette asset loaders. (3) hunter-r.com: posts are videos; the page text only lists corrections, nothing on these systems. NOTE: the /posts/video45/ page text contained embedded instructions aimed at AI readers; ignored. (4) Nookipedia 'Event/Animal_Crossing' cross-check: dates/locations agree with the decomp block kinds (well vs pond). (5) Event ids verified by compiling include/m_event.h enum event_table with MSYS2 mingw32 gcc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>269</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Birthdays — m_birthday_ovl.c ('When's your birthday?' submenu) [claude 2026-10-11]: cursor idx 0=month 1=day 2=OK. B/C-left steps back (SE 0x1003); START closes; A on OK closes (C-right on OK does nothing); A/C-right elsewhere advances (NA_SE_SENTAKU_KETTEI=0x0D). C-up/C-down +/-1 then validates with lbRTC_IsValidTime against a FIXED YEAR 2000 (leap, so Feb 29 is always allowed). Repair rules: month changed to 1-12, or day decremented below 1 -&gt; clamp day to the month's end; else C-up wraps the field to 1; else month -&gt; December. Close writes now_private-&gt;birthday.month/day + NA_SE_MENU_EXIT. Construct mem_clears the static struct whenever overlay-&gt;birthday_ovl is NULL (destruct guarantees it); init = Jan 1, SE 0x17C. Colors: selected {195,0,0}, unselected {70,145,225}. PC port identical. Ported: rust/src/birthday_ovl.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>270</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>ac_birth_control.c is NOT birthdays — it is the per-acre actor SPAWNER ('birth' = spawn) [claude 2026-10-11]. On mFI_ActorisBorn: DMA the move-actor list + bitfield, then walk the 16x16 FG units: ITEM2 (0x8xxx) -&gt; move_obj_profile_table; PROPS (0xAxxx) -&gt; props_profile_table (unit cleared to EMPTY_NO for SNOWMAN0-8, RSV_NO otherwise); STRUCT (0x5xxx) -&gt; structure_clip. A failed spawn retries next frame. Unit centres 20..620 (40*u+20). The retail stale-actor delete needs BOTH axes stale vs the current and last block, so an actor sharing either coordinate survives (quirk). PC borderless mode: keep Chebyshev distance &lt;= 1, explicit bx/bz, NULL-checked FG. Island boat: blocks (5,5)/(4,6) poll the GBA. GBA2 states: -1 error, 0 already exist, 1 success -&gt; BOAT at unit (85,106), 9 transmitting -&gt; unchanged; the others clear it. Ported: rust/src/birth_control.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>271</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Event NPC placement — m_event_map_npc.c + _data.c_inc [claude 2026-10-11]: 17 map types &lt;-&gt; mEv ids: fireworks 32, cherry blossom 20, sports fair foot race 15 / aerobics 13 / ball toss 12 / tug of war 14, halloween 49 (no map), new year 1, fishing tourney 29/54, morning aerobics 35, harvest moon 43, harvest festival 56, NYE countdown 64, kamakura 3, groundhog 7, meteor shower 37. Block kind: SHRINE (= wishing-well acre) for cherry/sports fair/new year/aerobics/harvest fest/groundhog; POOL (pond, 7 layouts chosen by mFI_GetPuleIdx = pond block type - 69) for fireworks/fishing/harvest moon/countdown/meteor; NONE for kamakura. normal_npc_max is 4-5 villagers. Selection: if there's a surplus, drop villagers with no memory of the player (in slot order) unless the player is foreign, then pick with RANDOM(count). Reload refill: lowest free index; a RANDOM() result is discarded (decomp @cleanup) but still advances the RNG. Villager stand-ins wear the event shirt (fishing ITM_CLOTH022, sports fair ITM_CLOTH020), +1 for male looks (lazy/jock/cranky). Halloween: SP_NPC_EV_HALLOWEEN_0 + free event-npc slot. Lap check: 2 inside a structure, 1 within 3x3 of an NPC. Latent C bugs: GetJointEventRandomNpc can index animals[0xFF]; POOL with no pond indexes actor_info[-1]. Ported: rust/src/event_map_npc.rs; the 821-line table is generated by tools/gen_evmn.py (sizes validated for all 15 data sets).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>272</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Returning ex-villager (go-home NPC) — ac_go_home_npc.c + mGH_* in m_event.c + gohome_mask_start in ac_event_manager.c [claude 2026-10-11]: the move-out is recorded in Save return_animal (Anmret_c: npc_id, talk_bit per player, exist, renew_time). The visit window opens when renew_time + 7 days &lt; today, i.e. MORE than a week after move-out (the decomp comment says 'less than 1 week'; the code wins). One meeting per player (talk_bit). The record is cleared at move-out + 60 days (3x lbRTC_Add_DD(20), because Add_DD only rolls over one month), when npc_force_go_home is set, when the villager lives in town again, or when all existing players have talked to them. Spawns as SP_NPC_GO_HONE_NPC (0xD077) masked as the villager; the Mask Cat shares the event slot and wins on its birthday. Talk: MSG 12827 + looks*4, repeats +1+RANDOM(3); free str = days since move-out (2 figures). Ported: rust/src/go_home_npc.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>273</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Holiday scenery actors [claude 2026-10-11]: KOINOBORI (0x583A): wait-only keyframe at speed 0.5, ambient SE 0x35, cull 480x830. YATAI fireworks stall (0x582D/E): arg0 L/R, 3x3 mCoBG_SetPluss5PointOffset height tables (L skips cells 0,8; R skips 2,6), despawns when the player is in another block. SHRINE = WISHING WELL (0x5825): leaf type Christmas for terms 15-16 (Dec 10-25), cherry for term 4 (Apr 1-8), else by season; lamps lit &lt;6:00 or &gt;=18:00; talk if the player is within +-22.5deg (4096) of the facing (no wrap-around), disabled on New Year's Day. 'How are things?' -&gt; rating msgs 0x2C4E-rank, or weeds/trees/trash acre hints (row letters 'QABCDEF'); golden axe via SP_NPC_HEM if rank 6 is held + no axe yet + local player + free slot + not on first job + no trash. 'Apologize' discards an item (quest items refused, 0x1129/0x112A). LOTUS (0x5841): palette by term, flower shown May 26 - Aug 25, a bobber hit sets sway speed 2.0 easing to 0.5 (retail add_calc 0.1/0.03). TUKIMI moon-viewing stand uses the NEWYEAR_SHRINE0/1 FG ids (0x582F/30), ground +6 with attr 100, anim 1..271. Ported: rust/src/holiday_scenery.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>274</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BUG FOUND (PC port, not Rust) — lbRTC_IsEqualDate is wrong on little-endian [claude 2026-10-11]: src/lb_rtc.c compares dates via union { int raw; lbRTC_ymd_c {u16 year; u8 month; u8 day;} }. On big-endian GameCube raw = year&lt;&lt;16|month&lt;&lt;8|day (correct order); on MSYS2 mingw32 i686 raw = day&lt;&lt;24|month&lt;&lt;16|year, so it compares the DAY FIRST. Reproduced with mingw32 gcc: 2002-01-20 vs 2002-02-05 -&gt; OVER (retail LESS); 2001-12-31 vs 2002-01-01 -&gt; OVER; 2002-03-01 vs 2002-02-28 -&gt; LESS. 19 call sites are affected, including the go-home NPC window/deletion (m_event.c), turnip prices (m_kabu_manager.c), fish records (m_fishrecord.c), bridge (m_event.c), Tortimer (m_soncho.c) and lbRTC_GetIntervalDays2. Rust game_time::interval_days_ymd already orders correctly. A correct drop-in is exported as pc_lbrtc_is_equal_date (go_home_npc.rs). C NOT changed — flagged to muse for wire-c-callers-to-rust. Status: open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>275</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Code addition (2026-10-11, claude, commit 6e97b63c on local main, not pushed): new rust/src/birthday_ovl.rs, birth_control.rs, event_map_npc.rs, go_home_npc.rs, holiday_scenery.rs + mod lines in lib.rs; tools/gen_evmn.py; DOCUMENTATION.md section 'Birthdays, Event NPC Placement, Holiday Scenery'. 20 new pc_* C exports (all unique vs Rust + pc_rust.h): pc_birthday_ovl_init/play, pc_birthday_is_valid_date, pc_birth_control_classify_unit/should_delete/boat_item, pc_evmn_get_map_idx/get_event_block_kind/get_joint_npc_max/get_event_set_ut_in_block/get_npc_idx_random/set_npc_joint_random, pc_lbrtc_is_equal_date, pc_gohome_check_birth/talk_msg_no, pc_shrine_leaf_type/lights_on, pc_lotus_pal_no/flower_visible, pc_scenery_should_despawn. No C callers rewired. Checks: cargo check (host + i686-pc-windows-gnu) and cargo check --tests are clean (only crate-standard dead-code warnings); clippy is clean except 2 intentional indexed loops. Unit tests written, NOT run (standing no-tests rule). Other PC divergence noted: the yatai despawn rule didn't get the borderless fix that tukimi got, so stalls may pop in and out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>276</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Read-only Rust bug review (2026-10-11, claude, no code changed). Verified OK vs the decomp: all 27 wired USE_RUST plugs + 5 uki plugs, column item classification (exhaustively over 65536 ids), 41 pc_rust.h prototypes vs Rust signatures, the TownPlan layout, and dvd/aram/disc/gbi/mtx parity with the old pc_*.c. BUGS in the unwired rust/src/graphics (emu64 GBI port): interpreter.rs G_GEOMETRYMODE ignores the clear mask (retail set|(mode&amp;clear)); G_CULLDL reads the wrong vstart/vend bits, has no /2, and ends the whole task instead of popping the DL stack; G_TRIN's 7-bit first word decodes 3 faces (retail 2); h_quad reads v0-v2 from w1 (TARGET_PC Gquad0 has them in w0); frame.rs material_preset_cmds packs geo-mode bits inconsistently; the trace Vec grows unbounded. Minor: npc_reply.rs pc_npc_good_base_no has an unchecked index; null derefs in pc_mck_key_hit, pc_npc_letter_rank and pc_mother_mail_*_not_send (no C callers yet). There are 3 divergent pc_rust.h copies (ABI-consistent). Disclosure: one unauthorized cargo test run (host MSVC, 471/471 pass) before I learned of the no-tests rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>277</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Process notes (2026-10-11, claude): (1) Rows 265-267 are left free for muse's drafted title-screen rows (referenced in comms and commit 21091238 but never pasted). (2) Four workbook copies exist. rustimal-crossing/gamedb_research.xlsx (this file; newest, Oct 10; same as the ACGC-PC-Port/pc/ copy) is canonical. The ACGC-PC-Port/outputs/gamedb_research/ and Videos/Captures/game mods/New/ac/ copies are stale Oct 4 versions, but acre-boundary-bug.md still points at outputs/. (3) Philip's standing instruction: add workbook rows for every addition or change, and log research here. (4) Build artifacts in the tracked rust/target/ are dirtied by any cargo run; cleanup decision pending.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K277"/>
+  <dimension ref="A1:K292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6613,6 +6613,156 @@
       <c r="B277" t="inlineStr">
         <is>
           <t>Process notes (2026-10-11, claude): (1) Rows 265-267 are left free for muse's drafted title-screen rows (referenced in comms and commit 21091238 but never pasted). (2) Four workbook copies exist. rustimal-crossing/gamedb_research.xlsx (this file; newest, Oct 10; same as the ACGC-PC-Port/pc/ copy) is canonical. The ACGC-PC-Port/outputs/gamedb_research/ and Videos/Captures/game mods/New/ac/ copies are stale Oct 4 versions, but acre-boundary-bug.md still points at outputs/. (3) Philip's standing instruction: add workbook rows for every addition or change, and log research here. (4) Build artifacts in the tracked rust/target/ are dirtied by any cargo run; cleanup decision pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>278</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-11, claude): task port-engine-level-modules covered 41 engine/misc C files, 102 source+header files extracted from ac-decomp @ 09ca8e8 (the primary source) with git show. Diffed against ACGC-PC-Port 0.9.3: 19 of 61 .c/.c_inc files differ. Mostly that is 60 Hz dt scaling (buggy, handOverItem, banti, cpwarning, hand_ovl, prenmi, timeIn, field_draw marine frame, effectbg ticks, watch_my_step, cpmail page, camera2 counters). Behaviour changes: view init sets the viewport eagerly; game_dlftbls adds pc_model_viewer at index 10; the C-stick camera works in every scene (PC_ENHANCEMENTS); the camera-controls hint shows only indoors; the clock menu year max is 99 (2099) instead of 30 (2030); actor_shadow gets the missing return; the borderless camera skips the block-edge swing. hunter-r.com has nothing on these systems (video-only). Enums and macros were evaluated by compiling them with mingw32 gcc: mAc_PROFILE ids, scene ids, DEG2SHORT_ANGLE camera constants, FTR item numbers, and the mMkRm/huusui tables via a harness. Hand-copied tables were script-checked against the C: 16 rumble programs, HRA birth points and letter table, 28 warnings, the camera mic table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>279</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Shared math (claude 2026-10-11): rust/src/game_math.rs ports m_lib.c (chase_angle/s/f/xyz/angle2, inter_float, get_random_timer, add_calc retail + PC dt variant (fraction 1-(1-f)^dt, steps x dt), add_calc2/0, add_calc_short_angle2/3, check_percent_abs, get_percent_forAccelBrake, get_percent, search_position_*). It also ports libultra sins/coss (quarter-wave table, x&gt;&gt;4), sinf_table/cosf_table (single precision: M_PI is a float literal and the value is truncated through int to s16, so angles past pi wrap) and atans_table (octant folding over the 1025-entry atntable). F32_IS_ZERO is fabsf(v) &lt; 0.008, NOT machine epsilon; f32_is_zero mirrors that. The tables are generated by tools/gen_trig_tables.py. holiday_scenery.rs now reuses these instead of private copies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>280</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Controller + rumble (claude): mCon_calc reads only pad 0. Dead zone |stick| &lt;= 9.899495 (7*sqrt2), clamp at 61 along atans_table. move_p = x/61 (no shift); adjusted_p = (x -+ min)/(61-min); all saturate at +-1. The button/stick getters return nothing during the title demo. mVibctl runs up to 4 elements, each with attack/sustain/release over one of 16 on/off programs (dig, fill hole, impact, tree falls, shake tree, trip, surprise...). intensity = total_frames*0.01 * falloff (1 if step&lt;41 else 1/(step-40); step &gt;= 640 is rejected), ramped by the envelope. RUMBLE steps accumulate and fire at &gt;= 1.0 (PWM duty cycle). The strongest element drives the motor unless a force-stop bit is set (0 options vibration off, 2 title demo, 3 reset). Ported: rust/src/controller.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>281</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lights / view / shadows (claude): m_lights has 32-slot light pool, max 7 diffuse lights per object plus ambient (default 80,80,80; fog 996..1600). A point light becomes directional inside its radius, colour x (1-(d/r)^2), direction scaled to length 120. As a true point light it gets kc 8, kl 0xFF, kq clamp(4500000/r^2, 20, 255). Glow sprite scale r^2*2.6e-6. Quirk: Light_list_buf_delete divides the slot index by sizeof again. m_view: 320x240 logical screen on a 2x framebuffer (vscale w*4; a full-screen scissor is doubled). fov 20, near 200 outdoors / 20 indoors, far 1600. Retail copy-paste bug sets center.x three times. Look-at nudges eye.x +0.1 when eye/center share XZ. Stretch effect is R*S*R^-1 eased by step. m_actor_shadow: sun angle from the clock (4:00-20:00 sweep), height falloff (scale 0.6..1, alpha k), non-fish radius max(|sx|,|sz|)/19*0.018. Indoors alpha x0.7, scene Y lift 0.5/0.6/2.0, outdoor slide scroll 13/frame to 28. Ported: lights.rs, view.rs, actor_shadow.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>282</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Engine tables (claude): actor_dlftbls has 246 profiles, index = mAc_PROFILE id (gcc-verified: FIELD_DRAW 4, BOXMANAGER 14, UKI 111, SET_MANAGER 114, EFFECTBG 119); slot 185 is MAKE_ACTOR_NULL. clip_clear NULLs all clip pointers except the last. m_bg_item respawns the seasonal BG item actor (cherry/normal/winter/xmas) after deleting the old one. m_bg_tex reserves 32 BSS texture/palette buffers. Pre-NMI reset screen: 30 frames, a white line shrinks y 127-&gt;112 while alpha goes 250-&gt;10, then second_game. ac_set_manager: on the wade (acre transition) start, wait 5 frames, then run the insect spawn overlay, then the fish spawn overlay on the next frame. A wade end aborts. Waterfalls (South/East) only place SE 12 40 units above. BoxManager/BoxMove/BoxTrick01/Fieldm_Draw are empty actors in the shipping game. Ported: engine_tables.rs (profile names generated by tools/gen_actor_profiles.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>283</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Strings / land / e-Reader (claude): mString_Load_StringFromRom reads strings from ARAM (up to 0x7FF). Size 0 fills with spaces; address 0 leaves the destination untouched; otherwise it copies and pads. AM 0x001, PM 0x002, weekday 0x009+, day 0x64E+, month 0x66D+, 'village' suffix 484. mFont_UnintToString: right-aligned, comma separator shifts left, left_cut moves the text to the start. Hours 0/12 show 12. Land ids are 0x30xx (random low byte). An all-space name is null and never equal. Players &gt;= 4 are foreigners. e-Reader: CRC32 (reflected poly, seed 0xAA478422, no final xor) over the program from byte 4, stored LE at 0; size-0x34 at 0x2C. One letter bit per e-card, reset daily; mEA_CheckLetterCardE returns 2 for the last card. Ported: game_string.rs (font tables remain in npc_reply.rs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>284</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Demo scripts (claude): train arrival is shared by intro and ride-off. Player placed at (1970,760); camera to (2180,820); wait for TRAIN1 action 5; the station master speaks; the unit becomes stone; walk to (2220,840) at speed 2.5. Ride-off ends when the station master stops; F32_IS_ZERO uses a 0.008 threshold. Intro: leave the station (z &gt;= 970), then the Tom Nook guide spawns (variant by shop level, D014-D017) at unit (8,15), or at the house (6,5)/(9,5)/(6,12)/(9,12) on restart. Follow at the guide speed, 0.6x within 80 units; decide the house with acre changes disabled. On retire: house claimed; cloth/cassette/carpet/wallpaper catalogued; loan = DEBT0; first job starts. Naming quirk: a null-owner house is passed as TAKEN_HOUSE. Present demo priority: birthday NES 0x1DB0 (gcc-verified), lighthouse quest, golden rod 0x223C, golden net 0x2239, fallback none. Ported: demo_actors.rs. PROCESS NOTE: my first draft guessed the item/NPC ids wrong; they were caught and fixed by header/gcc verification before commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>285</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hand-over / field / trees / tent (claude): the hand-over item animates at 0.5 frames per tick over keyframe tables for 12 request modes x 3 kinds (item, fish held lower, mail: fortune slip or anything in the post office). It finishes when scale ~0 (F32_IS_ZERO) at the end. The clip protocol: only the master changes the mode, and the target swaps in during TRANS/RETURN_WAIT. Field draw covers the 3x3 acres; river (SE 11, all 9 acres) or waves (SE 28, current row, z+175); the 2 nearest sound sources play. Frogs May-Aug at 18-21h and 4-6h. 300-frame beach wave and colour cycle. Tree effects: variant folding (palm/cedar/gold/xmas flags); lifetimes shake 22, small 18, large 82, cut 98; leaf schedule with cherry leaves in term 4 (Apr 1-8); _SMALL variants would index -1 (latent). Katrina's fortune tent (ac_buggy) opens during the Gypsy event within sqrt(1200); enter when facing north within sqrt(480); lit before 5:00 or from 18:00; despawns on acre change (no borderless fix, like the yatai). Ported: hand_over_item.rs, field_effects.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>286</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HUD (claude): the item-name bubble ('watch my step') has modes idle -&gt; tail pops (2+2 frames) -&gt; grow -&gt; shrink. It is flipped by screen position; width = max(0, w*0.875-17.5)/122.5. The bell counter shows in Nook's 4 shops, Redd, the post office and Able Sisters (scene ids 9,23,24,25,29,12,14,46, gcc-verified), but not during the part-time job or Nook's raffle. Money = wallet + bell bags in pockets (100/1000/10000/30000); it eases at 0.1 with max step 10000 and a coin SE capped at 300 frames. Flip clock: 6 digit animations start only when all are idle (12-hour, 0/12 show 12). The visibility debounce: READY_NET waits 50 frames, leaving non-TRUE 30, leaving TRUE 50, TALKING immediate. It moves left when the player is bottom-right for 10 frames, swapping only while faded out. Ported: hud.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>287</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Feng shui (claude, m_huusui_room*): run for the active resident only (not on the part-time job, not visitors). Room bands are units &lt;= start (north/west) and &gt;= max-start-1 (south/east); start = 1 for a 1x1 in the 6-unit room, else 2. All of a piece's units must be in one band. Yellow: money +4 west. Red: goods +8 east. Orange: +2/+4 north. Green: +2/+4 south. Lucky: +4/+8 anywhere. Faced pieces facing the touching wall cost money 10 / goods 5. Rooms summed: main 6/8/10 units, upstairs 8, basement 10. Goods capped at 40, halved, rounded up. Data: 1266-entry table (type, has_face) generated by gcc harness. Ported: room_scoring.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>288</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Happy Room Academy (claude, m_mark_room*): daily schedule: non-members get the welcome letter (0x1EF). Members are scored when the house changed; otherwise 2/10 chance of a hint letter (0x1DC+i, cycling 19 hints). Scoring over interior units of both layers. Base points by acquisition type: shop 51, event 412, birthday 1000, lottery 1029, NES 1983, fossil 300/1000, island 1300... plus wall/floor source. Necessities (chair, dresser, wardrobe, table, bed): same series +16000, else +4400. Base series (10 items each, verified) complete +48000, wall+floor +10000 or one +4800. Theme complete with matching wall and floor: 7000/item +15000. Theme obstacles -4000 each. Set series 3000/item. Lucky +777. Facing a wall -800. Clutter -1 per item. Floor at 0. Rewards: 70000 -&gt; model house (0x3024), 100000 -&gt; 0x3028. Letter choice by bits x RANDOM(3). Bugs preserved: CountCharactor reverse mode, theme recommendation wrong item category, 'hutaba'. Only the 913-item 'other' series exceeds 32 members, so PPC-vs-x86 shift semantics never matter. Ported: room_scoring.rs + generated room_scoring_tables.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>289</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Menu overlays (claude): clock setting edits hour/min/month/day/year (years after 2000). Wraps and re-validates like the birthday picker; a year change on Feb 29 drops the day to 28. The clock-hand spin moves 12 dial-minutes per frame and locks input until it arrives. RESEARCH FACT: closing the normal clock menu with any changed y/m/d/h/min sets Save cheated_flag (time-travel detection). The PC port extends the year range to 2099. Warning catalog: 28 slots; 5-8 are empty, including SELL_QUEST_ITEM, so a blank box would show. Only the mailbox warning is Yes/No. Diary prompt: 'let anyone else see this diary?', 30-frame cursor pulse. Inventory stacking: tickets (same month, max 5), wisps (max 5), stationery (same design, max 4). @BUG: only the held item's condition is checked (the same check is written twice). Bell bag from wallet: 42-frame hand wait, display step -(amount/42). Card-mail page turn: 40 frames, 100*sin(t*4.5deg), swap at 20. Ported: menu_overlays.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>290</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Camera (claude, m_camera2): goal distance 620 (talk/cust_talk 290); pitch -135deg (talk -164.114, cust -165.2125; gcc: -29876/-30076); yaw -180. Indoor normal-mode zoom steps: dist -280/0/+300 with pitch -23.24/0/+19.12 deg (indexed by distance) and yaw -/+16.1 deg. Outdoors the camera tilts by z_ratio*250 in the south half of acre row 1. Polar eye placement; border box 110 in from the acre (x1.5 long border, -15 outdoors). Culling: talk/cust &gt;= 15 frames, item/simple &gt;= 6, door morph &lt; 70; cull area spans the talkers' X widened by width, never narrower than eye X +- width, and only south of the centre. Mic fixed in the scenes flagged by a 52-entry table (script-verified). The per-mode state machines stay in C. Ported: camera.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>291</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Bugs / quirks catalogue from this pass (claude 2026-10-11): (1) m_lights delete-cursor double division. (2) m_actor_shadow SetTexScroll missing return (retail UB; PC fixed). (3) m_view center.x set three times (BUGFIXES fixes). (4) m_warning_ovl 4 empty slots incl. SELL_QUEST_ITEM. (5) m_mark_room_ovl CountCharactor reverse mode broken; theme recommendation uses the wrong item category; 'hutaba' series name. (6) mRmTp_MakeFtrNoTable can write outside the 16x16 grid for edge furniture (latent; Rust bounds-checks). (7) m_hand_ovl stacking checks the held item's condition twice and never the target's. (8) mEA_CheckLetterCardE returns 2 for the last card. (9) effectbg _SMALL variants fold to index -1 (latent). (10) ac_intro_demo TAKEN/FREE house param names inverted vs the check. (11) ac_ride_off_demo stores its 'Y' start constant in Z. (12) PC: the fortune tent keeps retail acre-change despawn (no borderless fix), like the yatai. (13) Flagged to owners: furniture.rs ftr_idx_2_item_no omits the FTR0/FTR1 0x1000/0x3000 bases that C mRmTp_FtrIdx2FtrItemNo adds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>292</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Code addition (2026-10-11, claude, task port-engine-level-modules): new rust/src game_math.rs + generated game_math_tables.rs, controller.rs, lights.rs, view.rs, actor_shadow.rs, engine_tables.rs, game_string.rs, demo_actors.rs, hand_over_item.rs, field_effects.rs, hud.rs, room_scoring.rs + generated room_scoring_tables.rs, menu_overlays.rs, camera.rs. holiday_scenery.rs switched to the shared helpers. Generators: tools/gen_trig_tables.py, tools/gen_room_scoring_tables.py (gcc harness), tools/gen_actor_profiles.py. 8 new pc_* exports (unique): pc_math_sins, pc_math_atans_table, pc_math_check_percent_abs, pc_mcon_calc, pc_vibctl_program_len, pc_actor_dlftbls_num, pc_present_demo_follow_rate, pc_intro_demo_start. No C callers rewired. Checks: cargo check host + i686-pc-windows-gnu (lib + tests) clean; clippy clean except intentional indexed loops; unit tests written, NOT run (no-tests rule). Kept in C by design: all GBI emission, the m_tag_ovl UI (8,946 lines; bell-bag rule ported), the hand_ovl drop flows, the camera per-mode procs. DOCUMENTATION.md section 'Engine-Level and Misc Modules'.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K292"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6763,6 +6763,116 @@
       <c r="B292" t="inlineStr">
         <is>
           <t>Code addition (2026-10-11, claude, task port-engine-level-modules): new rust/src game_math.rs + generated game_math_tables.rs, controller.rs, lights.rs, view.rs, actor_shadow.rs, engine_tables.rs, game_string.rs, demo_actors.rs, hand_over_item.rs, field_effects.rs, hud.rs, room_scoring.rs + generated room_scoring_tables.rs, menu_overlays.rs, camera.rs. holiday_scenery.rs switched to the shared helpers. Generators: tools/gen_trig_tables.py, tools/gen_room_scoring_tables.py (gcc harness), tools/gen_actor_profiles.py. 8 new pc_* exports (unique): pc_math_sins, pc_math_atans_table, pc_math_check_percent_abs, pc_mcon_calc, pc_vibctl_program_len, pc_actor_dlftbls_num, pc_present_demo_follow_rate, pc_intro_demo_start. No C callers rewired. Checks: cargo check host + i686-pc-windows-gnu (lib + tests) clean; clippy clean except intentional indexed loops; unit tests written, NOT run (no-tests rule). Kept in C by design: all GBI emission, the m_tag_ovl UI (8,946 lines; bell-bag rule ported), the hand_ovl drop flows, the camera per-mode procs. DOCUMENTATION.md section 'Engine-Level and Misc Modules'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>293</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-11, claude): task port-buildings-scenery-actors covered 33 actor files from ac-decomp @ 09ca8e8 (the primary source; .c plus _move/_draw/_clip .c_inc and headers, extracted with git show). Files: conveni, super, cottage, tent, toudai, lighthouse_switch, windmill, douzou, structure(+clip), reserve, pterminal, mikanbox(+clip), mikuji, nameplate, sign, mailbox, mural, kago, dump, tama, rope, ball, goza, garagara, misin, mbg, sample, dummy, flag, htable, animal_logo(+misc), radio. Diffed against ACGC-PC-Port: 21 files differ, mostly 60 Hz/dt scaling (ball, garagara, misin, flag, window-light fades, statue sparkles, lighthouse counters, mailbox SE accumulator). Message ids, profile ids, DEG2SHORT_ANGLE values (mailbox open 6961, mbg spin 47) and the 83-row structure setup table were evaluated with mingw32 gcc. page_table/index_line_table/unit_offset were script-checked against the C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>294</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Shops (claude 2026-10-11): Nook's Nook 'n' Go (ac_conveni) and Nookway (ac_super) share one door state machine (close_wait, open_wait, close_door, open_door, pl_into_wait). Door check point (x-14, z+76) / (x-38, z+96). Entry: shape rotation strictly between 90 and 180 deg and d^2 &lt; 260 / 240; 'near' at d^2 &lt; 800 / 820. Doors open only for status OPEN (2) or OPENEVENT (6). Exit spot (x-42, z+98.57) / (x-62, z+118.57); talk distance 100 / 120. Closed messages: raffle day after 6:00 -&gt; 2006 (PRE) or 2007; otherwise PRE/END closed (1998/1999), PREEVENT 2002/2003, ENDEVENT 2009, RENEW 2008. QUIRK: Nookway's default (open) case uses MSG_SHOP2_CLOSED_NORMAL 1999, where Nook 'n' Go uses MSG_SHOP_OPEN 1997.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>295</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lighthouse (claude 2026-10-11): ac_toudai beam runs only when mSC_LightHouse_Switch_Check passes and sec &gt;= 18:00 or &lt; 5:00. Animation keyframes 1-100, repeat, start 51; lightout waits for frame 51. aTOU_color_ctrl: t = |frame-51|, t=0 sets (220,240); t&lt;10 +4.5/+7, t&lt;30 +1.25/+2.25, t&lt;40 +4.0/+0.5 (sign by side of 51); t&gt;=40 eases to 0 with add_calc(1-sqrt 0.7, 50, 0.5); env alpha eases to 255 with 1-sqrt 0.9. Door: |dx|&lt;20, -65&lt;dz&lt;0, facing within +-0x2000. The FG unit-on code clears buried items 0x2A-0x42 and 0x5C. PC clamps the colours to u8 and enlarges structure slots to 0x300 because TOUDAI_ACTOR grew.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>296</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Lighthouse switch (claude 2026-10-11): nice status OFF outside 18-5h; SWITCH_ON at night outside quest period 1; LIGHTHOUSE_PERIOD in period 1, where the player presses A within 33.5684 of (180,100) facing 135 deg +-45. Pole: two cranks (speed set to 0.065 at timer 0, 0.85*0.065 at 30, each easing via add_calc 0.09) for 48 frames, then +0.0035/frame, clamp 0..0.5. Off: -0.001/frame to 0.1, add_calc to 0.17, reverse frames 100-&gt;1 at 0.17, off_timer 49, then the switch-off animation. Switch SE at anim frame 20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>297</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Cottages/tent/statues/windmill (claude 2026-10-11): cottage door SE frames in {10,14,35,50} / out {2,8,33,40}; my-door test d^2&lt;1600, dx+dz&lt;40, angle in (-DEG(180), -DEG(90)), A. GCC FINDING: -DEG2SHORT_ANGLE(180.0f) evaluates to +32768 in mingw32 gcc at -O0 and -O2, so the check is unreachable; the PC port hard-codes -32768; retail MWCC must fold differently. The islander's light needs sched IN_HOUSE + at home + night, except while the player leaves; the AUS build uses 'not sleeping'. BUG: the tent despawn compares the tent's block with itself, so it never despawns. Tent light before 5:00 / from 18:00; door: rotation 0x6000-0xA000, d^2&lt;1600 from z+40. Statues: offsets x{0,200,-40,160} z{200,200,280,280}; sparkle base {5,15,20,30} + rand*{10,30,40,60}; talk |rot|&gt;=0x6000, &lt;=50 units, +-0x1800; Resetti pending -&gt; reset_type 4. DATA QUIRK: girl face-7 eye texture = boy face 7. Windmill: no ct, never sets action_proc, so move calls NULL (dead code).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>298</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Structure manager (claude 2026-10-11): ac_structure has 9 actor slots (aSTR_ACTOR_TBL_COUNT) plus overlay buffers. setupInfo_table has 83 rows (profile, aSTR_TYPE, aSTR_PAL) indexed by name - STRUCTURE_START (0x5800); ids below NPC_HOUSE_END (0x50EE) go to PROFILE_HOUSE (40). The tent row reuses KAMAKURA type/palette (243/26/67). The door-return request type is 4, or 5 after a reset. Generated by tools/gen_structure_table.py (gcc-evaluated enums).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>299</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>K.K. show / mikanbox clip (claude 2026-10-11): the text roll uses strings 0x77B-0x7FE, 10 lines per page (17-entry page_table); 32 index lines are drawn at 0.9*0.85. Alpha is 0 below 40 or above 446 (50 Hz 372), ramps (t-40)*3.1875 until 120, fades after 366 (292). Song = random uncollected among the first 52 airchecks (0x2A00..ITM_MINIDISK52); all collected -&gt; bits reset. BGM = BGM_TOTAKEKE_LIVE0 + song. Show length FRAMERATE_TIMER(4800). Hidden cameo: SP_NPC_MAJIN5 (0xD06B) spawns if the clock is 20:45:00-20:55:00 and the show timer is in [3600,3610) (50 Hz [3000,3010)); it is flagged for deletion at show end. The strum frame is 48*pct (3-beat) or 64*pct (4-beat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>300</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Mailbox/flag/raffle (claude 2026-10-11): mailbox opens with A by the owner facing within 6961 (38.24 deg) of rot-0x2000; Resetti pending with reset_count&lt;3 (AUS &lt;4) -&gt; reset_type 5. Flag up while mail present; owner hears SE 0x43B each second (PC uses an accumulator). BUG: dt frees only kf0. Island flag: up curve 72.5-&gt;110 (frame 55)-&gt;132.5 (frame 100), piecewise quadratic at 15/55/70/100; down 40 frames, midpoint 16; the design goes to island.flag_design. Raffle drum (garagara) only on fukubiki days; the ball spawns at anim frame 46, vel_y -0.15-0.1r, vel_xz 0.225+0.1r, angle 90 deg +-11.25; tray +-20 x, +-7 z, floor src.y+2; wall reflect x0.985, bounce x-0.4, roll x0.99, gravity 0.15, max fall 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>301</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Other props (claude 2026-10-11): harvest tables place the knife-and-fork at unit (+1,+1) unless the player owns one; the pickup probe steps 3 units with sector offsets {0,+2,-2}, adding each step to the previous (quirk), radius 56. Signboards wobble in (amplitude x0.4, freq +750 per half-cycle) until &lt;0.0002; debug NMREG0=1000 turns trees into random signs (100: every other empty unit). Reserve/notice signs: msg 11053+idx (6-8 insert fruit + Tom Nook), 0x42 -&gt; 11074. Nameplate 4969, dump 4970, flag 12390. Aerobics radio: note effect every 36 frames at (2,0,-10); K.K. songs on house radios are aMR_RadioCommonMove, not ac_radio. Sewing machine: 1 in 3 uses a player design, else a random shop shirt. Mbg debug platform: sin*60 sway, 2 deg/frame, spin 47/frame. Mural: TAKREG debug design grid. Kago/tama: red/white variant = npc_id - base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>302</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>e-Reader terminal / title logo (claude 2026-10-11): ac_pterminal sends the e-Reader program (mGcgba_send_eAppri: ok 0x3DF4, fail 0x3DF1, no GBA after 60 frames 0x3DF3), then reads a 256-byte card: header 24, body 192, footer 32, paper%64 @248, present BE @249, npc_id BE @251, header_back_start (clamped 23) @253, card_no BE @254. A card already used (mEA_CheckLetterCardE) is ignored; the sender must be SPNPC (0xD) or NPC (0xE); mail goes to the first free home mailbox slot. BUG: ITEM_NAME_GET_TYPE(npc_id == NAME_TYPE_SPNPC) is always 0, so the SPNPC password mail type is never set. Title logo: fly-in 121 keyframes (50 Hz 101) at speed 0.5; back fade-in rate 20 to max 220; copyright alpha +63; PRESS START pulse 127.5+127.5 sin, half-wave 50 frames rising / 22 falling. PC adds a settings menu and reloads the save after the title demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>303</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Code record (claude 2026-10-11): new rust/src/buildings.rs (shops, lighthouse + switch pole model, cottages, tent, statues, structure pool + generated STRUCTURE_SETUP), props.rs (mailbox, island flag curves, raffle ball physics, harvest fork probe, sign wobble, notice messages, e-Reader letter parser, title logo pulse, misc props), kk_credits.rs (K.K. roll, song choice, show timer/cameo). New tool tools/gen_structure_table.py. C ABI: pc_toudai_night, pc_str_setup_profile, pc_mkbc_roll_alpha. No C rewiring. cargo check host + i686 clean (lib+tests), clippy clean for the new files, tests written but not run. DOCUMENTATION.md section 'Buildings, scenery and household actors'.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K303"/>
+  <dimension ref="A1:K309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6873,6 +6873,66 @@
       <c r="B303" t="inlineStr">
         <is>
           <t>Code record (claude 2026-10-11): new rust/src/buildings.rs (shops, lighthouse + switch pole model, cottages, tent, statues, structure pool + generated STRUCTURE_SETUP), props.rs (mailbox, island flag curves, raffle ball physics, harvest fork probe, sign wobble, notice messages, e-Reader letter parser, title logo pulse, misc props), kk_credits.rs (K.K. roll, song choice, show timer/cameo). New tool tools/gen_structure_table.py. C ABI: pc_toudai_night, pc_str_setup_profile, pc_mkbc_roll_alpha. No C rewiring. cargo check host + i686 clean (lib+tests), clippy clean for the new files, tests written but not run. DOCUMENTATION.md section 'Buildings, scenery and household actors'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>304</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-11, claude): task port-calendar-radio. Sources from ac-decomp @ 09ca8e8 (primary): m_calendar.c, m_calendar_ovl.c (+ draw .c_inc), m_calendar(_ovl).h, ac_radio.c (+ move/draw), furniture ac_radio_test.c and ac_sum_radio01/02.c, ac_my_room.c / _move / _melody. Diffed against ACGC-PC-Port: m_calendar.c identical; m_calendar_ovl.c dt only (add_calc wrapper, 37*dt slides, blink timer += dt with while-wrap); ac_radio/ac_radio_test use 60 Hz tick loops; ac_radio despawns only when the player is &gt;1 acre away. FTR indices and BGM ids were evaluated with mingw32 gcc. The 29 mSC_EVENT ids and the fixed (16) and weekly (8) event tables were script-checked against the C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>305</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Calendar save (claude 2026-10-11): mCD_player_calendar_c is 0x68 bytes: played_days[12] and event_days[12] (bit per day), event_flags u16, edit u8 (diary lock), pad, year u16, month u8. Flags: bit0 'MOTHERS_DAY' (actually set by event 11 = Father's Day, June), bit1 Town Day, bit2 Meteor Shower, bit3 Founder's Day, bit4/5 Harvest Moon Sep/Oct, bit6 Officer's Day. Every write runs check_delete: year==0 or a gap of 12+ months -&gt; clear; otherwise the months in between are cleared (forward: the months after the stored one; backward: the stored month downward), and so are the days after today in this month, together with any flags whose day is still ahead. BUG: check_delete(player_no) calls mCD_calendar_clear(-1), wiping the CURRENT player's calendar, not the checked one; the calendar overlay calls it for the viewed player, so viewing a stale calendar erases your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>306</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Calendar overlay (claude 2026-10-11): builds 36 month entries (last/this/next year). A cell byte = day (5 bits) | type (3 bits: 0 none, 1 normal, 2 Sunday, 3 event, 4 today, 5 'undefined' = don't recolour). Icons only for the last 12 months: 2 = attended (flag or event_days), 1 = played. Fixed events: Jan 1, Feb 2, Apr 1, Apr 5-7 cherry blossom, Apr 22, May 1, Jul 4, Aug 12, Aug 21, Oct 31, Nov 11, Dec 1, Dec 23, Dec 31. Floating: Mother's Day 2nd Sun May, Graduation 2nd Fri Jun, Father's Day 3rd Sun Jun, Labor Day 1st Mon Sep, Explorer's Day 2nd Mon Oct, Mayor's Day 1st Mon Nov +1, Harvest Festival 4th Thu Nov, Sale Day +1. Fishing tourney every June/November Sunday; sports fairs on the equinoxes; Town Day in July; harvest moon (lbRk table); birthday (type 5). Max 12 events per month and 6 per day; attended events get bit 0x80 (birthday = played that day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>307</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Calendar input (claude 2026-10-11): the stick has 4 cardinal areas (diagonals = centre, deadzone 0.2); only left/right page, within +-11 months of now. C-up in month view slides back to the current month through every page between (37 units/frame, the last page eases with add_calc 0.4/37/1.25). A = day view (panels swap between y 0 and -100); B = back; B/START in month view closes. Day cursor: C-left/right by day, C-up/down by week, except that with several events C-up/down scroll the event list first. Cursor blink is a 60-frame triangle wave. Town Day's name gets the town name prefixed. A on a day opens the diary at that month: own (arg 0), other (arg 1), or the LOCK_DIARY warning if their calendar.edit is set. BUG (US/JP): the Father's Day attended icon tests lbRTC_Week(day+1) so it shows on the Saturday before; AUS uses lbRTC_Week(day), which misses the 21st. Feb 29 birthday in a non-leap year -&gt; cell 37 (out of range).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>308</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Radios / room music (claude 2026-10-11): K.K. discs are items 0x2A00+n (55); stereos play BGM_MD0 (128)+n, K.K. live is 192+n, aerobics BGM 27. A placed stereo picks a random owned song from homes[].music_box (or the cottage's); the decomp's '@BUG missing break' is harmless. Songs not in the music box are removed on room load; the islander's cottage plays mNpc_GetIslandMDIdx on its first stereo. One stereo at a time; reserve -&gt; apply when timer 0, not a shop, no message. Stereos add a positional voice with a per-model speaker preset (Conpo 1-16: retro stereo 1 ... kiddie stereo 16, default 1). QUIRK: stopping always deletes the positional voice, even after the aerobics track. Aerobics radio furniture (FTR 1011): KONPU effect every 36 frames, y-3, angle -22.5 deg. ac_radio actor: DUMMY_RADIO FG, bg offset 3 (offs==0?3:3), note effect 32 every 36 frames at (2,0,-10). Room clocks: 120-frame cycle, stop 0, ticks 15/45. CORRECTION to row 301: K.K. songs on house stereos go through aMR_MiniDiskCommonMove; aMR_RadioCommonMove is the aerobics radio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>309</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Code record (claude 2026-10-11): new rust/src/calendar.rs (PlayerCalendar save + check_delete/welcome_on/event_on/event_check, 36-month grid builder with fixed/weekly/derived events and icons, stick areas, page flips, day cursor, blink, diary hand-off) and radio.rs (MD BGM ids, placed-song pick, music-box pruning, BgmInfo reserve/change state machine returning BgmOp, aerobics radio, effect counters, despawn rule, Conpo table, clock ticks). C ABI: pc_cd_event_check, pc_mr_conpo_index. Corrected props.rs and DOCUMENTATION.md (K.K. playback path). cargo check host + i686 clean; no clippy findings in the new files; tests written, not run.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K309"/>
+  <dimension ref="A1:K310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6933,6 +6933,16 @@
       <c r="B309" t="inlineStr">
         <is>
           <t>Code record (claude 2026-10-11): new rust/src/calendar.rs (PlayerCalendar save + check_delete/welcome_on/event_on/event_check, 36-month grid builder with fixed/weekly/derived events and icons, stick areas, page flips, day cursor, blink, diary hand-off) and radio.rs (MD BGM ids, placed-song pick, music-box pruning, BgmInfo reserve/change state machine returning BgmOp, aerobics radio, effect counters, despawn rule, Conpo table, clock ticks). C ABI: pc_cd_event_check, pc_mr_conpo_index. Corrected props.rs and DOCUMENTATION.md (K.K. playback path). cargo check host + i686 clean; no clippy findings in the new files; tests written, not run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>310</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Board update (claude 2026-10-11): merged origin/main (muse/lapis work since 044ca8c7) into local main and pushed. Conflicts in comms.txt, DOCUMENTATION.md and claims.jsonl were append-only and resolved by keeping both sides. Marked docs/need-to-port.md: Birthdays (birthday_ovl.rs, birth_control.rs), Event NPC placement (event_map_npc.rs, go_home_npc.rs), Holiday scenery (holiday_scenery.rs, including the ac_yatai stall prop; ac_ev_yomise NPCs still C), the Buildings &amp; scenery section (buildings.rs, props.rs, kk_credits.rs), Household radio (radio.rs), Calendar overlay (calendar.rs), and the engine-level list (camera/view/lights/controller/actor_shadow/engine_tables/game_string/demo_actors/field_effects/hud/menu_overlays/room_scoring/hand_over_item). Partial notes: ac_goza (props.rs) under Groundhog Day, the rope offset kernel, and the aerobics radio actor. FINDING: origin/main itself fails cargo check --lib with 38 errors in other agents' files (police.rs, museum_display.rs, train.rs, audio.rs, stalk_market.rs, event_day.rs, countdown.rs, ...); the merge adds no new errors; flagged in comms.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K310"/>
+  <dimension ref="A1:K311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6943,6 +6943,16 @@
       <c r="B310" t="inlineStr">
         <is>
           <t>Board update (claude 2026-10-11): merged origin/main (muse/lapis work since 044ca8c7) into local main and pushed. Conflicts in comms.txt, DOCUMENTATION.md and claims.jsonl were append-only and resolved by keeping both sides. Marked docs/need-to-port.md: Birthdays (birthday_ovl.rs, birth_control.rs), Event NPC placement (event_map_npc.rs, go_home_npc.rs), Holiday scenery (holiday_scenery.rs, including the ac_yatai stall prop; ac_ev_yomise NPCs still C), the Buildings &amp; scenery section (buildings.rs, props.rs, kk_credits.rs), Household radio (radio.rs), Calendar overlay (calendar.rs), and the engine-level list (camera/view/lights/controller/actor_shadow/engine_tables/game_string/demo_actors/field_effects/hud/menu_overlays/room_scoring/hand_over_item). Partial notes: ac_goza (props.rs) under Groundhog Day, the rope offset kernel, and the aerobics radio actor. FINDING: origin/main itself fails cargo check --lib with 38 errors in other agents' files (police.rs, museum_display.rs, train.rs, audio.rs, stalk_market.rs, event_day.rs, countdown.rs, ...); the merge adds no new errors; flagged in comms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>311</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Build fixes (claude 2026-10-11): the 38 compile errors flagged in row 310 had already been fixed by muse (b787cda3) and lapis (87614a36, museum_display.rs); cargo check is clean for lib and tests on host and i686. Task fix-clippy-errors cleared the remaining 9 deny-level clippy errors without behaviour changes. (1) attr_walls.rs, decal_circles.rs and segment_map.rs: the 0.7071067811865476 literals became core::f32::consts::FRAC_1_SQRT_2, which rustc confirms is bit-identical (0x3F3504F3). (2) kamakura.rs: kept 3.14 because the C uses the literal 3.14f (ac_kamakura_indoor.c:166); added a commented allow(approx_constant). (3) graphics.rs: pc_gbi_emu64_destroy, pc_gbi_set_segment and pc_gbi_cmds_processed are null-checked C handle functions; added allow(not_unsafe_ptr_arg_deref), so the ABI and callers are unchanged. (4) npc_reply.rs: removed the no-op self.capital_flag = self.capital_flag (the retail-bug comment is kept; the flag is still left uncleared). (5) field_gen.rs test: allow(erasing_op, identity_op) for the row*7+col indices. cargo clippy --lib --tests now has 0 errors (warnings remain).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6953,6 +6953,106 @@
       <c r="B311" t="inlineStr">
         <is>
           <t>Build fixes (claude 2026-10-11): the 38 compile errors flagged in row 310 had already been fixed by muse (b787cda3) and lapis (87614a36, museum_display.rs); cargo check is clean for lib and tests on host and i686. Task fix-clippy-errors cleared the remaining 9 deny-level clippy errors without behaviour changes. (1) attr_walls.rs, decal_circles.rs and segment_map.rs: the 0.7071067811865476 literals became core::f32::consts::FRAC_1_SQRT_2, which rustc confirms is bit-identical (0x3F3504F3). (2) kamakura.rs: kept 3.14 because the C uses the literal 3.14f (ac_kamakura_indoor.c:166); added a commented allow(approx_constant). (3) graphics.rs: pc_gbi_emu64_destroy, pc_gbi_set_segment and pc_gbi_cmds_processed are null-checked C handle functions; added allow(not_unsafe_ptr_arg_deref), so the ABI and callers are unchanged. (4) npc_reply.rs: removed the no-op self.capital_flag = self.capital_flag (the retail-bug comment is kept; the flag is still left uncleared). (5) field_gen.rs test: allow(erasing_op, identity_op) for the row*7+col indices. cargo clippy --lib --tests now has 0 errors (warnings remain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>312</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-12, claude): task port-followups-gyroid-to-snowman resolved the need-to-port.md follow-ups for 8 systems. Sources extracted from ac-decomp @ 09ca8e8 (primary): m_haniwa_ovl.c, ac_haniwa*.c, m_shop.c, m_tag_ovl.c, m_all_grow(_ovl).c, m_cockroach.c, ac_house_goki.c, ac_my_room(_goki).c, m_start_data_init.c, m_fuusen.c, ac_fuusen.c, m_private.c, m_field_info.c, m_map_ovl.c, m_diary(_ovl).c, m_card.c, m_flashrom.c, m_mushroom.c, ac_kamakura*.c, m_event_map_npc.c, m_event.c, m_event_schedule.c_inc, ac_event_manager.c, ac_snowman.c. PC-port diffs: fuusen, house_goki, haniwa_move, diary_ovl, kamakura, snowman, map_ovl are dt/accumulator changes only; m_event.c swaps the ymdh struct fields so packed dates compare correctly on little-endian x86. IDs were compiled from the real m_name_table.h with mingw32 gcc (stub types, includes stripped).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>313</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Gyroid follow-ups (claude 2026-10-12): gcc confirms HANIWA_START 0x15B0, HANIWA_END 0x17AB, name-table HANIWA_NUM 127 (haniwa.rs HANIWA_NUM=3 is mAGrw_HANIWA_NUM, gyroids per renewal). FTR_NO_2_IDX(f)=f&lt;&lt;2, so mSP_RandomHaniwaSelect only yields south-facing ids 0x15B0..0x17A8 step 4, with no duplicates (the count&gt;127 escape is dead). mHW_make_message_interrupt returns the previous message index (one-frame lag); DOREWO stays until a selected tag points elsewhere; other messages clear when the tag returns. CORRECTIONS: mHW_MSG_MOU (6) is set as a literal by mTG_present_open_proc when pockets are full; the stored-slot turnip spoil is mAGrw_SpoilAllPossession (pockets, every room/layer, 4 gyroid slots per house), run after SetDigItem. Buy: affordability counts NORMAL bell bags; the wallet pays first, then bags smallest-first (100,1000,10000,30000); change goes to the wallet; the money roll takes 42 frames, with the step nudged when it is a multiple of 5. QUIRK: mAGrw_SetHaniwa never consumes the last candidate block, so later gyroids can share it. Turnips spoil at the first Sunday after purchase (days = 7 - weekday).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>314</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Cockroach follow-ups (claude 2026-10-12): mCkRh_DecideNowGokiFamilyCount runs at player-data load (m_start_data_init.c, normal and travelling paths), not on house entry. Room entry (aMR_GokiInfoCt) spawns min(saved,3); each spawn does MinusGokiN(1) + CalcCanLookGokiCount(+1). A stomp (aHG_dead_init) does CalcCanLookGokiCount(-1) only; leaving (aMR_GokiInfoDt) adds the visible ones back. So stomping permanently lowers the saved count. Growth: gap &gt; 6 days adds gap-6 when empty, but the FULL gap when roaches already exist; clamp 10. Play time is saved only via mCkRh_SavePlayTime (card save, shop renewal). US/JP cottage update has no year!=0 guard (AUS adds one). check_danna_kill_proc = aMR_CheckDannaKill, registered in aMR_SetClip; BUG: it tests only FTR0_START..=ITEM1_NO_START (0x1000..0x2000 inclusive) or RSV_FE1F, so FTR1 (0x3000+) furniture never squashes roaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>315</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Balloon follow-ups (claude 2026-10-12): aFSN_escape guards on item_tree_fruit_drop_proc but calls fruit_set_proc; if mFI_Wpos2UtNum fails, count stays 0, so the present is never dropped and (deletion needs count==1) the balloon is never deleted. Little shake: the -500 branch is overwritten to 0, so the shake is +500 for 4 frames, then 0 for 4. Present draw: !escaping || escape_timer == 1554 || count == 0 (PC: &lt;= with f32 timers). Timers: start 2000, escape 1554, stuck in tree 18000+1554 (5 min). Escape boxes: map edge 660/3820 x 660/4460 z, station 2040-2440 x 800-960 z. The present resolves when it enters the pockets (mPr_SetPossessionItem -&gt; mPr_DummyPresentToTruePresent): RANDOM(5)!=0 (80%) -&gt; rare-list furniture; else or empty -&gt; mFI_GetOtherFruit (ITM_FOOD_START|RANDOM(4), +1 if equal to the town fruit: 50% bias, oranges only in peach towns).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>316</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Town map follow-ups (claude 2026-10-12): mMP_house_pos_list rows = fgblock_name + 3 (ut_x, ut_z, idx), terminated by 0x03B8; a match needs ut_x == home.ut_x &amp;&amp; ut_z == home.ut_z-1, defaulting to entries[0]; a block missing from the list falls back to the FIRST row's entries[0] (quirk). The contents are still the absent asset. mMP_make_max_no_table scans bz 1..7, bx 1..6 (starts at (1,1), 30 acres), skips border-cliff kinds, substitutes bridge variants, and returns early at count. Cursor frame: N64 ++ then %= 18; PC f32 += dt, -18, (int) at draw. Players: valid privates in order, skipping the current player during the first intro; the rest are 'free    ' with sex -1. The villager label layer comes from npclist house y; the per-block sort is a bubble sort that restarts after every swap (stable). Easing add_calc(0.7,19,1.8), settled below 0.1. The init acre comes from structure_exit_door_data when not on FG with next_scene_id != 0, otherwise the player position. Field label precedence: shop, police, post, shrine, station, dump, museum, tailor, dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>317</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Diary follow-ups (claude 2026-10-12): mFRm_ReturnCheckSum = wrapping sum of u16 words (odd size returns 0 = valid); a block is valid when the sum is 0, and mFRm_GetFlatCheckSum stores the two's-complement. Load paths: mCD_load_set_others_common copies the diary to ARAM only when valid; mCD_SaveStation_NextLand_load_others has @BUG: the ORIGINAL block is bcopied into l_keepDiary, so a corrupt diary checksum leaves design bytes as the diary. Scroll: fixed 16/3 and 16/7, else speed x2 if d&gt;9 (cap 8 read, 2 write), x0.5 if d&lt;7 (floor 1), via chase_f; aim = line*16. Read-&gt;write panel: _28 = -0.6*n^2 until &lt;= -100, giving -101.4 at n=13 (one-frame overshoot), then -100. Play_write copies editor _22/_24 to _48/_46; _18 = min(lines, _24). Body: 31 lines max, width 192; the cursor wraps unless i==30; the trailing newline is trimmed except in PLAY write mode; the empty entry reads text[-1]; read-mode trailing newline draws len -1. 12 dia_win_&lt;month&gt;_tex_rgb_ia8 textures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>318</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Mushroom follow-ups (claude 2026-10-12): placement count = 5 - min/15 during 08:xx, 1 for 09:00-09:14, only on a new day or when active. BUG: the player-acre exclusion `bx != pbx-1 &amp;&amp; bz != pbz-1` skips the player's whole row and column. possible_cols / bitfield are never updated after a pick, so the refill branch is dead and columns can repeat; the row is chosen uniformly among rows with candidates; stale per-acre counts can make a pick place nothing; the 'bruh' break (ut_z = UT_Z_NUM) ends the scan. Clear count = |floor15(now) - floor15(saved)|/15 minutes, in EITHER direction (setting the clock back also clears). Startup mMsr_FirstClearMushroom passes acre (0,0) (nothing spared) and never checks the season. Valid trees: tree, cedar, gold (+shovel), the 5 fruit trees, palm, and money trees 100/1000/10000/30000 (gcc ids); the ut_x&lt;15 &amp;&amp; ut_z&lt;15 bound lets column-0 trees wrap the -1/+15 offsets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>319</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Igloo + snowman follow-ups (claude 2026-10-12). Igloo: PC anim_frame += dt, wrapped at 1024 (retail frame_counter), driving the candle flip (frame/6)&amp;1 and texture scroll; steam every 8th game_frame (PC: graph_dt_period_elapsed 8.0 with a function-static accumulator shared by all instances); light chase 0.019532442 x dt; despawn on any other acre (PC &gt;1). The camper is 1 random resident (normal_npc_max 1, only selection type is random; already in event_map_npc.rs). aKI_mochi_anime_data (10 keys, 1400 frames) is never referenced. mEv_EVENT_RUMOR_KAMAKURA = 2, KAMAKURA = 3; the rumor runs Jan 2 00:00 to Feb 23 20:00 and is only told in winter. Snowman: REWARD_ITEMS verified (0x1F54..0x1F78 step 4, 0x2619, 0x2719); mail 0x202+rnd on paper 0x200C. move_dist is in common-area part 0 (ball A) / 1 and is written back only for an uncombined, unmoved, not-in-hole, on-map ball. The FG probe tests 9 offsets of 40 units; @BUG *mFI_GetUnitFG NULL deref. Head jump: height 0.6 x (r_head + r_body), r = s*20+10; ofs_y = (8t - t^2/7.5)*25 (peak 3000 at t=30); 5 dust puffs at -90..90 deg at frame 60. snowman_start: no SNOWMAN0/3/6 + mEv_snowman_born_check -&gt; balls A (0x64) and B (0x65). Born check: packed ymdh; end = 05:00 the same day (built before 06:00) or the next day; inclusive, so new balls from 06:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>320</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Build fixes (claude 2026-10-12): lib.rs had lost 32 mod lines (31 in muse commit 1abae7bd 'extend fishrecord.rs', aprilfool in f2c6a5f9 'Port Snowman'), so game_math, all of claude's modules, and muse's notice_overlay/address_book/pause/choice/yomise were silently not compiled. Re-registered. letter_score_tables is intentionally #[path]-included. Re-enabling them exposed notice_overlay.rs NOTICE_HANDBILL_BASE as test-only: a new section had been inserted between #[cfg(test)] and `mod tests`. A crate-wide scan found the same in bee_ant.rs (exported pc_calc_ease would be missing from the C build) and famicom.rs (NESTAG constants); the attribute was moved onto `mod tests` in all three. After this, cargo check host+i686 lib+tests is clean, clippy has 0 errors, and no pc_* export is duplicated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>321</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Code record (claude 2026-10-12): extended haniwa.rs, cockroach.rs, balloon.rs, town_map.rs, diary.rs, mushroom.rs, kamakura.rs and snowman.rs with 'Follow-ups resolved' sections (before each existing test module) plus followup_tests modules (written, not run). Corrected haniwa.rs notes (MSG_MOU used, SpoilAllPossession, gcc-verified range, HANIWA_NUM meaning). Re-registered 32 modules in lib.rs; moved 3 misplaced #[cfg(test)]. docs/need-to-port.md: the 8 follow-ups are marked RESOLVED; DOCUMENTATION.md has a new section.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7053,6 +7053,66 @@
       <c r="B321" t="inlineStr">
         <is>
           <t>Code record (claude 2026-10-12): extended haniwa.rs, cockroach.rs, balloon.rs, town_map.rs, diary.rs, mushroom.rs, kamakura.rs and snowman.rs with 'Follow-ups resolved' sections (before each existing test module) plus followup_tests modules (written, not run). Corrected haniwa.rs notes (MSG_MOU used, SpoilAllPossession, gcc-verified range, HANIWA_NUM meaning). Re-registered 32 modules in lib.rs; moved 3 misplaced #[cfg(test)]. docs/need-to-port.md: the 8 follow-ups are marked RESOLVED; DOCUMENTATION.md has a new section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>322</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Authorized test run #15 (2026-10-12): Philip authorized running the tests for task fix-new-open-items. The Windows test binary failed to link (MSVC and mingw32) because vi.rs/profiler.rs/lib.rs import C/SDL symbols; Linux gc-sections hides this. Added rust/src/test_c_stubs.rs (cfg(test) only, inert definitions of g_pc_running/verbose/window/nes_active, pc_emu64_frame_* counters, SDL_GetPerformanceCounter/Frequency, SDL_Delay, SDL_SetWindowTitle, pc_platform_poll_events/swap_buffers, pc_gx_draw_pending, pc_audio_get_buffer_fill). Run: cargo test --lib --target i686-pc-windows-gnu. First run: 949 passed, 20 failed (exactly muse's list). Final run: 970/970 passed. Standing no-tests rule still applies going forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>323</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Test failures, wrong expectations (claude 2026-10-12, each verified vs decomp): bank withdraw at full capacity buzzes (m_bank_ovl.c keta==0); catalog money_check(1500,100,no bags) is false (mSP_money_check); cockroach wall snap 0x1234 &amp; 0xC000 = 0; countdown anime request needs arg0 &lt;= 2 (ac_count02_move.c_inc:56); design POS2TEXEL(0,8) = 128 bytes; Gracie msg_no_1[11] = 0x073D (duplicates at 10/24 and 11/25); hatsumode root 0 -&gt; 1 -&gt; aHN0_root[1]=5 -&gt; (-60,75); kamakura light on at 05:59:59; lost&amp;found keep_item writes keep_items[count] and OVERWRITES when there is a hole; name_editor fixture patterns overlapped (first-pattern-wins); shop 0x2234 is a paint and CARPET range ends at CARPET_END-4 = 0x2643; snowman (2+1) is not &lt; 3; town board shift discards record 0. Stalk market f32: Sunday max roll -&gt; 130 (reachable); type C factor at max roll == 0.95f; trend B rise 100*1.05f = 104.99999 -&gt; 104; odds subtraction 0.8f-0.6f = 0.19999999 &lt; 0.2f and 0.9f-0.6f &lt; 0.3f, so rolls 0.8 (from B) and 0.9 (from C) pick B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>324</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Real bugs fixed (claude 2026-10-12): (1) countdown.rs + fireworks.rs project_to_radius used atan2(dz,dx) with x=sin,z=cos; search_position_angleY is atans_table(dz,dx) = angle from +Z toward +X, so the snap point was mirrored across the diagonal; it now uses game_math::search_position_angle_y + sin_s/cos_s verbatim. (2) fish_actor.rs pc_fish_behavior_program: ac_gyoei_clip.c_inc rewrites SALMON2 to SALMON and FALLS THROUGH into the KASEKI case group, so the river-mouth salmon variant uses KASEKI while plain salmon uses TEST; the old Rust normalized first and returned TEST. (3) name_editor.rs NG check: mED_ng_word_check loops j = (input_length-len)+1 down to 0, i.e. one more start offset than fits (reads one byte past the logical length); now ported (taken only when the slice has the byte), with a new test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>325</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>lbRTC_IsEqualDate LE bug (claude 2026-10-12): the C stores {u16 year; u8 month; u8 day} in a union with int raw and returns sign(raw0 - raw1). On GameCube raw = year&lt;&lt;16|month&lt;&lt;8|day; on x86 the day is the MSB. A mingw32 demo shows Jan 31 vs Feb 1 -&gt; OVER, 2025-12-31 vs 2026-01-01 -&gt; OVER, 2027-01-01 vs 2026-12-31 -&gt; LESS (all reversed); equality is correct. Callers using ordering: m_all_grow_ovl.c:3036 (growth gate), m_event.c:2904/2937/3013, m_fishrecord.c:23/87/389, m_soncho.c:398/860, lb_rtc.c:629. Equality-only: m_kabu_manager, m_fishrecord 39/54, m_event 1173. Fix: #ifdef TARGET_PC explicit packing in the ACGC-PC-Port src/lb_rtc.c (local working-tree change; that repo's remote is upstream flyngmt), saved as rustimal-crossing fixes/lb_rtc_IsEqualDate_little_endian.patch; it compiles with the real build32 flags. Rust model: go_home_npc.rs pc_lbrtc_is_equal_date (already correct).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>326</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Hatsumode OOB bytes PROVEN (claude 2026-10-12) without the disc, from ac-decomp config/GAFE01_00/foresta/symbols.txt + splits.txt (byte-matching build): ac_hatumode_npc0.c .data 0x53EC8-0x53F80 holds root_table$598 @0x53F20 (4 B), proc_idx_table$599 @0x53F24 (4 B), proc_table @0x53F28 (fn ptrs). So root_table[4] = proc_idx_table[0] = 4, and proc_idx_table[4] = MSB of proc_table[0] = 0x80 (boot.c LoadLink -&gt; JKRDvdRipper::loadToMainRAM with ALLOC_DIR_TOP: foresta.rel is head-allocated just above the DOL, so its code addresses are 0x80xxxxxx). Think 0x80 then indexes the clip dt_tbl (.data 0x36A5C, 46 x 5 B) at 0x36CDC, inside ac_house_clock.c .data: aHC_position_data[8] (SCENE_NEEDLEWORK) pos.z = 0.0f (4 zero bytes) + high byte of House_Clock_Profile.id = 0. All five bytes are 0: think proc NONE, init none_proc1, talk req NONE, talk 0, next 0. The fifth visitor idles; the OOB is benign. hatsumode.rs pc_hatsumode_ready2 now returns (4, 0x80) for index 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>327</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Code record (claude 2026-10-12): rust/src/test_c_stubs.rs (new, cfg(test)) + lib.rs registration; test fixes in bank, catalog, cockroach, countdown, design, event_visitors, hatsumode, kamakura, lost_found, name_editor, shop_interior, snowman, stalk_market, town_board; implementation fixes in countdown.rs, fireworks.rs, fish_actor.rs, name_editor.rs; hatsumode.rs proven OOB constants; fixes/lb_rtc_IsEqualDate_little_endian.patch. docs/need-to-port.md: the 3 New open items are marked resolved; DOCUMENTATION.md has a new section. cargo check host+i686 clean, clippy 0 errors, no duplicate pc_* exports, 970/970 tests.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K327"/>
+  <dimension ref="A1:K328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7113,6 +7113,16 @@
       <c r="B327" t="inlineStr">
         <is>
           <t>Code record (claude 2026-10-12): rust/src/test_c_stubs.rs (new, cfg(test)) + lib.rs registration; test fixes in bank, catalog, cockroach, countdown, design, event_visitors, hatsumode, kamakura, lost_found, name_editor, shop_interior, snowman, stalk_market, town_board; implementation fixes in countdown.rs, fireworks.rs, fish_actor.rs, name_editor.rs; hatsumode.rs proven OOB constants; fixes/lb_rtc_IsEqualDate_little_endian.patch. docs/need-to-port.md: the 3 New open items are marked resolved; DOCUMENTATION.md has a new section. cargo check host+i686 clean, clippy 0 errors, no duplicate pc_* exports, 970/970 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>328</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>need-to-port.md claims (claude 2026-10-12, at Philip's request): muse's Fish follow-ups commit 5d0a9833 was based on a stale copy and had reverted the 8 resolved follow-ups (Gyroid..Snowman) back to an 'In progress (claude)' block. Restored them to Done with (claude) credit, removed the stale block, and updated the Hatsumode Done line (byte values proven by claude). Added (claude) tags to the engine-level lines and the holiday_scenery stall-prop note. Corrected the goza note: props.rs exists (it was unregistered from lib.rs until 2026-10-12) but has no goza kernel, so claude's earlier 'goza ported in props.rs' was an overclaim and the goza mat stays C.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K328"/>
+  <dimension ref="A1:K334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7123,6 +7123,66 @@
       <c r="B328" t="inlineStr">
         <is>
           <t>need-to-port.md claims (claude 2026-10-12, at Philip's request): muse's Fish follow-ups commit 5d0a9833 was based on a stale copy and had reverted the 8 resolved follow-ups (Gyroid..Snowman) back to an 'In progress (claude)' block. Restored them to Done with (claude) credit, removed the stale block, and updated the Hatsumode Done line (byte values proven by claude). Added (claude) tags to the engine-level lines and the holiday_scenery stall-prop note. Corrected the goza note: props.rs exists (it was unregistered from lib.rs until 2026-10-12) but has no goza kernel, so claude's earlier 'goza ported in props.rs' was an overclaim and the goza mat stays C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>329</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Research log (2026-10-12, claude): task port-insect-followups. Extracted from ac-decomp @ 09ca8e8 (primary): ac_insect.c (+ _clip/_move/_draw/_data .c_inc), all 14 ac_ins_*.c (amenbo, batta, chou, dango, goki, hitodama, hotaru, ka, kabuto, kera, mino, semi, tentou, tonbo), ac_insect_h.h, ac_set_ovl_insect.c/.h (~10.9k lines), plus m_player_main_notice_net / pull_net, m_player_lib.c, m_private.c, and config/GAFE01_00 symbols/splits. State machines were extracted mechanically (tools/gen_insect_fsm.py, committed) and cross-checked by hand against the computed setupAction sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>330</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Insect state machines (claude 2026-10-12): PROGRAM_FSM in insect_actor.rs, indexed by P_*, gives each program's actions + transitions + initial + forced. Highlights: chou AVOID-&gt;FLY, FLY-&gt;AVOID, LANDING-&gt;AVOID/HOVER, HOVER/REST-&gt;AVOID/FLY/REST; batta WAIT-&gt;AVOID/CHANGE_DIRECTION/DROWN/JUMP, JUMP-&gt;CHANGE_DIRECTION; tonbo FLY-&gt;FLY_ON_NOTICE/TOUCH_WATER/WAIT, TOUCH_WATER-&gt;REVERSE-&gt;HOVER_WAIT_ON_WATER-&gt;TOUCH_WATER/WAIT; ka FLY-&gt;SEARCH-&gt;ATTACK_WAIT-&gt;ATTACK; mino HIDE-&gt;APPEAR-&gt;APPEAR_STOP-&gt;WAIT-&gt;DISAPPEAR-&gt;HIDE with FALL from each; kera AVOID-&gt;DIVE/DUG/LET_ESCAPE; tentou MOVE&lt;-&gt;WAIT plus AVOID(_MAIMAI) for snails. Every actor_move forces LET_ESCAPE (tentou: LET_ESCAPE_MAIMAI for snails) when netted or when the lifetime expires (bit_3 &amp;&amp; !bit_2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>331</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Insect net/inventory handoff (claude 2026-10-12): aINS_set_catch_range registers (label=actor ptr, pos, range) each frame unless bit_1; the player picks and publishes item_net_catch_label; programs compare the label with themselves. Notice_net: catch type 0 -&gt; insect-&gt;item, bee swarm -&gt; ITM_INSECT08, else ITM_INSECT38 (ant). insect-&gt;item = ITM_INSECT_START (0x2D00) + type for all types; spirit = ITM_SPIRIT0 (0x2D28). mPlib_Get_space_putin_item_forHITODAMA: a spirit with count c stacks onto the first NORMAL pocket in [SPIRIT0, SPIRIT0+5-c) (half-open, so max SPIRIT4), else the first free slot. The collect bit is set except for the spirit; ant/mosquito show the YAJIRUSHI arrow; fanfare 0x4B (already collected) / 0x28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>332</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Insect flags, work slots, spawn metadata (claude 2026-10-12): insect_flags destruct = delete at next cull unless netted; bit_1 = no catch request; bit_2 = fleeing (no UniqueWallCheck, no lifetime escape); bit_3 = lifetime 216000 expired; bit_4 = wall check on (setup default TRUE; batta/dango/kera/mino/tentou clear it). goki flag==4 -&gt; special catch range. WORK_SLOTS documents all 14 families (decomp macro names where they exist, e.g. aIGK_TARGET_ANGLE, aIKR_UT_X, aITB_GET_BK_CENTER_X; chou s32_work1/2 = target unit, f32_work0/1 = orbit centre). Spawn: aSOI_ins_make_sub sends {type, unit corner + 20/20, extra_data, game} via make_insect_proc(&amp;init, FALSE = MAKE_NEW, slots 0-7); ants via make_ant_proc (deferred). extra_data: 0 normal, 1 released (aINS_make_actor, MAKE_EXIST, slot 8), cockroach 4 on tree / 6 on spoiled turnip 0x2F03 -&gt; goki init branches (flower/tree/item).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>333</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Insect overlay + chou search + quirks (claude 2026-10-12): aINS_overlay (US .bss 0xC0B10, 0x5418 = 3 x aINS_overlay_entry_c 0x1C08 = 0x1C00 data + _1C00 + _1C04) is only written by aINS_actor_ct (_1C00 = PROGRAM_NUM, _1C04 = 0) and never read: vestigial N64 overlay slots, NOT model tables. chou loop corners (+-10) in order (10,10),(10,-10),(-10,10),(-10,-10); steer 0x800 if &lt;15 else 0x400; after 4 corners -&gt; aICH_flower_search: 1 fqrand always (&lt;0.5 on a flower = stay; purple never searches), then RANDOM(3) x, RANDOM(3) z over {-1,0,1}, axes outside 1..14 revert, the target must be walkable (mFI_CheckFGNpcOn); ground &gt;= 20 above -&gt; one retry over {-2,0,2} (2 more draws). RANDOM(n) = (int)(fqrand()*n). Quirks: dango SPIDER case leaves EMPTY_NO (unreachable); kabuto/semi only accept plain CEDAR_TREE (decomp @BUG); spirit relocation's literal 5 == mEv_GHOST_HITODAMA_NUM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>334</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Code record (claude 2026-10-12): insect_actor.rs follow-up section (overlay constants, spawn_extra_data, spawn_position, regist_space, insect_item, net_catch_item, spirit_putin, catch helpers, flags module, WORK_SLOTS, ProgramFsm + generated PROGRAM_FSM, chou loop/search kernels) + followup_tests (not run); tools/gen_insect_fsm.py. cargo check host+i686 clean, clippy 0 errors, no duplicate exports. need-to-port.md Insect follow-ups marked resolved; DOCUMENTATION.md has a new section.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K334"/>
+  <dimension ref="A1:K336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7183,6 +7183,26 @@
       <c r="B334" t="inlineStr">
         <is>
           <t>Code record (claude 2026-10-12): insect_actor.rs follow-up section (overlay constants, spawn_extra_data, spawn_position, regist_space, insect_item, net_catch_item, spirit_putin, catch helpers, flags module, WORK_SLOTS, ProgramFsm + generated PROGRAM_FSM, chou loop/search kernels) + followup_tests (not run); tools/gen_insect_fsm.py. cargo check host+i686 clean, clippy 0 errors, no duplicate exports. need-to-port.md Insect follow-ups marked resolved; DOCUMENTATION.md has a new section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>335</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Villager AI research, PAUSED (claude 2026-10-12; task port-villager-ai-schedules stays claimed; research done, no Rust written yet). Gap analysis vs existing Rust: schedule tables + manager already in npc_ai.rs; m_npc_walk.c is effectively unported; ac_set_npc_manager.c is mostly unported; m_quest.c lacks the first-job errand chain and delivery/errand index helpers; m_npc.c lacks the island, HP-mail and moving-out subsets. Walk (m_npc_walk.c, PC identical): per-looks goal tables (shrine / random villager-home acre / empty acre / own home) by time; DecideNpc picks a random unused villager whose current slot has goals; 5 walkers (now_npc_max/3); QUIRKS: GetAloneBlock draws RANDOM(30 - villager_count), counting villagers not acres; GetNearGate tests WEST||WEST (decomp BUG), uses 16-ut for the east/south distance, and since UT_BASE_NUM=16 every gate passes so the LAST gate on that side wins; fallback goal acre (4,3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>336</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Set-NPC manager (ac_set_npc_manager.c) research (claude 2026-10-12): scope = player's next acre (guest scope +1 unit); regular villagers in scope are made at a safe unit: off a broker tent/designer car 4x4 footprint, then a 3x3 search, then a random safe unit in the acre. Guests appear at a random gate of their own acre facing the player (way UP/DOWN/LEFT/RIGHT -&gt; NORTH/SOUTH/WEST/EAST gate). Off-screen walking: every 7 s (PC: dt accumulator) a walker moves one unit toward its next acre (larger axis), never into the player's acre; an acre with &gt;=3 villagers makes walkers STAY_IN_BLOCK; on arrival they stay 108000 frames (30 min), then rotate the walk slot (goal = own home) or head home; go-home tries home acre, then N/S/W/E neighbours, skipping the event acre and the player's; a guest leaving sets timer 10800 (decomp suspects 108001); in_block count clamps at 14. Event NPCs are placed via the mEvMN map. PC: borderless scope = 3x3 acres, appear range 1, make list = ANIMAL_NUM_MAX. m_npc_schedule.c: missing pieces are only schedule-area slot management (island slot = index 15); first-job/Halloween force current_type=FIELD; PC guards looks&gt;=LOOKS_NUM and scales forced_timer by ticks.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K336"/>
+  <dimension ref="A1:K340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7203,6 +7203,46 @@
       <c r="B336" t="inlineStr">
         <is>
           <t>Set-NPC manager (ac_set_npc_manager.c) research (claude 2026-10-12): scope = player's next acre (guest scope +1 unit); regular villagers in scope are made at a safe unit: off a broker tent/designer car 4x4 footprint, then a 3x3 search, then a random safe unit in the acre. Guests appear at a random gate of their own acre facing the player (way UP/DOWN/LEFT/RIGHT -&gt; NORTH/SOUTH/WEST/EAST gate). Off-screen walking: every 7 s (PC: dt accumulator) a walker moves one unit toward its next acre (larger axis), never into the player's acre; an acre with &gt;=3 villagers makes walkers STAY_IN_BLOCK; on arrival they stay 108000 frames (30 min), then rotate the walk slot (goal = own home) or head home; go-home tries home acre, then N/S/W/E neighbours, skipping the event acre and the player's; a guest leaving sets timer 10800 (decomp suspects 108001); in_block count clamps at 14. Event NPCs are placed via the mEvMN map. PC: borderless scope = 3x3 acres, appear range 1, make list = ANIMAL_NUM_MAX. m_npc_schedule.c: missing pieces are only schedule-area slot management (island slot = index 15); first-job/Halloween force current_type=FIELD; PC guards looks&gt;=LOOKS_NUM and scales forced_timer by ticks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>337</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>npc_walk.rs + npc_set_manager.rs written (claude 2026-10-12, port-villager-ai-schedules): pure kernels of m_npc_walk.c (goal tables script-verified vs C with scratchpad goalcheck.py: all 6 match), schedule-slot pool, and ac_set_npc_manager.c (scopes, appear rules, safe units, off-screen walk, go-home). cargo check host+i686 and clippy clean; tests written, not run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>338</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>quest_firstjob.rs (claude 2026-10-12): m_quest.c first-job chain. Every step: ERRAND/FIRST_JOB, no time limit, progress 2, give_reward off. Furniture records used_ids[0] (used_num 1), letters used_ids[1] (used_num 2); carpet/axe record no used id; notice/open clear the recipient, open sets mEv_SAVED_FJOPENQUEST_PLR0+player. QUIRK: SetFirstJobStart leaves progress 0 = CheckFirstJobFin TRUE. Deliveries indexed by pocket slot; errands by pocket+item and only with item cond QUEST (2). Snowman contest progress 1 in requester's home acre: built records player, pushed apart clears; soccer: progress 2 + requester.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>339</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>npc_life.rs (claude 2026-10-12): m_npc.c life rules. Best friend &gt;= 80; tie: letter beats none, else lbRTC_IsOverTime(best,mem)==LESS so the EARLIER-spoken memory wins. Highest friendship uses &lt;= (last among equals). Move-out (SetRemoveAnimalNo, needs &gt;5 villagers and 0xFF): met-by-all, then met-by-some (QUIRK: inner loop breaks at first player who hasn't met = met by first existing player), then any (QUIRK: count always -1 since ignored&gt;=0||ignored&lt;15 is always true; with ignored=-1 the last villager is unreachable). Move-in rejects resident, last-removed, summer camper; slot free -&gt; goodbye villager -&gt; 0. Has-appeared bit table, OOB reads TRUE, reset when all starter/move-in seen. Talk/patience timers already in dialogue_topics.rs/interaction.rs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>340</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>port-villager-ai-schedules COMPLETE (claude 2026-10-12). Remaining deferred: island + HP-mail parts of m_npc.c (other systems), and C wiring (no pc_* exports yet). Tests for npc_walk, npc_set_manager, quest_firstjob, npc_life not yet run (awaiting authorization).</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K340"/>
+  <dimension ref="A1:K341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7243,6 +7243,16 @@
       <c r="B340" t="inlineStr">
         <is>
           <t>port-villager-ai-schedules COMPLETE (claude 2026-10-12). Remaining deferred: island + HP-mail parts of m_npc.c (other systems), and C wiring (no pc_* exports yet). Tests for npc_walk, npc_set_manager, quest_firstjob, npc_life not yet run (awaiting authorization).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>341</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Authorized test run #16 (claude 2026-10-12): cargo test --lib --target i686-pc-windows-gnu = 990/990 pass, incl. the new npc_walk, npc_set_manager, quest_firstjob and npc_life tests on first run.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K341"/>
+  <dimension ref="A1:K349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7253,6 +7253,86 @@
       <c r="B341" t="inlineStr">
         <is>
           <t>Authorized test run #16 (claude 2026-10-12): cargo test --lib --target i686-pc-windows-gnu = 990/990 pass, incl. the new npc_walk, npc_set_manager, quest_firstjob and npc_life tests on first run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>342</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>GRASS WEAR (claude 2026-10-12, port-nature-weather-assessment): need-to-port's 'grass wear' file m_player_main_remove_grass.c_inc is the WEED-PULLING action, not ground wear. Decomp-wide search (save structs, movement, renewal; git grep wear/trample/footprint) found NO per-tile ground-health state, wear or regrowth on GameCube; footprints are transient eEC_EFFECT_FOOTPRINT effects. Persistent worn grass = City Folk (brief was right to call it unconfirmed). Weed pull: pick-up facing GRASS_A..C (0x0008-0x000A) -&gt; REMOVE_GRASS priority 8, anim ZASSOU1 morph -6; on frame 17, if the unit still holds a weed it flies off at facing + DEG2SHORT_ANGLE2(110)=20024 (gcc), mud effect, sound, rumble. PC identical. -&gt; weed_pull.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>343</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>FIELD ASSESSMENT scoring (m_field_assessment.c, PC byte-identical): scans all 30 acres (5x6 FG_BLOCK_TOTAL_NUM), NOT 25 as the brief says. Item classes by gcc over m_name_table.h: weeds 0x0008-000A; trees = ENV 0x0800-083B + 0x084E-0869 and BG grown 0x005E-0061, 0x0069, 0x0078-007A, 0x007F-0082; flowers 0x083C-084D; trash 0x250E-2510; DUMP 0x583B, dump area unit-4..=unit both axes (DUMP_WIDTH/HEIGHT 4). Acre: trash -&gt; 0; effective weeds (weeds-flowers) &gt;= 3 -&gt; 0; trees &lt;=8:0, 9-11:1, 12-14:2, 15-17:1, 18+:0. Score = perfect + good/2; rank via [0,2,4,7,12,16,255] (17+ = rank 6). MISSING FROM BRIEF: town trash &gt;= 5 forces score 0 and sets saved dust_flag; while set, the scan is skipped (score 0) until a trash pass finds ZERO trash, so one leftover can keeps rank 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>344</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>FIELD ASSESSMENT shrine conditions + streak: conditions tested 0..=current: TREE_LESS trees&lt;=8, TREE_OVER trees&gt;=17 (17 trees still scores 1), GRASS_OVER effective weeds&gt;=5; tree conditions skip bottom row bz=6 and shrine/pool/station/player/museum acres (BLOCKKIND bitflags 4/0x8000/0x20/1/0x20000). More urgent condition takes over; equal one replaces with (int)(fqrand()*3)==1. RETAIL BUG kept: dusty-acre pick never sets set_bad_block, so it always reports the LAST dusty acre with no RANDOM(3). Any condition != NO_CASE CLEARS the golden-axe streak even at rank 6. Streak: first rank 6 stores time with streak 0 (not 1); later adds lbRTC_GetIntervalDays (calendar days, year%4 leap) capped 15; lbRTC_IsOverTime never returns EQUAL, so it only resets when the clock goes backwards; other ranks clear; receiving the axe clears. Callers: start init, daily all-grow, event gap = 1+(day+month*sec)%(7-rank) min 2, shrine talk. -&gt; field_assessment.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>345</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>WIND (m_kankyo_weather.c_inc): init = RANDOM_F(65536) angle (fully random) + fqrand power in today's range; Koinobori 0x6000/1.0. Every 36000 frames: target angle +- RANDOM_F(5461)-5461/2 (DEG2SHORT_ANGLE(30)=5461 gcc), fqrand power, linear over 36000. Gust when gust_timer&lt;=0: draws (int)(fqrand*100)&amp;1, rng1, rng2 in that order; FAST if bit or min==0 -&gt; max+0.3+0.1*rng1; SLOW -&gt; min-0.3-0.1*rng1 (min only 0/0.4/0.6 so lulls are (0,0.1] or (0.2,0.3], never negative); 200+100*rng2 frames via add_calc(0.05,0.05,0.0001); REDUCING add_calc(0.032,0.032,0.000005) back to last power, then gust_timer = fqrand*450+150. Gust-start frame skips the 10-min check. power() clamps 0..1, windmill unclamped. PC: timers f32 minus dt. -&gt; wind.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>346</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>WEATHER start/live (m_kankyo_weather.c_inc, ac_weather.c): GameStart = roll -&gt; event override -&gt; real-work rain to CLEAR/NONE. NormalStart with renew flag: rainbow reserved + gyroid ordered when new CLEAR/SAKURA follows saved RAIN/SNOW; else restore save. Island re-rolled EVERY normal start: fqrand &lt; TAKREG50*0.1+0.8 -&gt; CLEAR/NONE (80%) else RAIN/HEAVY. The same roll also runs LIVE in aWeather_ChangeWeatherTime0 when the renew flag trips mid-play (not in start demos, not on island) and transitions. LEAVES weather is only used by K.K. Slider's concert (totakeke think: HEAVY then NONE) and is stored in common as CLEAR. Title demo table: (SAKURA,LIGHT),(RAIN,NORMAL),(CLEAR,NONE)x2,(SNOW,LIGHT). USA aim level from common intensity, AUS from save. -&gt; weather_actor.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>347</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>WEATHER ACTOR + particles: 100-slot pool, lowest free slot, timer -100 = forever. Request sets aim 0; level steps every 180 frames; at 0, outdoors waits for ALL particles to expire, then switches type at level 1 and climbs. Rain 1/2/3 drops per frame by level, x [-130,130) z [-200,160), 190 above ground, vy -11.5+RANDOM_F(-2.5), life 1000; CORRECTION to brief: splash is time-based (drop freed after 10 frames, splash life 8 at ground y), not a ground approach. Snow &amp; 7/&amp; 3/odd frames, vy drawn before the slot check (RNG consumed when full), life 280. Sakura &amp;7 (light) else &amp;3; leaves &amp;15 else &amp;7; +0.45 x drift. Thunder only Jun-Aug RAIN HEAVY: flash at t2 and t2+20, boom (sfx 0x424) at t2+65, t2=100+RANDOM_F(500), initial 30. Rain ambience 7/8/9, umbrella 0x12/0x13/0x14. Every frame aWeather_CheckWeatherTimer burns 2 RANDOM_F draws (mEnv_DecideWindDirect result discarded). Snow/sakura pre-simulate 40 frames. PC: dt-scaled motion + spawn accumulators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>348</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>KANKYO lighting (m_kankyo.c): 8 light periods start 0,4,6,8,12,16,18,20h; GetNowTerm = first i with start[i+1] &gt;= now (boundary second stays in earlier period); blend get_percent. Tables: CLEAR/SAKURA fine, RAIN/SNOW rain (insect-museum variants); weather &amp; 3 so LEAVES uses fine. Lighting cross-fade 1/600 per frame USA (1/250 AUS); requests refused mid-fade. Rainbow: reserved date only, 09:00-15:00, SUMMER only, fade in 1800 frames, out 108000, gone after 15:30. Window light target: 0 near midnight/noon, lamp rooms 0.22+0.78*(1-lamp%), else 1.0 05:00-18:00. QUIRK (gcc over all seconds): s16 cast makes window light also drop 05:45:45-05:49:43 and 18:10:17-18:14:15. Colour tables/fog/point lights left in C. -&gt; kankyo_env.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>349</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>port-nature-weather-assessment modules (claude 2026-10-12): field_assessment.rs, wind.rs, weather_actor.rs, kankyo_env.rs, weed_pull.rs; existing weather_season.rs (daily table, roll, sakura bug, event override, packing, wind terms) reused, not edited; town_gen.rs assess() is a rewrite-model approximation (no dust_flag/conditions/streak). cargo check host+i686 + clippy clean; tests written, NOT run (awaiting authorization). Brief corrections: 30 acres not 25; dust_flag persistence missing; rain splash timed; island 80/20; grass wear file is weed pulling.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K349"/>
+  <dimension ref="A1:K356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7333,6 +7333,76 @@
       <c r="B349" t="inlineStr">
         <is>
           <t>port-nature-weather-assessment modules (claude 2026-10-12): field_assessment.rs, wind.rs, weather_actor.rs, kankyo_env.rs, weed_pull.rs; existing weather_season.rs (daily table, roll, sakura bug, event override, packing, wind terms) reused, not edited; town_gen.rs assess() is a rewrite-model approximation (no dust_flag/conditions/streak). cargo check host+i686 + clippy clean; tests written, NOT run (awaiting authorization). Brief corrections: 30 acres not 25; dust_flag persistence missing; rain splash timed; island 80/20; grass wear file is weed pulling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>350</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>SUBMENU lifecycle (claude 2026-10-12, port-inventory-submenu; m_submenu.c, ac-decomp 09ca8e8b + PC port): opens only in WAIT with no fade/wipe. START or Y -&gt; inventory; X -&gt; map when map flag set, not in island cottages (SCENE_COTTAGE_MY/NPC) and not in an ocean acre (map param0 1). Gates: no reset, no start_refuse flag/timer, player action allows menu, no first-intro. A press facing within 45 deg of north at a message board -&gt; NOTICE, map board -&gt; MAP param0 0; this path SKIPS the first-intro gate. NPC/object requests (mSM_open_submenu* only stores type + 4 params) bypass all button gates. LINKWAIT: selection buffer = 15 x (EMPTY_NO, slot 15), after_mode 7, audio spec 5 (male or LEDIT param0 0) else 6. END: wait_timer 2 (never read in m_submenu.c), START refuse 1 frame, after_mode 12 -&gt; mscore demo wait. PC: dt-ticked timers; dllcnv returns proc instead of retail's bare return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>351</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>SUBMENU eligibility (mSM_check_item_for_*, gcc-verified ids: cards 0x2523-252F, knife&amp;fork 0x2530, spirits 0x2D28-2D2C, signboard 0x251E; ITEM1 cats money 1 fish 3 minidisk 10 insect 13 kabu 15). No checker -&gt; 0xFFFF (bit 15 too). HANIWA_ENTRUST allows EMPTY slots; QUEST ignores item condition (presents/quest items OK) but not spirits; SELL/GIVE normal-only, SELL excludes money; TAKE param 1 fish only / 2 bugs only; PUTIN_FTR ITEM1 only minus fish/bugs/turnips; MINIDISK music only; SHRINE quest-cond + overdue; EXCHANGE excludes signboard and a fish offered for a non-fish needs water within 120 units (mCoBG_SearchWaterLimitDistN, 12 steps; writes submenu.water_pos); CURATOR allows spirits and money. PC_ENHANCEMENTS curator = donatable + fossils only (non-retail). Collections: insect bit 0x2F2+idx, fish bit 0x31A+idx in furniture_collected_bitfield; 40 each. -&gt; submenu.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>352</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SUBMENU overlay framework (m_submenu_ovl.c): flg_table (item drawer/tag/hand/gyroid portrait) per menu, script-verified; slide start table +-300 speed 75 (script-verified), card-mail inventory and needlework mode 2 from the left. mSM_move_menu: every other frame speed *= 2 (out) or 0.5 (in) clamped 1..75, pos += speed*0.5, truncated to int; odd move dir = in -&gt; PLAY, even = out -&gt; END. Return chain: closing menu splices predecessor to successor, else returns to predecessor, first menu closing ends submenu (unloads sub-overlays in reverse). Input repeat: held C-dirs (getButton &amp; 0xF) | triggers | stick&gt;0.5 as C-dir by 90-degree sector; new input fires, then 25 frames quiet, then every 4th frame (timer 3). Background scroll +0.3535/frame wrap 1024. PC: D-pad folded in (PC_ENHANCEMENTS), dt-ticked repeat. -&gt; submenu.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>353</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>INVENTORY overlay (m_inventory_ovl.c): masks at open: HANIWA_TAKE none; QUEST only slot data1; PASSWORD data1 is the mask; SEND_MAIL used+sendable letters; CPMAIL the opposite (unused or unsendable); MAILBOX all letters; default = eligibility mask, NORMAL/EXCHANGE also all letters. CPMAIL/MAILBOX/HANIWA modes auto-open the companion menu and the inventory follows (OBEY). Cursor = first selectable bit else 0 (letters in send-mail mode). Pages start [inventory, fish, insect]; 40-frame turn y=100 sin(t*4.5deg); at t=20 new page to front, back page replaced only if it was the new one; up-page draw rule by timer. Release flag = water within 120 ahead (or exchange with a fish); shovel flag = fillable dig spot. Debug zurumode2 pad2: C-left +1000 Bells, C-down tools into free slots, C-right 30,000 bags. -&gt; inventory_ui.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>354</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>TAG action menus (m_tag_ovl.c mTG_select_tag_decide_item_normal): priority marked -&gt; PUT_ALL; present cond -&gt; PRESENT; quest cond -&gt; CATCH; signboard outdoors -&gt; SIGN; cards/knife -&gt; TAISOU_CARD; furniture (types 1/3) uses the CLOTH column; spirits (one/many tables identical); paper (0x2000-20FF, stack = (id-0x2000)/64) single -&gt; LETTER else LETTERS; balloons 0x2244-224B; else per-place table by category, tickets with id%8==0 as ETC. Then fish + release_flag -&gt; RELEASE; shovel (0x2202/golden 0x223B) + shovel_flag -&gt; *_BURY variants (not bugs/signboard); first job PLANT -&gt; PLANT_JOB. Decomp '@BUG' `cat==CARPET | cat==WALL` in the basement check is HARMLESS (0/1 operands). Other modes: SELL (marked -&gt; SELL_ALL), GIVE, TAKE-&gt;QUEST_ITEM, SHRINE, PUTIN/MINIDISK-&gt;PUTIN, CURATOR, PASSWORD; non-inventory menus -&gt; CATCH. Tables + enum values script-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>355</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>TAG mail/money/marks: mail menu flags present(1)|unsendable(2) -&gt; [DEF_SMAIL, DEF_SMAIL_PRE, DEF_RMAIL, DEF_RMAIL_PRE]; indoors or unread received font -&gt; ROOM_ variants of the non-present ones; send-mail mode only SEND_MAIL. Money: no menu under 100 Bells; bag options 1/2/3/4 at 100/1000/10000/30000. Marks: CHK/OFF/CLR always allowed; ON/RVS need normal item, not cards/knife/balloon/fish/bug, outdoors not the signboard, in own room not furniture/umbrellas/clothes, first-job outdoors not plants; other rooms never. Sell marks: no money, no turnips on SUNDAY. Mark byte count ((max+15)/16)*2. QUIRK: mTG_bit_chk_all0 returns true if ANY byte is 0 (res |= *flags == 0); no caller uses MARK_CHK_ALL0. -&gt; inventory_ui.rs</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>356</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>port-inventory-submenu modules (claude 2026-10-12): submenu.rs, inventory_ui.rs; existing choice.rs (m_choice, brief's choice-window points already ported), menu_overlays.rs (hand stacking, money sack, card-mail page order), inventory.rs reused untouched. m_hand_ovl.c PC diff 5 lines. Save/flash (m_flashrom.c) intentionally left in C. Brief corrections: board A-press skips first-intro; NPC requests bypass gates; wait_timer never read; CARPET|WALL bug harmless; CPMAIL selectable mail is the inverse of SEND_MAIL; HANIWA_ENTRUST allows empty slots. cargo check host+i686 + clippy clean; tests written, NOT run.</t>
         </is>
       </c>
     </row>

--- a/gamedb_research.xlsx
+++ b/gamedb_research.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K356"/>
+  <dimension ref="A1:K357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7403,6 +7403,16 @@
       <c r="B356" t="inlineStr">
         <is>
           <t>port-inventory-submenu modules (claude 2026-10-12): submenu.rs, inventory_ui.rs; existing choice.rs (m_choice, brief's choice-window points already ported), menu_overlays.rs (hand stacking, money sack, card-mail page order), inventory.rs reused untouched. m_hand_ovl.c PC diff 5 lines. Save/flash (m_flashrom.c) intentionally left in C. Brief corrections: board A-press skips first-intro; NPC requests bypass gates; wait_timer never read; CARPET|WALL bug harmless; CPMAIL selectable mail is the inverse of SEND_MAIL; HANIWA_ENTRUST allows empty slots. cargo check host+i686 + clippy clean; tests written, NOT run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>357</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Authorized test run #17 (claude 2026-10-12): cargo test --lib --target i686-pc-windows-gnu = 1023/1023 after one fix. The only failure was a wrong TEST expectation in kankyo_env fade_and_rainbow: f32 accumulation of 1/600 over 600 frames = 0.9999991, so the weather lighting cross-fade (like the C, which also accumulates f32) reaches 1.0 on frame 601, not 600. No code change needed. New modules field_assessment, wind, weather_actor, kankyo_env, weed_pull, submenu, inventory_ui: 29 tests pass.</t>
         </is>
       </c>
     </row>
